--- a/briefing.xlsx
+++ b/briefing.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal index" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All papers'!$A$1:$I$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All papers'!$A$1:$K$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,7 +625,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rolling archive across 15 journals · last updated 2026-07-14</t>
+          <t>Rolling archive across 15 journals · last updated 2026-07-15</t>
         </is>
       </c>
     </row>
@@ -944,18 +944,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -976,30 +978,40 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Themes</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Keywords</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Abstract</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>DOI / Link</t>
         </is>
@@ -1021,28 +1033,38 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>The Cost of Convenience: A Hedonic Approach to Travel Time Valuation and Cost-Benefit Analysis</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Isaac Mann; David M. Levinson</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
+          <t>Transportation; Housing &amp; real estate; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr"/>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
           <t>This paper presents a novel revealed-preference approach to estimating the value of travel time (VTT) and calculating consumer surplus for the economic evaluation of transport infrastructure. Departing from traditional stated-preference models, we derive time valuations by linking residential rental transactions in Greater Sydney to employment accessibility. We estimate a hedonic price function that controls for unobserved amenities and spatial sorting, recovering VTT estimates consistent with current cost-benefit analysis practice. Furthermore, we leverage the non-linearity of the price gradient, as well as cross-market variation in the price gradient, to perform a second-stage regression without instrumental variables, recovering the structural demand function for accessibility. This allows us to quantify welfare changes from non-marginal accessibility shocks, demonstrated on the Sydney Metro West project, grounding project appraisal in revealed spatial behavior.</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70065</t>
         </is>
@@ -1064,28 +1086,38 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Impact of Place-Based Policy on Land Lease Price and Its Productivity Premium: Evidence From China's Development Zone Program</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Lin Mei; Qiangmin Xi</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr"/>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate; Place-based policy &amp; inequality; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr"/>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
           <t>Combining micro data of DZs, land and firm in China, this study examines the impact of DZs on land lease price and its productivity premium by using Boundary Discontinuity (BD) model and the unconditional distribution characteristic-parameter correspondence method. Under the condition of market-oriented allocation of land resources, the increase in land demand brought about by the agglomeration of firms in DZs and the tight supply of land will jointly promote the land lease price in DZs. Moreover, increasing the DZs' land lease price raises the entry threshold of firms, thereby reducing the entry proportion of inefficient firms due to the selection effect, and enhancing the productivity of incumbent firms under the influence of competition and agglomeration effects. Land lease price is an important mediator variable for place-based policy to promote firms' productivity.</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70064</t>
         </is>
@@ -1107,28 +1139,38 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>The Impact of Autonomous Truck Technology on US Interstate Trade</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Taejun Mo; Sandy Dall'erba; William Ridley; Yilan Xu; Hyungsun Yim</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
           <t>Recent advances in autonomous and semi-autonomous vehicle technologies promise substantial cost savings for goods shipped by truck. In this study, we quantify the impacts of these transport cost reductions on the US interstate trade using a structural gravity model of domestic trade. Based on projected cost savings from the widespread adoption of self-driving technologies, we estimate significant increases in total interstate trade value. State-level impacts vary from 40.3% of GDP in Mississippi to 5.9% in Florida, while the largest impacts in dollar value are observed in Texas and New York. The sectoral analysis highlights motorized vehicles, mixed freight, and electronics as the industries experiencing the largest trade value growth. Additionally, goods with low value-to-weight ratios—where shipping costs represent a large share of the delivered value—are expected to benefit most in relative terms. These findings underscore the transformative potential of autonomous vehicle technologies in reshaping US trade patterns and sectoral dynamics.</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70067</t>
         </is>
@@ -1150,28 +1192,38 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Urban Administrative Restructuring and Gender Gap in the Labor Market: Evidence From China's City-County Merger Reform</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Hao Li; Xiuyan Liu; Jingjing Ye</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
+          <t>Migration &amp; labor; China &amp; urban transformation; Transportation</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
           <t>As a major form of urban administrative restructuring in China, city-county mergers dismantle boundaries between municipal districts and surrounding counties, creating more integrated local labor markets. Using longitudinal data from the China Household Finance Survey and a difference-in-differences framework, we examine how this restructuring affects gender disparities in labor market outcomes. We find that the reform significantly widens the gender wage gap. Mechanism analysis shows that this gap is driven by several channels, including increased labor competition from migrant inflows, the expansion of manufacturing activity, improvements in transportation infrastructure, and rising housing values. The effects are highly heterogeneous: rural and less-educated women, as well as women in more developed counties, experience the largest losses relative to men.</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70068</t>
         </is>
@@ -1193,28 +1245,38 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>House Prices and Bank Lending to SMEs: Evidence From UK Local Authorities</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Jalal Siddiki; Zilong Wang</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
           <t>Rising house prices crowd out SME lending and increase mortgage lending, in a UK panel 2014-2021.</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70069</t>
         </is>
@@ -1236,28 +1298,34 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Local Crime Spillover Onto Public-Private Partnership Financing Commitment</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>King Yoong Lim; Lin Lang; Diego Morris; Waseem A. Toraubally</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>Local crime reduces government reimbursement to PFI partners in England/Wales; moderated by local affluence and urban proximity.</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70070</t>
         </is>
@@ -1279,28 +1347,34 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Voting Red Again: How Social Capital and Local Change Drove the Trump Swing</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Pedro Fierro; Andres Rodriguez-Pose; Francisco Rowe; Ellen Johanna Helsper</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr"/>
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>County-level analysis (2016/2020 elections) shows bonding social capital linked to higher Trump vote margins, bridging capital the opposite.</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70071</t>
         </is>
@@ -1322,28 +1396,38 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Dynamic Probit Models With Network Interdependence and Unobserved Heterogeneity With an Application to Multinational-Firm Participation in China</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Peter H. Egger; Michaela Kesina</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
+          <t>China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
           <t>Proposes MCMC control-function estimators for dynamic panel probit models with network interdependence; applied to Chinese firm data.</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70072</t>
         </is>
@@ -1365,28 +1449,38 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>From Isolation to Integration: The Legacy of Treaty Ports on Inter-City Connectivity</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Shi Chen; Daidai Shen; Huan Yang</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
+          <t>China &amp; urban transformation; Transportation; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
           <t>China's historic treaty ports (1840s-1910s) show persistent effects on modern inter-city connectivity (banking, migration, airlines, HSR).</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70073</t>
         </is>
@@ -1408,28 +1502,38 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Uneven Greening: Dynamics of Urban-Rural Income Gap During the Green Transition</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Xiaoping He; Jiahui Chen; Yuxuan Yu</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; Transportation; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
           <t>Finds a U-shaped relationship between green transition and the urban-rural income gap in Chinese cities 2016-2023.</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70074</t>
         </is>
@@ -1451,28 +1555,38 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>When Integration Backfires: Examining the Effects of Mandatory Inter-Municipal Cooperation on Local Housing Markets</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Alessandro Sovera</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
           <t>Italy's 2010 mandatory cooperation reform lowered residential (4-6%) and commercial (11-18%) property values via service deterioration.</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70076</t>
         </is>
@@ -1494,28 +1608,34 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>From Fragmentation to Integration? How Globalization Reshaped the Global Urban Hierarchy, 1950-2030</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>Alessandro Muolo; Ioannis Konaxis; Luca Salvati</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>Uses UN World Urbanization Prospects and MGWR to show increasing global adherence to Zipf's law / urban hierarchy integration 1950-2030.</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70081</t>
         </is>
@@ -1537,28 +1657,34 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>The Great British Productivity Puzzle and Regional Industries: A Dynamic Multilevel Spatial Frontier Analysis</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Anthony J. Glass; Karligash Kenjegalieva</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>Introduces a multilevel spatial stochastic frontier model applied to GB NUTS3 industries to explain the UK post-2008 productivity slowdown.</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70077</t>
         </is>
@@ -1580,28 +1706,38 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>The Unintended Consequence of Infrastructure on Firms: Evidence From the Construction of Subway in China</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Qingfeng Cai; Jinyuan Xie; Guangjun Shen; Jingxian Zou</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
+          <t>Transportation; China &amp; urban transformation; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
           <t>Subway construction raises effective tax rates on local firms via fiscal pressure/implicit debt; incumbent firms see rising profitability/investment/employment but also more exits.</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70079</t>
         </is>
@@ -1623,28 +1759,38 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>The Road Toll of Heat: The Impact of High Temperatures on Traffic Accidents</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Yilan Luo; Yajie Sun</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
+          <t>Transportation; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
           <t>Examines high ambient temperatures and road accidents in Taipei City using Poisson PML regression; finds days &gt;27C significantly increase accidents, larger for two-wheel vehicles, driven by psychological risk-taking channels.</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/jors.70078</t>
         </is>
@@ -1666,28 +1812,34 @@
           <t>2026-04 (iss.2)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>How contagious are health shocks on political outcomes? Evidence from the 1918 Spanish flu in Germany</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Mona Foertsch; Felix Roesel</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100139</t>
         </is>
@@ -1709,28 +1861,38 @@
           <t>2026-04 (iss.2)</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Short and long-run effects of inter-governmental redistribution of property tax on housing supply</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Xieer Dai; Daniel Felsenstein</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr"/>
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100138</t>
         </is>
@@ -1752,28 +1914,38 @@
           <t>2026-06 (iss.3)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>The geography of the green transition: Performance, vulnerabilities and opportunities</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Sebastian Ritter; Vicente Royuela</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Transportation</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100150</t>
         </is>
@@ -1795,28 +1967,38 @@
           <t>2026-06 (iss.3)</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>The 'borrowed-size' effect in carbon reduction: Does the spatial structure of urban agglomeration matter?</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Honghong Wei; Ying Wang</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100146</t>
         </is>
@@ -1838,28 +2020,38 @@
           <t>2026-06 (iss.3)</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Agglomeration and sector composition across cities: Evidence from China</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Yuting Bai</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100145</t>
         </is>
@@ -1881,28 +2073,38 @@
           <t>2026-06 (iss.3)</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Agglomeration of knowledge intensive activities as driver of high skilled inter-regional migration: A gravity model with Spanish labor mobility data</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Jose Blanco-Alvarez; Manuel Gonzalez-Lopez</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100149</t>
         </is>
@@ -1924,28 +2126,34 @@
           <t>2026-06 (iss.3)</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Regressive deconcentration and knowledge-intensive business services: New evidence for the Brazilian regional development agenda</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Adilson Giovanini; Wallace Marcelino Pereira</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr"/>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100148</t>
         </is>
@@ -1967,28 +2175,38 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Climate change, spatial interactions, and the dynamics of regional economic convergence</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Juan M. Aristizabal; Carlos A. Astudillo; Gustavo A. Garcia; Gilberto Osorio-Gomez</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr"/>
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100158</t>
         </is>
@@ -2010,28 +2228,38 @@
           <t>2026-08 (iss.4)</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Spatial inequality in elderly longevity: Evidence from Taiwan's regional healthcare system</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Congmin Peng; Jiun-Nan Pan</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr"/>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100155</t>
         </is>
@@ -2053,28 +2281,34 @@
           <t>2026-08 (iss.4)</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>The heterogeneous effects of crises on productivity. Regional evidence from the Great Recession</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Gianluigi Coppola; Sergio Destefanis; Giulia Nunziante</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr"/>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr"/>
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100151</t>
         </is>
@@ -2096,28 +2330,38 @@
           <t>2026-08 (iss.4)</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Spatial distribution of income in cities. Polycentric structure of employment, amenities and spatial effects</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Rafa Madariaga; Raymond Lagonigro; Ferran Oro-Aran; Joan Carles Martori</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr"/>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="K27" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100156</t>
         </is>
@@ -2139,28 +2383,38 @@
           <t>2026-08 (iss.4)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Mining, labour markets and uneven regional economic development</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>David Fleming-Munoz; Lavinia Poruschi; Taryn M. Kong; Amanda Davies; Allison Britt; Linda Robson; Simone Felton</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.pirs.2026.100154</t>
         </is>
@@ -2182,32 +2436,42 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Convergence or divergence? Spatiotemporal coupling coordination analysis between digital intelligence and greening in Chinese agriculture</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Chulin Pan; Shiyi Shen; Hongpeng Guo; Yufeng Jiang; Shuang Xu</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; Climate &amp; green transition; AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Agricultural digital intelligence; Agricultural greening; Coupling coordination; Spatial differences; Distributional dynamic evolution; Exploratory space-time data analysis</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>Provincial panel data (China, 2014-2023) on coupling coordination between agricultural digital intelligence and greening.</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01508-4</t>
         </is>
@@ -2229,28 +2493,38 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Unintended consequences of place-based and person-based policies: a mechanism-based framework</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Samuel Redinger; Amanda Ross</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
           <t>Conceptual framework organizing unintended consequences of regional policy around five mechanisms (displacement, agglomeration, market access, behavioral response, intergenerational spillovers).</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01504-8</t>
         </is>
@@ -2272,28 +2546,38 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Impacts of community reinvestment act designation on employment in the presence of spatial spillovers</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Anil Rupasingha; Stephan J. Goetz</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
+          <t>Migration &amp; labor; Place-based policy &amp; inequality; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr"/>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
           <t>Synthetic DID analysis (2012-2019) shows CRA designation raises the employment-to-population ratio with a metro&gt;micro&gt;rural gradient and spatial spillovers.</t>
         </is>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01485-8</t>
         </is>
@@ -2315,28 +2599,34 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>FURS: Fuzzy urban and regional sets</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Eric J. Heikkila; Seula Lee</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr"/>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>Introduces a fuzzy set theory framework for urban/regional analysis using Dallas-Fort Worth census tract data.</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01507-5</t>
         </is>
@@ -2358,28 +2648,38 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>The distributional effects of EU structural funds in Italy: a location-scale approach</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>Francesco Frangiamore; Debora Insolda; Marco Maria Matarrese; Khatereh Yarveisi</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr"/>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
           <t>A location-scale model shows EAFRD/ERDF funds narrow the dispersion of regional GDP per capita in Italy.</t>
         </is>
       </c>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="K33" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01506-6</t>
         </is>
@@ -2401,28 +2701,38 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Marine tourism adaptive capacity factors in willingness to participate in climate change learning</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>I Wayan Koko Suryawan; Imelda Masni Juniaty Sianipar; Chun-Hung Lee; Ari Rahman; Evi Siti Sofiyah</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
           <t>Household survey (n=520) in Komodo Subdistrict, Indonesia on adaptive capacity and willingness to engage in climate learning programs.</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01505-7</t>
         </is>
@@ -2444,28 +2754,38 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Can centralized environmental management reduce air pollution in administrative border areas? Evidence from vertical management reform of environmental protection institutions in China</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>Xin Zhang; Cong Zhang; Qiying Ran; Yudong Li</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr"/>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
           <t>DID analysis of 221 Chinese border prefecture cities, 2011-2022; VREP reform reduces border-area air pollution via enhanced regulatory capacity.</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="K35" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01510-w</t>
         </is>
@@ -2487,28 +2807,38 @@
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Are agglomeration rents taxable in developing economies? Evidence from Colombia</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Jesus Lopez-Rodriguez; Jubelly Marcela Ortiz-Munoz; Brais Pocina-Sanchez</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
           <t>Cross-sectional analysis of 1083 Colombian municipalities finds a positive association between market potential and local business tax rates.</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01509-3</t>
         </is>
@@ -2530,28 +2860,38 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Breaking through the evolutionary path: market potential and regional industrial dynamics</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>Peifeng Zhang; Canfei He</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
+          <t>China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
           <t>Market potential (demand-side) drives entry of path-breaking new industries in Chinese cities via income/demand-structure and productivity/innovation channels.</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="K37" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01512-8</t>
         </is>
@@ -2573,28 +2913,38 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Evolution of rural population-settlement coupling relationships and targeted governance pathways under a shrinkage context: a case study of Gansu Province, China</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Libang Ma; Qing Zhu; Shoucun Zhao; Litang Yao; Cui Cao</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
+          <t>China &amp; urban transformation; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
           <t>Studies rural population shrinkage vs. settlement expansion coupling in Gansu using the Tapio index; identifies four governance-type categories.</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01515-5</t>
         </is>
@@ -2616,28 +2966,38 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>The local effects of income support to families with children in Italy and Greece</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Francesco Figari; Marcello Matranga; Manos Matsaganis</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr"/>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality; Transportation; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
           <t>The paper showcases a new spatial microsimulation model, used here to assess the anti-poverty effects of child benefits in Italy (Assegno Unico Universale) and Greece at local level. We assess such effects by comparing the actual income distribution, observed under the current policy regime of income support to families with children, with the counterfactual one, that would have prevailed had the previous system been allowed to continue. We compare the values of the total child poverty gap (an indicator that combines the poverty rate and the poverty gap) under the new and the old policy regimes in 107 provinces in Italy and 74 local administrative units in Greece, equivalent to the NUTS-3 level. Our results reveal considerable heterogeneity at local level and identify areas in which the total child poverty gap appears to have increased, as losers from the reform outnumbered winners at the bottom of the income distribution. The paper informs the debate on the optimal design of income support to families with children and illustrates the potential of spatial microsimulation as a tool for the analysis of the local effects of public policies.</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="K39" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01514-6</t>
         </is>
@@ -2659,28 +3019,38 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Environmental crime and regional development: evidence from Italian regions</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Gaetano Perone</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; Migration &amp; labor; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
           <t>This paper investigates how environmental crime shapes regional development trajectories in Italy. Using regional panel data from 2012 to 2022, the study applies a combination of panel data techniques and a dynamic panel vector autoregression (PVAR) framework to ensure the robustness of the results. The findings show that environmental crimes are associated with lower GDP and formal employment, while being linked to higher irregular employment. The analysis identifies a unidirectional predictive relationship running from environmental crime to GDP and from irregular employment to environmental crime, and a bidirectional relationship between environmental crime and formal employment. These results highlight the damaging role of environmental crime in undermining economic development, reinforcing territorial inequalities, and weakening governance capacities, consistent with its interpretation as locally embedded informal institutions and manifestations of the 'dark side' of social capital. By adopting a place-based development perspective, the paper contributes to broader debates on governance, institutional quality, and uneven territorial development in Europe. It calls for integrated policy strategies that combine enforcement with institutional strengthening to foster fair competition, decent work, and inclusive regional growth.</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="K40" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01511-9</t>
         </is>
@@ -2702,28 +3072,38 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Related diversification strategies and regional development traps in the Brazilian manufacturing industry</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Marcio Julio Pereira Henriques; Igor Santos Tupy; Rafael F. de A. Campos</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr"/>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality; Transportation</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
           <t>This paper examines the potential and limitations of related diversification as a regional industrial development strategy in Brazil, drawing on the framework of evolutionary economic geography. Using the concept of regional development traps, we analyze the manufacturing sector across Brazilian microregions between 2012 and 2022, classifying them according to sectoral complexity and relatedness density. The results reveal a highly unequal productive structure, in which more complex and technologically intensive activities occupy central and strongly connected positions, while most regions remain concentrated in peripheral sectors with low connectivity. Microregions in the Southeast and South exhibit higher productive coherence and adaptive capacity, positioning them within self-reinforcing complexity loops. In contrast, most regions in the North, Northeast, and parts of the Central West remain locked in structural traps characterized by low complexity and weak sectoral relatedness. We also find strong temporal persistence and a prevalence of regressive transitions, indicating limited structural mobility and reinforcing long-standing patterns of uneven industrial development. These findings suggest that related diversification is strongly conditioned by initial regional structures and may intensify disparities if implemented through uniform industrial policies. Effective strategies, therefore, require place-based approaches focused on strengthening productive linkages and expanding local capabilities.</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="K41" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01513-7</t>
         </is>
@@ -2745,28 +3125,38 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>The impact of digital technology on industrial green transition-an empirical study of Chinese cities</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Changxue Wang; Yan Wang; Chenglong Xu</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; China &amp; urban transformation; Transportation</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
           <t>With its distinct advantages of informatization, personalization, and intelligence, digital technology (DT) is becoming integral to industrial green transition (IGT). This paper aims to investigate the complex impact of DT on IGT. To this end, utilizing data across 283 Chinese cities from 2013 to 2022, we employ a two-way fixed-effects model, a mediation model, and a threshold effect model. The results show that (1) DT significantly and positively enhances IGT, as shown by robustness and endogeneity tests; (2) government environmental penalties (GEP) and industrial structure rationalization (ISR) serve as mediation pathways through which DT influences IGT; (3) IGT performance in eastern and central regions, nonresource-based cities, major population-scale cities, and inland cities benefits more from DT than that in other cities; (4) an increase in the DT of neighboring cities not only enhances the IGT of the city itself but also generates spatial spillover effects on neighboring cities; and (5) under a moderate level of government attention (LGA), the positive threshold effect of DT on IGT is most notable. On the basis of these results, this paper proposes targeted policy recommendations, including DT-driven initiatives, enhanced environmental monitoring, industrial structure optimization, regional differentiated development, and an appropriate LGA.</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01516-4</t>
         </is>
@@ -2788,28 +3178,38 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Digital transformation and remote work: gender, family size, and education in shaping work-from-home perceptions during COVID-19</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Sergio Scicchitano; Marco Biagetti; Cosimo Magazzino</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr"/>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
+          <t>AI &amp; digital economy; Migration &amp; labor; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr"/>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
           <t>The COVID-19 pandemic accelerated the adoption of work-from-home (WFH) practices, prompting a structural shift in labor organization and deepening preexisting digital divides. This research examines how gender, family size, and educational attainment shape individual perceptions of remote work, drawing on 2020 data from the Italian National Institute for Public Policy Analysis (INAPP) Survey on Labor Participation and Unemployment. The research uncovers substantial heterogeneity in WFH experiences across social groups, with gender disparities evident in how men and women evaluate flexibility, stress, and work-family balance. Educational background matters primarily through intergenerational pathways—particularly mothers' education—in shaping autonomy and productivity assessments. The study concludes that remote work's digital transformation risks reinforcing existing inequalities without inclusive, gender-sensitive policy interventions.</t>
         </is>
       </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00168-026-01469-8</t>
         </is>
@@ -2831,28 +3231,38 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Transport in low- and middle-income countries</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Adam Storeygard</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
+          <t>Transportation; Place-based policy &amp; inequality; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
           <t>Survey of transportation economics in poor/middle-income countries covering urban informal transit, gender, BRT, congestion policy, colonial legacy, and rural roads. (Via NBER w34354.)</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104231</t>
         </is>
@@ -2874,24 +3284,34 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Measuring the cost of building infrastructure over time: Very hard to do well</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr"/>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr"/>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr"/>
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="K45" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104234</t>
         </is>
@@ -2913,24 +3333,30 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Dormitories or grants? Need-based aid and university students' mobility in Italy</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr"/>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr"/>
-      <c r="H46" s="17" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104232</t>
         </is>
@@ -2952,24 +3378,34 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>Using the past to understand cities: Transportation before the Industrial Revolution in Urban Economics</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr"/>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr"/>
-      <c r="H47" s="16" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr"/>
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="K47" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104233</t>
         </is>
@@ -2991,28 +3427,38 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Private provision of local public goods and housing market responses: Evidence from London</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Stefano Cellini; Francisco Nobre (unconfirmed)</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr"/>
-      <c r="H48" s="17" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104243</t>
         </is>
@@ -3034,28 +3480,38 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>The urban wage premium in historical perspective</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>Kyle Butts; Taylor Jaworski; Carl Kitchens</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr"/>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr"/>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
           <t>Estimates the US urban wage premium 1940-2010 controlling for sorting; the premium was highest mid-20th century (~12%), declining to a few percent by 2010. (Via NBER w31387.)</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="K49" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104245</t>
         </is>
@@ -3077,28 +3533,38 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Sport stadiums &amp; land values</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Alexander Cardazzi; Hiroaki Funahashi (unconfirmed)</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr"/>
-      <c r="H50" s="17" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="K50" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104244</t>
         </is>
@@ -3120,28 +3586,38 @@
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>Urban internal structures and gender commuting gap: Evidence from China</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>Xiaofang Dong; Yalin Wang (unconfirmed)</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr"/>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation; Transportation; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr"/>
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="K51" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104246</t>
         </is>
@@ -3163,24 +3639,34 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Transportation infrastructure and urban and regional development</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr"/>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr"/>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
+      <c r="K52" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104247</t>
         </is>
@@ -3202,24 +3688,34 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>Making room for vacationers? The effect of Airbnb entry on eviction filings in the United States</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr"/>
-      <c r="F53" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr"/>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr"/>
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="K53" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104248</t>
         </is>
@@ -3241,24 +3737,34 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>Transport infrastructure and urban spatial structure</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr"/>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr"/>
-      <c r="H54" s="17" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
+      <c r="K54" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104250</t>
         </is>
@@ -3280,28 +3786,38 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>The long-run effects of Interstate highways on rural America</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Heejin Kim; John Anders; Craig Carpenter; Marcus Bernard; Trey Malone (unconfirmed)</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr"/>
-      <c r="H55" s="16" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>Transportation; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr"/>
+      <c r="J55" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I55" s="15" t="inlineStr">
+      <c r="K55" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104249</t>
         </is>
@@ -3323,28 +3839,38 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>Assessment persistence</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>Daniel McMillen; Ruchi Singh</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr"/>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
           <t>Studies the persistence of unusually low/high property assessment ratios in Cook County, IL, 1976-2020. (From related working paper; may not exactly match final text.)</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="K56" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104251</t>
         </is>
@@ -3366,28 +3892,38 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>Ports, Technology and Inter-City Trade: The Economics and Geopolitics of Evolving Maritime Transport Networks</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>Reka Juhasz; David Krisztian Nagy; Claudia Steinwender; Woan Foong Wong</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr"/>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
+          <t>Transportation; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr"/>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
           <t>Survey of maritime shipping network transformation via containerization, port concentration, Chinese state-owned terminal operators, and welfare/geopolitical implications. (Via NBER w35449.)</t>
         </is>
       </c>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="K57" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104261</t>
         </is>
@@ -3409,28 +3945,38 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Where do place-based policies work? Evidence from Italy's inner areas strategy</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>Michele Mariani</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr"/>
-      <c r="H58" s="17" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
+      <c r="K58" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.regsciurbeco.2026.104252</t>
         </is>
@@ -3452,28 +3998,34 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>A research agenda for economic geography: Reframing 21st century capitalism</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>Jose A. Borello</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr"/>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr"/>
+      <c r="I59" s="14" t="inlineStr"/>
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="K59" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2685439</t>
         </is>
@@ -3495,28 +4047,34 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>Resilience or lock-in? Path dependency and structural change after the 2009 L'Aquila earthquake</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>Paolo Bottero; Marco Modica; Giulia Urso</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr"/>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I60" s="12" t="inlineStr">
+      <c r="K60" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2676262</t>
         </is>
@@ -3538,28 +4096,38 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>Predicting local taxation decision-making: evidence from Italian municipalities</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
+      <c r="F61" s="14" t="inlineStr">
         <is>
           <t>Nicola Caravaggio; Giuliano Resce; Idola Francesca Spano</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr"/>
-      <c r="H61" s="16" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr"/>
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="K61" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2676238</t>
         </is>
@@ -3581,28 +4149,38 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
         <is>
           <t>The geography of artificial intelligence in European regions: innovation, exposure and use</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>Bernardo Buarque; Pablo Casas; Enrique Fernandez-Macias; Ignacio Gonzalez-Vazquez; Ryan Hynes; Dieter F. Kogler; Simone Salotti</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr"/>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr"/>
+      <c r="J62" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I62" s="12" t="inlineStr">
+      <c r="K62" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2681659</t>
         </is>
@@ -3624,28 +4202,34 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
         <is>
           <t>Border permeability and cross-border mobility in Europe, 1960-2020</t>
         </is>
       </c>
-      <c r="E63" s="14" t="inlineStr">
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>Andrzej Jakubowski; Piotr Rosik; Tomasz Komornicki; Marcin Mazur</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr"/>
-      <c r="H63" s="16" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr"/>
+      <c r="I63" s="14" t="inlineStr"/>
+      <c r="J63" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="K63" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2682503</t>
         </is>
@@ -3667,28 +4251,34 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
         <is>
           <t>A media-based indicator for studying functional cross-border regions</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Jennifer Bettis; Francesco Cappellano; Teemu Makkonen; Derek Moscato</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr"/>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr"/>
+      <c r="J64" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="K64" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2682498</t>
         </is>
@@ -3710,28 +4300,38 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>Sub-ecosystem coupling in Sherbrooke's entrepreneurial ecosystem: a network perspective</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>Karim Messeghem; Laurence Cloutier</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr"/>
-      <c r="H65" s="16" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr"/>
+      <c r="J65" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="K65" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2681660</t>
         </is>
@@ -3753,28 +4353,38 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Short-term rentals and transnational gentrification in Mexico City: a mixed-methods approximation</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Tamara Velasquez Leiferman</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr"/>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr"/>
+      <c r="J66" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I66" s="12" t="inlineStr">
+      <c r="K66" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2682501</t>
         </is>
@@ -3796,28 +4406,34 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>Sustainable regional value capture by social businesses: a dynamic capability perspective</t>
         </is>
       </c>
-      <c r="E67" s="14" t="inlineStr">
+      <c r="F67" s="14" t="inlineStr">
         <is>
           <t>Chrysostomos Apostolidis; Bidit L. Dey; Mujahid Mohiuddin Babu; Lefteris Kretsos; David M. Brown; Pallavi Singh; Sadaat Ali Yawaar</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr"/>
-      <c r="H67" s="16" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr"/>
+      <c r="I67" s="14" t="inlineStr"/>
+      <c r="J67" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="K67" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2685047</t>
         </is>
@@ -3839,28 +4455,38 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>The geography of the disability employment gap: a new decomposition of spatial variation</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Mark Bryan; Andrew Bryce; Jennifer Roberts; Cristina Sechel</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr"/>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I68" s="12" t="inlineStr">
+      <c r="K68" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2681662</t>
         </is>
@@ -3882,28 +4508,38 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
         <is>
           <t>Orchestrating place-based micro-missions: the grand challenge of decarbonisation at Shoreham Port</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>Kyle S. Herman; Andrew Davies; Stephan Manning</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr"/>
-      <c r="H69" s="16" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Place-based policy &amp; inequality; Transportation</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr"/>
+      <c r="J69" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I69" s="15" t="inlineStr">
+      <c r="K69" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2688957</t>
         </is>
@@ -3925,28 +4561,38 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>Transformative innovation policy and collaborative governance in regions and cities</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>David A. Wolfe</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr"/>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I70" s="12" t="inlineStr">
+      <c r="K70" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2688966</t>
         </is>
@@ -3968,28 +4614,38 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
         <is>
           <t>Towards talent dividend: how urban amenities shape the geography of skilled labour's economic contribution in China</t>
         </is>
       </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="F71" s="14" t="inlineStr">
         <is>
           <t>Yingju Wu; Hengyu Gu</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr"/>
-      <c r="H71" s="16" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr"/>
+      <c r="J71" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I71" s="15" t="inlineStr">
+      <c r="K71" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2688962</t>
         </is>
@@ -4011,28 +4667,38 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>Creativity and AI skill demand in the post-ChatGPT labour market: evidence from UK job vacancies</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Zihan Wang; Aniket Baksy; Hasan Bakhshi; Josh Siepel</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr"/>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor; AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
+      <c r="K72" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2688960</t>
         </is>
@@ -4054,28 +4720,34 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
         <is>
           <t>Community-based social capital, neighbourhood characteristics and SME resilience: a configurational analysis</t>
         </is>
       </c>
-      <c r="E73" s="14" t="inlineStr">
+      <c r="F73" s="14" t="inlineStr">
         <is>
           <t>Arash Sadeghi; Taimaz Larimian; John Harrison</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G73" s="14" t="inlineStr"/>
-      <c r="H73" s="16" t="inlineStr">
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr"/>
+      <c r="I73" s="14" t="inlineStr"/>
+      <c r="J73" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I73" s="15" t="inlineStr">
+      <c r="K73" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00343404.2026.2679523</t>
         </is>
@@ -4097,28 +4769,34 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>Functional classifications of small towns. The comparison of three methodological attempts</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>Marcin Mazur; Jerzy Banski; Damian Mazurek</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="inlineStr"/>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr"/>
+      <c r="J74" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
+      <c r="K74" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2649616</t>
         </is>
@@ -4140,28 +4818,38 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
         <is>
           <t>Housing market impacts of air pollution. Do objective or subjective measures of air quality matter?</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="F75" s="14" t="inlineStr">
         <is>
           <t>Juan M. Aristizabal; Gustavo A. Garcia</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G75" s="14" t="inlineStr"/>
-      <c r="H75" s="16" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr"/>
+      <c r="J75" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I75" s="15" t="inlineStr">
+      <c r="K75" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2655698</t>
         </is>
@@ -4183,28 +4871,38 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>Digital transformation in Greater Manchester: determinants of technology adoption and implications for firms' performance</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Silvia Massini; Mabel Sanchez-Barrioluengo; Xiaoxiao Yu; Reza Salehnejad</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr"/>
-      <c r="H76" s="17" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr"/>
+      <c r="J76" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
+      <c r="K76" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2662375</t>
         </is>
@@ -4226,28 +4924,34 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
         <is>
           <t>Trade integration in Europe in the presence of unobservable barriers</t>
         </is>
       </c>
-      <c r="E77" s="14" t="inlineStr">
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>Santiago Perez-Balsalobre; Carlos Llano; Nuria Gallego</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="inlineStr"/>
-      <c r="H77" s="16" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr"/>
+      <c r="I77" s="14" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="K77" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2662378</t>
         </is>
@@ -4269,28 +4973,34 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>Spatial variation in mobility across England: evidence from 21 million geo-coded credit-card flows</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Nicholas Patrick Sweeney</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="inlineStr"/>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr"/>
+      <c r="J78" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I78" s="12" t="inlineStr">
+      <c r="K78" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2650132</t>
         </is>
@@ -4312,28 +5022,38 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
         <is>
           <t>Displacement and disconnection: the impact of violence on migration networks and highway traffic in Mexico</t>
         </is>
       </c>
-      <c r="E79" s="14" t="inlineStr">
+      <c r="F79" s="14" t="inlineStr">
         <is>
           <t>Michele Coscia; Roxana Gutierrez-Romero</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr"/>
-      <c r="H79" s="16" t="inlineStr">
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>Transportation; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr"/>
+      <c r="J79" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="K79" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2662381</t>
         </is>
@@ -4355,28 +5075,38 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>A spatial analysis of financial development and green economic efficiency</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Liting Fang; Zhaohua Li</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr"/>
-      <c r="H80" s="17" t="inlineStr">
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr"/>
+      <c r="J80" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
+      <c r="K80" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2660736</t>
         </is>
@@ -4398,28 +5128,38 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
         <is>
           <t>Gender composition in African parliaments and foreign aid patterns</t>
         </is>
       </c>
-      <c r="E81" s="14" t="inlineStr">
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t>Valentina Chiariello</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="inlineStr"/>
-      <c r="H81" s="16" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="inlineStr"/>
+      <c r="J81" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I81" s="15" t="inlineStr">
+      <c r="K81" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2668372</t>
         </is>
@@ -4441,28 +5181,34 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>An alternative to vulnerability index. A new way to measure the vulnerability of NUTS 3</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Giani-Ionel Gradinaru; Alin-Cristian Maricut; Diana Petre; Gianina Petrascu; Costin Taulescu</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr"/>
-      <c r="H82" s="17" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr"/>
+      <c r="J82" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I82" s="12" t="inlineStr">
+      <c r="K82" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2668370</t>
         </is>
@@ -4484,28 +5230,38 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
         <is>
           <t>Urbanisation and fertility rate in China: nonlinear effects and policy implications</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>Hui Zhou; Yang Liu; Weiwen Qian</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr"/>
-      <c r="H83" s="16" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr"/>
+      <c r="J83" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I83" s="15" t="inlineStr">
+      <c r="K83" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2668382</t>
         </is>
@@ -4527,28 +5283,34 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>Spatial spillover effects of sustainable development in the EU</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>Cagla Bucak; Abdurrahman Nazif Catik</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G84" s="11" t="inlineStr"/>
-      <c r="H84" s="17" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="11" t="inlineStr"/>
+      <c r="J84" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
+      <c r="K84" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2682825</t>
         </is>
@@ -4570,28 +5332,38 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>The geography of AI adoption: AI diffusion in Dutch municipalities 2012-2020</t>
         </is>
       </c>
-      <c r="E85" s="14" t="inlineStr">
+      <c r="F85" s="14" t="inlineStr">
         <is>
           <t>Harm-Jan Rouwendal; Sierdjan Koster; Teresa Farinha</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr"/>
-      <c r="H85" s="16" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr"/>
+      <c r="J85" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I85" s="15" t="inlineStr">
+      <c r="K85" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2685647</t>
         </is>
@@ -4613,28 +5385,34 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>Disentangling relatedness density: the complementary impact of non-specialised related technologies</t>
         </is>
       </c>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>Gloria Cicerone; Philip McCann; Viktor A. Venhorst</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="inlineStr"/>
-      <c r="H86" s="17" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr"/>
+      <c r="J86" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I86" s="12" t="inlineStr">
+      <c r="K86" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2685648</t>
         </is>
@@ -4656,28 +5434,38 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>A dynamic data envelopment analysis of regional innovation efficiency in China</t>
         </is>
       </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>Yuanyu Lou; Mingxia Xiang; Guoliang Yang; Zhongcheng Guan; Tong Chen</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr"/>
-      <c r="H87" s="16" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr"/>
+      <c r="J87" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr">
+      <c r="K87" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2671849</t>
         </is>
@@ -4699,28 +5487,34 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>A spatial Herfindahl-Hirschman Index for inter- and intra-type competition</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>Norbert Jaworski; Tomasz Kopczewski</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="inlineStr"/>
-      <c r="H88" s="17" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr"/>
+      <c r="J88" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I88" s="12" t="inlineStr">
+      <c r="K88" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17421772.2026.2692317</t>
         </is>
@@ -4742,28 +5536,38 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
         <is>
           <t>Scales of Inequality: Applying a Two-Stage Theil Decomposition Approach to Examine the Changing Spatial Dimensions of Regional Inequality in the US, 1970-2020</t>
         </is>
       </c>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="F89" s="14" t="inlineStr">
         <is>
           <t>Annie Seong Lee; Sebastien Breau</t>
         </is>
       </c>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G89" s="14" t="inlineStr"/>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
+          <t>Place-based policy &amp; inequality; Transportation; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="inlineStr"/>
+      <c r="J89" s="14" t="inlineStr">
+        <is>
           <t>Applies a two-stage nested Theil decomposition to examine the role of geographical scale in describing inter-regional income inequalities over 1970-2020, using quasi-states, commuting zones, and counties. Inter-regional inequalities increase over time across all three scales, but the speed varies; by 2020, inequalities within commuting zones explain the largest portion, suggesting smaller-scale divergence within local labor market areas is a key driver of the recent rise in inter-regional inequality.</t>
         </is>
       </c>
-      <c r="I89" s="15" t="inlineStr">
+      <c r="K89" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/01600176261440842</t>
         </is>
@@ -4785,28 +5589,38 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>Smart Specialisation in Swedish Regions as a Governance Tool for Societal Transformation</t>
         </is>
       </c>
-      <c r="E90" s="11" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>Ida Grundel; Brita Hermelin</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="inlineStr"/>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
+          <t>AI &amp; digital economy; Climate &amp; green transition; Transportation</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr"/>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
           <t>Investigates how smart specialisation strategies (S3) in Swedish regions are evolving to align with the European Green Deal (EGD). Drawing on content analysis of 14 S3 strategies from seven regions across two EU programme periods (2014-2020 and 2021-2027), it explores integration of EGD focus areas and cross-sectoral transformative goals. While energy, industry, and food systems are commonly addressed, integration varies; traditional innovation approaches remain dominant, with emerging mission-oriented ambitions but limited inclusion of broader societal actors.</t>
         </is>
       </c>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="K90" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/01600176261445985</t>
         </is>
@@ -4828,28 +5642,38 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
         <is>
           <t>Urban Collaborative Innovation Relationship in China: Inter-Subject Collaboration and Inter-City Correlation</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr">
+      <c r="F91" s="14" t="inlineStr">
         <is>
           <t>Tao Zhuang; Linlin Liu; Shuliang Zhao</t>
         </is>
       </c>
-      <c r="F91" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr"/>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
+          <t>China &amp; urban transformation; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="inlineStr"/>
+      <c r="J91" s="14" t="inlineStr">
+        <is>
           <t>Based on triple helix theory and innovation network theory, this study constructs a theoretical framework of the urban collaborative innovation system. Using invention patent data of 30 innovative cities from 2014 to 2023, it examines characteristics, evolution, and synergetic degree of the urban innovation system in China. Inter-city cooperation evolved from a 'dual-core driven' to a 'multi-center driven' structure; university-industry bilateral relationships within cities are closest; the Yangtze River Delta and Guangdong-Hong Kong-Macao Greater Bay Area show the strongest inter-city correlation.</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
+      <c r="K91" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/01600176261457906</t>
         </is>
@@ -4871,28 +5695,38 @@
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>Influencing Factors of Digital Talent Mobility: Interactions and Spatio-Temporal Heterogeneity</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Yuanfang Chen; Kok Haur Ng</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr"/>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
+          <t>Migration &amp; labor; AI &amp; digital economy; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
           <t>Digital talent mobility is crucial for enhancing regional competitiveness, yet its influencing factors exhibit notable spatio-temporal heterogeneity. This study examines how interacting macro-, meso-, and micro-level factors shape digital talent mobility across urban agglomerations in China. GeoDetector identifies key interaction effects, incorporated into a Geographically and Temporally Neural Network Weighted Regression model. Effects of macroeconomic and industrial conditions are highly uneven across space and time, further shaped by healthcare provision and air quality. Findings support more differentiated regional talent policies.</t>
         </is>
       </c>
-      <c r="I92" s="12" t="inlineStr">
+      <c r="K92" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/01600176261457907</t>
         </is>
@@ -4914,28 +5748,38 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
         <is>
           <t>When Knowledge Increases Fear: The Moderating Role of Health Status on Disaster Risk Perception</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="F93" s="14" t="inlineStr">
         <is>
           <t>Soyoon Kim; Brian H. S. Kim</t>
         </is>
       </c>
-      <c r="F93" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr"/>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr"/>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
           <t>Ensuring the social acceptance of disaster management policies and promoting the well-being of residents in safe environments requires consideration not only of objective risk levels but also of subjective risk perception. This study distinguishes between natural and man-made disasters to analyze factors influencing risk perception. Using pooled cross-sectional data from four waves of Statistics Korea's Social Survey (2018-2024), a binary logistic model shows coping knowledge reduces fear associated with risk perception, but its effect varies by health status. Regional emergency response accessibility mitigates perceived risk of natural disasters, highlighting the importance of accessibility to emergency services in strengthening disaster response capacity.</t>
         </is>
       </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="K93" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/01600176261463758</t>
         </is>
@@ -4957,28 +5801,38 @@
           <t>2026-08 (iss)</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>Mapping the expansion of artisanal and large-scale mining in Birim North District, Ghana using land use land cover change and digitized mine sites</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>Aaron Tettey Tetteh; Lily Lisa Yevugah; Abdul-Wadood Moomen</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr"/>
-      <c r="H94" s="17" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr"/>
+      <c r="J94" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I94" s="12" t="inlineStr">
+      <c r="K94" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100325</t>
         </is>
@@ -5000,28 +5854,38 @@
           <t>2026-08 (iss)</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>The potentials of 'new data' in border studies: A scoping review</t>
         </is>
       </c>
-      <c r="E95" s="14" t="inlineStr">
+      <c r="F95" s="14" t="inlineStr">
         <is>
           <t>Stefan Hippe; Vit Paszto; Jaroslav Burian; Tobias Chilla; Karel Macku; Vit Vozenilek</t>
         </is>
       </c>
-      <c r="F95" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr"/>
-      <c r="H95" s="16" t="inlineStr">
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I95" s="14" t="inlineStr"/>
+      <c r="J95" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I95" s="15" t="inlineStr">
+      <c r="K95" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100324</t>
         </is>
@@ -5043,28 +5907,38 @@
           <t>2026-08 (iss)</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
         <is>
           <t>Digitalization and remote work in peripheral labour markets in the Nordic region</t>
         </is>
       </c>
-      <c r="E96" s="11" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Gretar Thor Eythorsson; Hjalti Johannesson</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G96" s="11" t="inlineStr"/>
-      <c r="H96" s="17" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy; Place-based policy &amp; inequality; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr"/>
+      <c r="J96" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I96" s="12" t="inlineStr">
+      <c r="K96" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100321</t>
         </is>
@@ -5086,28 +5960,38 @@
           <t>2026-08 (iss)</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>FDI-led reindustrialisation and regional catching-up: Evidence from Hungary</t>
         </is>
       </c>
-      <c r="E97" s="14" t="inlineStr">
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>Zsofia Vas; Imre Lengyel</t>
         </is>
       </c>
-      <c r="F97" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G97" s="14" t="inlineStr"/>
-      <c r="H97" s="16" t="inlineStr">
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I97" s="14" t="inlineStr"/>
+      <c r="J97" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I97" s="15" t="inlineStr">
+      <c r="K97" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100320</t>
         </is>
@@ -5129,28 +6013,38 @@
           <t>2026-08 (iss)</t>
         </is>
       </c>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
         <is>
           <t>Does regional context affect populist voting? A comparative multilevel analysis from Czechia and eastern Germany</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>Martin Refisch; Josef Bernard; Tomas Kostelecky; Andreas Klarner</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr"/>
-      <c r="H98" s="17" t="inlineStr">
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr"/>
+      <c r="J98" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I98" s="12" t="inlineStr">
+      <c r="K98" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100322</t>
         </is>
@@ -5172,28 +6066,38 @@
           <t>2026-09 (iss)</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
         <is>
           <t>Valuing latent attributes of a recreation and wildlife habitat management area</t>
         </is>
       </c>
-      <c r="E99" s="14" t="inlineStr">
+      <c r="F99" s="14" t="inlineStr">
         <is>
           <t>Irene Zapata-Moran; David Aadland; Christelle Khalaf; Brian Harnisch</t>
         </is>
       </c>
-      <c r="F99" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G99" s="14" t="inlineStr"/>
-      <c r="H99" s="16" t="inlineStr">
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr"/>
+      <c r="J99" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I99" s="15" t="inlineStr">
+      <c r="K99" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100329</t>
         </is>
@@ -5215,28 +6119,38 @@
           <t>2026-09 (iss)</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
         <is>
           <t>Perceived fairness in access to higher education in wartime Ukraine: Social inequalities and trust in admission testing</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr">
+      <c r="F100" s="11" t="inlineStr">
         <is>
           <t>Halyna Mishchuk; Vita Krol; Yuriy Bilan</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr"/>
-      <c r="H100" s="17" t="inlineStr">
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr"/>
+      <c r="J100" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I100" s="12" t="inlineStr">
+      <c r="K100" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100327</t>
         </is>
@@ -5258,28 +6172,38 @@
           <t>2026-09 (iss)</t>
         </is>
       </c>
-      <c r="D101" s="14" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
         <is>
           <t>Transforming hot-spring cities into innovation hubs: A comparative cluster-based analysis of Beppu, Bath, and Vichy</t>
         </is>
       </c>
-      <c r="E101" s="14" t="inlineStr">
+      <c r="F101" s="14" t="inlineStr">
         <is>
           <t>Takayuki Kubo; Akira Yamasaki</t>
         </is>
       </c>
-      <c r="F101" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G101" s="14" t="inlineStr"/>
-      <c r="H101" s="16" t="inlineStr">
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="inlineStr"/>
+      <c r="J101" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I101" s="15" t="inlineStr">
+      <c r="K101" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100333</t>
         </is>
@@ -5301,28 +6225,38 @@
           <t>2026-09 (iss)</t>
         </is>
       </c>
-      <c r="D102" s="11" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>Decentralized cooperation and regional development planning in Morocco: Institutional misalignments and their implications for regional policy and territorial cohesion</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>Jamaa Lamkies; Mohammed Kehel</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G102" s="11" t="inlineStr"/>
-      <c r="H102" s="17" t="inlineStr">
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr"/>
+      <c r="J102" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I102" s="12" t="inlineStr">
+      <c r="K102" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100326</t>
         </is>
@@ -5344,28 +6278,38 @@
           <t>2026-09 (iss)</t>
         </is>
       </c>
-      <c r="D103" s="14" t="inlineStr">
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
         <is>
           <t>Counterurban migration and regional structural change</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr">
+      <c r="F103" s="14" t="inlineStr">
         <is>
           <t>Sarper Neyse; Rikard H. Eriksson</t>
         </is>
       </c>
-      <c r="F103" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G103" s="14" t="inlineStr"/>
-      <c r="H103" s="16" t="inlineStr">
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="inlineStr"/>
+      <c r="J103" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I103" s="15" t="inlineStr">
+      <c r="K103" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100332</t>
         </is>
@@ -5387,28 +6331,38 @@
           <t>2026-10 (iss)</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
         <is>
           <t>The making of regional inequality: Market stages in an Integrated or Fragmented world</t>
         </is>
       </c>
-      <c r="E104" s="11" t="inlineStr">
+      <c r="F104" s="11" t="inlineStr">
         <is>
           <t>Andrea Caragliu; Roberto Dellisanti</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr"/>
-      <c r="H104" s="17" t="inlineStr">
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr"/>
+      <c r="J104" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I104" s="12" t="inlineStr">
+      <c r="K104" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.rspp.2026.100328</t>
         </is>
@@ -5430,32 +6384,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D105" s="14" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
         <is>
           <t>Identifying the general equilibrium effects of narcotics enforcement</t>
         </is>
       </c>
-      <c r="E105" s="14" t="inlineStr">
+      <c r="F105" s="14" t="inlineStr">
         <is>
           <t>Zachary Porreca</t>
         </is>
       </c>
-      <c r="F105" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G105" s="14" t="inlineStr">
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
         <is>
           <t>Drug markets; Supply-side enforcement; Cell phone locations; Kensington</t>
         </is>
       </c>
-      <c r="H105" s="14" t="inlineStr">
+      <c r="J105" s="14" t="inlineStr">
         <is>
           <t>Examines demand-side consequences of Philadelphia's 2018 Kensington narcotics-enforcement initiative using SafeGraph cell-phone location data; finds reduced traffic to the target area plus regional spillover reductions in drug-market traffic and overdose deaths, contrary to typical substitution effects.</t>
         </is>
       </c>
-      <c r="I105" s="15" t="inlineStr">
+      <c r="K105" s="15" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119025000944</t>
         </is>
@@ -5477,32 +6441,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
         <is>
           <t>JUE Insight: Floods &amp; urban density</t>
         </is>
       </c>
-      <c r="E106" s="11" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
         <is>
           <t>Pierre Magontier; Rodrigo Martinez-Mazza</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Rural, food &amp; land; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>Floods; Land use; Urban density; Adaptation</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr">
         <is>
           <t>Using Spanish building data (1996-2021), finds floods promote taller, more compact urban development and higher property values, redirecting land use away from agriculture/industry; adaptive response may offset flood damage.</t>
         </is>
       </c>
-      <c r="I106" s="12" t="inlineStr">
+      <c r="K106" s="12" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119026000021</t>
         </is>
@@ -5524,32 +6498,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D107" s="14" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
         <is>
           <t>Working from home increases work-home distances</t>
         </is>
       </c>
-      <c r="E107" s="14" t="inlineStr">
+      <c r="F107" s="14" t="inlineStr">
         <is>
           <t>Sena Coskun; Wolfgang Dauth; Hermann Gartner; Michael Stops; Enzo Weber</t>
         </is>
       </c>
-      <c r="F107" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G107" s="14" t="inlineStr">
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor; Transportation</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
         <is>
           <t>Working from home; Commuting; Urban labor markets</t>
         </is>
       </c>
-      <c r="H107" s="14" t="inlineStr">
+      <c r="J107" s="14" t="inlineStr">
         <is>
           <t>German employment data show commuting distances rose more for WFH-capable occupations since 2021, especially for new hires and big-city jobs; no significant gender difference found.</t>
         </is>
       </c>
-      <c r="I107" s="15" t="inlineStr">
+      <c r="K107" s="15" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119026000033</t>
         </is>
@@ -5571,32 +6555,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
         <is>
           <t>Does political partisanship affect housing supply? Evidence from US cities</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
         <is>
           <t>Fernando Ferreira; Joseph Gyourko</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
         <is>
           <t>Housing supply; Political partisanship; Local politics</t>
         </is>
       </c>
-      <c r="H108" s="11" t="inlineStr">
+      <c r="J108" s="11" t="inlineStr">
         <is>
           <t>Regression-discontinuity design on close mayoral races (1980-) finds partisanship has no statistically or economically significant effect on housing permit supply.</t>
         </is>
       </c>
-      <c r="I108" s="12" t="inlineStr">
+      <c r="K108" s="12" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119026000136</t>
         </is>
@@ -5618,32 +6612,38 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
         <is>
           <t>Sticky places: The effect of college on where you live</t>
         </is>
       </c>
-      <c r="E109" s="14" t="inlineStr">
+      <c r="F109" s="14" t="inlineStr">
         <is>
           <t>Andreas Fidjeland; Tora Knutsen; Magnus Stubhaug</t>
         </is>
       </c>
-      <c r="F109" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G109" s="14" t="inlineStr">
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H109" s="14" t="inlineStr"/>
+      <c r="I109" s="14" t="inlineStr">
         <is>
           <t>College choice; Effects of college; Place of residence</t>
         </is>
       </c>
-      <c r="H109" s="14" t="inlineStr">
+      <c r="J109" s="14" t="inlineStr">
         <is>
           <t>Uses Norway's centralized admissions system as a natural experiment; admission to a preferred study location raises the probability of later residing there by 15-20 pp.</t>
         </is>
       </c>
-      <c r="I109" s="15" t="inlineStr">
+      <c r="K109" s="15" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119026000148</t>
         </is>
@@ -5665,32 +6665,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>The redistribution of housing wealth caused by rent control</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Kenneth R. Ahern; Marco Giacoletti</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>Rent control; Real estate valuation; Wealth transfers; Externalities</t>
         </is>
       </c>
-      <c r="H110" s="11" t="inlineStr">
+      <c r="J110" s="11" t="inlineStr">
         <is>
           <t>St. Paul, MN's 2021 rent control cut property values 4.0-5.5%; renters gained wealth (more so higher-income renters), while landlords and homeowners lost via capitalization/spillover effects.</t>
         </is>
       </c>
-      <c r="I110" s="12" t="inlineStr">
+      <c r="K110" s="12" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0094119026000161</t>
         </is>
@@ -5712,32 +6722,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D111" s="14" t="inlineStr">
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
         <is>
           <t>The topography of regulatory costs: The shadow cost-gradient of parking standards</t>
         </is>
       </c>
-      <c r="E111" s="14" t="inlineStr">
+      <c r="F111" s="14" t="inlineStr">
         <is>
           <t>W. Bowman Cutter; Sofia F. Franco; W. Skyler Lewis</t>
         </is>
       </c>
-      <c r="F111" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H111" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
         <is>
           <t>Parking minimums; Land use regulations; Non-residential market; Mixed geographically weighted regression; Shadow cost; Regulation cost gradient</t>
         </is>
       </c>
-      <c r="H111" s="14" t="inlineStr">
+      <c r="J111" s="14" t="inlineStr">
         <is>
           <t>Uses a Mixed Geographically Weighted hedonic regression on LA County commercial parcels to estimate location-specific shadow costs of mandatory parking minimums.</t>
         </is>
       </c>
-      <c r="I111" s="15" t="inlineStr">
+      <c r="K111" s="15" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S009411902600001X</t>
         </is>
@@ -5759,32 +6779,42 @@
           <t>2026 (Vol.152)</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>When the neighbors are watching: Immigrant integration policy and housing wealth</t>
         </is>
       </c>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Mario F. Carillo; Lavinia Piemontese; Francesco Flaviano Russo</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G112" s="11" t="inlineStr">
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Migration &amp; labor; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
         <is>
           <t>Immigration; Integration; Reception; Attention; Real estate prices</t>
         </is>
       </c>
-      <c r="H112" s="11" t="inlineStr">
+      <c r="J112" s="11" t="inlineStr">
         <is>
           <t>Event study of refugee-center-to-integration-facility conversions; negative housing-wealth effects only emerge during periods of high public attention to immigration.</t>
         </is>
       </c>
-      <c r="I112" s="12" t="inlineStr">
+      <c r="K112" s="12" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S009411902600015X</t>
         </is>
@@ -5806,28 +6836,38 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="D113" s="14" t="inlineStr">
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
         <is>
           <t>The effects of immigration restrictions on innovation: lessons from the age of mass migration in the USA</t>
         </is>
       </c>
-      <c r="E113" s="14" t="inlineStr">
+      <c r="F113" s="14" t="inlineStr">
         <is>
           <t>Benjamin Cornejo-Costas; Andrea Morrison</t>
         </is>
       </c>
-      <c r="F113" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G113" s="14" t="inlineStr"/>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
+          <t>Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr"/>
+      <c r="J113" s="14" t="inlineStr">
+        <is>
           <t>Studies the US 1921-1924 Quota Act's effect on patenting; counties and technologies most affected by the immigration restriction saw sharp declines in patenting, with geographic variation and reduced breakthrough innovations.</t>
         </is>
       </c>
-      <c r="I113" s="15" t="inlineStr">
+      <c r="K113" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/jeg/lbag014</t>
         </is>
@@ -5849,32 +6889,42 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
         <is>
           <t>Crowdfunding and industrial diversification</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Nicola Cortinovis</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G114" s="11" t="inlineStr">
+      <c r="G114" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
         <is>
           <t>credit insecurity; crowdfunding; industrial diversification; relatedness; US</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr">
+      <c r="J114" s="11" t="inlineStr">
         <is>
           <t>Evolutionary-economic-geography analysis showing crowdfunded industries tend to integrate into existing local specialization patterns, especially where they align with existing capabilities; the effect is stronger in credit-constrained regions.</t>
         </is>
       </c>
-      <c r="I114" s="12" t="inlineStr">
+      <c r="K114" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/jeg/lbag032</t>
         </is>
@@ -5896,28 +6946,38 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D115" s="14" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
         <is>
           <t>Structural embeddedness and brokerage in property markets: an iterative approach to evolving market architectures</t>
         </is>
       </c>
-      <c r="E115" s="14" t="inlineStr">
+      <c r="F115" s="14" t="inlineStr">
         <is>
           <t>Maira Magnani; Gabriel Barros</t>
         </is>
       </c>
-      <c r="F115" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G115" s="14" t="inlineStr"/>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr"/>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
           <t>Combines relational thinking, economic geography, and economic sociology to examine asset managers' growing power in property markets, focused on Brazil's real estate sector; argues market power stems from structural embeddedness and brokerage strategies.</t>
         </is>
       </c>
-      <c r="I115" s="15" t="inlineStr">
+      <c r="K115" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/jeg/lbag027</t>
         </is>
@@ -5939,28 +6999,34 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>Care in economic geography: foundation and frontier</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>Amy Horton</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G116" s="11" t="inlineStr"/>
-      <c r="H116" s="11" t="inlineStr">
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H116" s="11" t="inlineStr"/>
+      <c r="I116" s="11" t="inlineStr"/>
+      <c r="J116" s="11" t="inlineStr">
         <is>
           <t>Commentary (marking JoEG's 25th anniversary) arguing care has been marginalized in economic geography despite its foundational economic role, and proposing it as an emerging research frontier.</t>
         </is>
       </c>
-      <c r="I116" s="12" t="inlineStr">
+      <c r="K116" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/jeg/lbag047</t>
         </is>
@@ -5982,32 +7048,42 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="D117" s="14" t="inlineStr">
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
         <is>
           <t>Out of Sight? Revealing Creativity-Led Innovation in Rural Regions</t>
         </is>
       </c>
-      <c r="E117" s="14" t="inlineStr">
+      <c r="F117" s="14" t="inlineStr">
         <is>
           <t>Carolina Castaldi; Nicola Cortinovis; Milene S. Tessarin</t>
         </is>
       </c>
-      <c r="F117" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G117" s="14" t="inlineStr">
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
         <is>
           <t>creativity; innovation; regions; rural; urban; creative occupations; patents; trademarks</t>
         </is>
       </c>
-      <c r="H117" s="14" t="inlineStr">
+      <c r="J117" s="14" t="inlineStr">
         <is>
           <t>Challenges economic geography's urban bias by studying creativity-led innovation in peripheral/rural regions using trademarks (not just patents) across European regions, 2011-2019; finds rural creativity-led innovation is real but only visible via trademark data.</t>
         </is>
       </c>
-      <c r="I117" s="15" t="inlineStr">
+      <c r="K117" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00130095.2026.2654521</t>
         </is>
@@ -6029,28 +7105,38 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
         <is>
           <t>Fiscal Geographies of Housing Governance: Interplay Between Local- and National-Level Property Development Regulations in France</t>
         </is>
       </c>
-      <c r="E118" s="11" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
         <is>
           <t>Pierre Le Brun; Sara Ozogul; Sarah L. Mawhorter</t>
         </is>
       </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G118" s="11" t="inlineStr"/>
-      <c r="H118" s="17" t="inlineStr">
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr"/>
+      <c r="J118" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I118" s="12" t="inlineStr">
+      <c r="K118" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00130095.2026.2658559</t>
         </is>
@@ -6072,28 +7158,34 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D119" s="14" t="inlineStr">
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
         <is>
           <t>Bright Spots and Fading Lights: Dynamics of Knowledge Spillovers and Geographic (Dis)Association in the Florence Fashion Shows, 1951-84</t>
         </is>
       </c>
-      <c r="E119" s="14" t="inlineStr">
+      <c r="F119" s="14" t="inlineStr">
         <is>
           <t>Valeria Pinchera; Diego Rinallo</t>
         </is>
       </c>
-      <c r="F119" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="inlineStr"/>
-      <c r="H119" s="16" t="inlineStr">
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="inlineStr"/>
+      <c r="I119" s="14" t="inlineStr"/>
+      <c r="J119" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I119" s="15" t="inlineStr">
+      <c r="K119" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00130095.2026.2675376</t>
         </is>
@@ -6115,32 +7207,42 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
         <is>
           <t>The political economy of institutionalizing Central Bank Digital Currencies: Disruption, disintermediation, and incumbency within the Bahamas' Sand Dollar and the Eastern Caribbean's DCash</t>
         </is>
       </c>
-      <c r="E120" s="11" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
         <is>
           <t>Andrew Hook</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G120" s="11" t="inlineStr">
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>AI &amp; digital economy; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
         <is>
           <t>Central Bank Digital Currencies; economic geography; disruption; Caribbean</t>
         </is>
       </c>
-      <c r="H120" s="11" t="inlineStr">
+      <c r="J120" s="11" t="inlineStr">
         <is>
           <t>Fieldwork on the Sand Dollar and DCash pilots finds these CBDCs proving less disruptive to incumbent finance than anticipated, due to intermediated design, cash-heavy economies, and incumbent resistance.</t>
         </is>
       </c>
-      <c r="I120" s="12" t="inlineStr">
+      <c r="K120" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261449498</t>
         </is>
@@ -6162,32 +7264,42 @@
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D121" s="14" t="inlineStr">
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
         <is>
           <t>Soil carbon markets for climate change mitigation? Pragmatic economists and matters of concern</t>
         </is>
       </c>
-      <c r="E121" s="14" t="inlineStr">
+      <c r="F121" s="14" t="inlineStr">
         <is>
           <t>Chi-Mao Wang; Julie Ingram; Philippa Simmonds; Damian Maye</t>
         </is>
       </c>
-      <c r="F121" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G121" s="14" t="inlineStr">
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
         <is>
           <t>pragmatic economists; matters of concern; soil carbon markets; marketisation; environmental markets</t>
         </is>
       </c>
-      <c r="H121" s="14" t="inlineStr">
+      <c r="J121" s="14" t="inlineStr">
         <is>
           <t>Comparative Taiwan/UK study of soil-carbon-market construction, highlighting the role of 'pragmatic economist' intermediaries and governance/equity concerns.</t>
         </is>
       </c>
-      <c r="I121" s="15" t="inlineStr">
+      <c r="K121" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261453753</t>
         </is>
@@ -6209,32 +7321,42 @@
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
         <is>
           <t>The ripples of housing financialization: Old actors, new practices in Beirut (Lebanon)</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>Mona Fawaz; Abir Zaatari; Soha Mneimneh</t>
         </is>
       </c>
-      <c r="F122" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
         <is>
           <t>Housing financialization; Developers; Speculative urbanism; Beirut; Lebanon</t>
         </is>
       </c>
-      <c r="H122" s="11" t="inlineStr">
+      <c r="J122" s="11" t="inlineStr">
         <is>
           <t>Introduces 'ripples of financialization' to describe how Beirut's 2004-2014 building boom saw local developers channel capital via social/religious/political networks into speculative housing beyond luxury segments.</t>
         </is>
       </c>
-      <c r="I122" s="12" t="inlineStr">
+      <c r="K122" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261452081</t>
         </is>
@@ -6256,32 +7378,42 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D123" s="14" t="inlineStr">
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
         <is>
           <t>The service transition as double fix: Mass low-end employment, gendered care economies, and the limits of global growth</t>
         </is>
       </c>
-      <c r="E123" s="14" t="inlineStr">
+      <c r="F123" s="14" t="inlineStr">
         <is>
           <t>Claire Cahen; Jaime Jover</t>
         </is>
       </c>
-      <c r="F123" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G123" s="14" t="inlineStr">
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor; Transportation; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
         <is>
           <t>service transition; care; gender; economic geography; low-end employment; double fix</t>
         </is>
       </c>
-      <c r="H123" s="14" t="inlineStr">
+      <c r="J123" s="14" t="inlineStr">
         <is>
           <t>Feminist-geography framework arguing low-end services expand globally as a 'double fix' absorbing surplus labor and sustaining social reproduction, with internal growth-limiting contradictions.</t>
         </is>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="K123" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261453754</t>
         </is>
@@ -6303,32 +7435,42 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>National government in the casino?</t>
         </is>
       </c>
-      <c r="E124" s="11" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>Kelly Kay; Renee Tapp</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="inlineStr">
         <is>
           <t>Fiscal; Austerity; United Kingdom; Financialization</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr">
+      <c r="J124" s="11" t="inlineStr">
         <is>
           <t>Commentary responding to Andy Pike's 'Financialization and Local Statecraft,' asking whether national government has effectively assumed responsibility for local fiscal/public-service risk.</t>
         </is>
       </c>
-      <c r="I124" s="12" t="inlineStr">
+      <c r="K124" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261454518</t>
         </is>
@@ -6350,32 +7492,42 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D125" s="14" t="inlineStr">
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
         <is>
           <t>Reading Canada Lands Company against the archive</t>
         </is>
       </c>
-      <c r="E125" s="14" t="inlineStr">
+      <c r="F125" s="14" t="inlineStr">
         <is>
           <t>Heather Whiteside</t>
         </is>
       </c>
-      <c r="F125" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G125" s="14" t="inlineStr">
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Transportation</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
         <is>
           <t>archives; Canada; ideation; land; state owned enterprise</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr">
+      <c r="J125" s="14" t="inlineStr">
         <is>
           <t>Critical archival analysis of Canada Lands Company (est. 1956, 'reactivated' 1995) revealing scandals and significant activity during its officially 'dormant' period at sites like Quebec City's old port and Toronto's waterfront.</t>
         </is>
       </c>
-      <c r="I125" s="15" t="inlineStr">
+      <c r="K125" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261456540</t>
         </is>
@@ -6397,32 +7549,42 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
         <is>
           <t>The CBD will survive: Forecasting the impacts of the Covid-19 pandemic on long-term firm location preferences</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>Akshay Vij; Ali Ardeshiri; Lynette Washington; Chris Leishman; Andrew Beer</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Housing &amp; real estate; AI &amp; digital economy</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
         <is>
           <t>agglomeration; firm location; future cities; CBDs; COVID-19; remote work</t>
         </is>
       </c>
-      <c r="H126" s="11" t="inlineStr">
+      <c r="J126" s="11" t="inlineStr">
         <is>
           <t>Stated-preference survey of 789 Australian firms finds robust demand for CBD locations (compensating rent differential ~$875/sqm/yr), challenging the 'donut effect' hypothesis.</t>
         </is>
       </c>
-      <c r="I126" s="12" t="inlineStr">
+      <c r="K126" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261456582</t>
         </is>
@@ -6444,32 +7606,42 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D127" s="14" t="inlineStr">
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
         <is>
           <t>Value struggles in the foundational economy: Reclaiming marketplaces as foundational infrastructure</t>
         </is>
       </c>
-      <c r="E127" s="14" t="inlineStr">
+      <c r="F127" s="14" t="inlineStr">
         <is>
           <t>Sara Gonzalez; Myfanwy Taylor</t>
         </is>
       </c>
-      <c r="F127" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G127" s="14" t="inlineStr">
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Transportation; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
         <is>
           <t>foundational economy; value struggles; marketplaces; retail gentrification; activist research</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
+      <c r="J127" s="14" t="inlineStr">
         <is>
           <t>Mixed-method study (survey of 1,500 marketplace users, 3 UK case studies) tracing marketplaces' devaluation as public infrastructure and revalorization as commercial/real-estate assets.</t>
         </is>
       </c>
-      <c r="I127" s="15" t="inlineStr">
+      <c r="K127" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261454066</t>
         </is>
@@ -6491,32 +7663,42 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
         <is>
           <t>Consolidating homegrown property empires and transforming a local state: The multiple trajectories behind commercial cityscapes in Johannesburg after apartheid</t>
         </is>
       </c>
-      <c r="E128" s="11" t="inlineStr">
+      <c r="F128" s="11" t="inlineStr">
         <is>
           <t>Sarita Pillay Gonzalez</t>
         </is>
       </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
         <is>
           <t>Apartheid; Post-apartheid; Real estate; Corporate landlords; Local state</t>
         </is>
       </c>
-      <c r="H128" s="11" t="inlineStr">
+      <c r="J128" s="11" t="inlineStr">
         <is>
           <t>Examines Johannesburg's 1990s-2000s commercial real estate boom as the product of homegrown property oligopolies and post-apartheid local-state transformation, not solely external financialization.</t>
         </is>
       </c>
-      <c r="I128" s="12" t="inlineStr">
+      <c r="K128" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261456542</t>
         </is>
@@ -6538,32 +7720,42 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D129" s="14" t="inlineStr">
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
         <is>
           <t>Envisioning circular futures in shrinking cities and regions: Goal dependencies underpinning transition drivers</t>
         </is>
       </c>
-      <c r="E129" s="14" t="inlineStr">
+      <c r="F129" s="14" t="inlineStr">
         <is>
           <t>Marjan Marjanovic; Wendy Wuyts; Sebastien Bourdin</t>
         </is>
       </c>
-      <c r="F129" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G129" s="14" t="inlineStr">
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Transportation</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
         <is>
           <t>circular economy; goal dependency; evolutionary governance theory; shrinking cities; urban shrinkage</t>
         </is>
       </c>
-      <c r="H129" s="14" t="inlineStr">
+      <c r="J129" s="14" t="inlineStr">
         <is>
           <t>Comparative study of Satakunta (Finland) and Parkstad Limburg (Netherlands) showing circular-economy discourse functions as a strategic governance tool for regions facing population decline, not a fixed endpoint.</t>
         </is>
       </c>
-      <c r="I129" s="15" t="inlineStr">
+      <c r="K129" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/0308518X261456543</t>
         </is>
@@ -6585,28 +7777,38 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>Older people and food insecurity in rural places: Invisibility, complexity and sociality</t>
         </is>
       </c>
-      <c r="E130" s="11" t="inlineStr">
+      <c r="F130" s="11" t="inlineStr">
         <is>
           <t>Paul Milbourne; Megan Blake; Ollie Chesworth</t>
         </is>
       </c>
-      <c r="F130" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G130" s="11" t="inlineStr"/>
-      <c r="H130" s="17" t="inlineStr">
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr"/>
+      <c r="J130" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I130" s="12" t="inlineStr">
+      <c r="K130" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104287</t>
         </is>
@@ -6628,28 +7830,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D131" s="14" t="inlineStr">
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
         <is>
           <t>"Here, everybody looks after everybody else": Older people and a 'rural ethic of care'</t>
         </is>
       </c>
-      <c r="E131" s="14" t="inlineStr">
+      <c r="F131" s="14" t="inlineStr">
         <is>
           <t>Noah Hurton</t>
         </is>
       </c>
-      <c r="F131" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G131" s="14" t="inlineStr"/>
-      <c r="H131" s="16" t="inlineStr">
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr"/>
+      <c r="J131" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I131" s="15" t="inlineStr">
+      <c r="K131" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104321</t>
         </is>
@@ -6671,28 +7883,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
         <is>
           <t>Floating and fading village attachment: A geo-ethnographic investigation into rural junior high adolescents in China</t>
         </is>
       </c>
-      <c r="E132" s="11" t="inlineStr">
+      <c r="F132" s="11" t="inlineStr">
         <is>
           <t>Tangsenyi Shi; Hejia Shi</t>
         </is>
       </c>
-      <c r="F132" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G132" s="11" t="inlineStr"/>
-      <c r="H132" s="17" t="inlineStr">
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr"/>
+      <c r="J132" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I132" s="12" t="inlineStr">
+      <c r="K132" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104320</t>
         </is>
@@ -6714,28 +7936,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D133" s="14" t="inlineStr">
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
         <is>
           <t>"De-tagging the digital Village": How Shuizhuyuan Village transforms rural governance in China's mountainous areas via the synergy of digital technology and cultural development</t>
         </is>
       </c>
-      <c r="E133" s="14" t="inlineStr">
+      <c r="F133" s="14" t="inlineStr">
         <is>
           <t>Hui Liu; Jie Qiao; Jiasen Li; Yongqi Zhao</t>
         </is>
       </c>
-      <c r="F133" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G133" s="14" t="inlineStr"/>
-      <c r="H133" s="16" t="inlineStr">
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; AI &amp; digital economy; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr"/>
+      <c r="J133" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I133" s="15" t="inlineStr">
+      <c r="K133" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104319</t>
         </is>
@@ -6757,28 +7989,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>Exploring the spatial impact of China's government-led tourism development model on vernacular architecture in a traditional village: The case of Yaodong in Lijiashan Village in Shanxi Province, China</t>
         </is>
       </c>
-      <c r="E134" s="11" t="inlineStr">
+      <c r="F134" s="11" t="inlineStr">
         <is>
           <t>Peiyan Li; Kojiro Sho; P. Monica Chien; Shichen Zhao</t>
         </is>
       </c>
-      <c r="F134" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G134" s="11" t="inlineStr"/>
-      <c r="H134" s="17" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr"/>
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I134" s="12" t="inlineStr">
+      <c r="K134" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104318</t>
         </is>
@@ -6800,28 +8042,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D135" s="14" t="inlineStr">
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
         <is>
           <t>Regenerative agriculture in the UK: Stakeholder perspectives and tensions around livestock's role in sustainable land management</t>
         </is>
       </c>
-      <c r="E135" s="14" t="inlineStr">
+      <c r="F135" s="14" t="inlineStr">
         <is>
           <t>Ulrike Ehgartner; Steffen Hirth</t>
         </is>
       </c>
-      <c r="F135" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G135" s="14" t="inlineStr"/>
-      <c r="H135" s="16" t="inlineStr">
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H135" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I135" s="14" t="inlineStr"/>
+      <c r="J135" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I135" s="15" t="inlineStr">
+      <c r="K135" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104314</t>
         </is>
@@ -6843,28 +8095,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
         <is>
           <t>Informal women entrepreneurs' identity in the agri-food sector: An empirically grounded conceptual framework</t>
         </is>
       </c>
-      <c r="E136" s="11" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>Matthew Ayamga; Blandine A. Ekpodile-Domingo; Shayegheh Ashourizadeh</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G136" s="11" t="inlineStr"/>
-      <c r="H136" s="17" t="inlineStr">
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; Migration &amp; labor</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr"/>
+      <c r="J136" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I136" s="12" t="inlineStr">
+      <c r="K136" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104312</t>
         </is>
@@ -6886,28 +8148,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D137" s="14" t="inlineStr">
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
         <is>
           <t>Locally grown consumers: The socio-material agencing of alternative food consumers</t>
         </is>
       </c>
-      <c r="E137" s="14" t="inlineStr">
+      <c r="F137" s="14" t="inlineStr">
         <is>
           <t>Christian Fuentes; Jonas Baath; Emmelina Eriksson</t>
         </is>
       </c>
-      <c r="F137" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G137" s="14" t="inlineStr"/>
-      <c r="H137" s="16" t="inlineStr">
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr"/>
+      <c r="J137" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I137" s="15" t="inlineStr">
+      <c r="K137" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104311</t>
         </is>
@@ -6929,28 +8201,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
         <is>
           <t>The transformation and regeneration of the function of mianzi order in rural Chinese society: A conceptual framework based on relational dimension theory</t>
         </is>
       </c>
-      <c r="E138" s="11" t="inlineStr">
+      <c r="F138" s="11" t="inlineStr">
         <is>
           <t>Wenxiu Wang; Ang Liu</t>
         </is>
       </c>
-      <c r="F138" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G138" s="11" t="inlineStr"/>
-      <c r="H138" s="17" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr"/>
+      <c r="J138" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I138" s="12" t="inlineStr">
+      <c r="K138" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104310</t>
         </is>
@@ -6972,28 +8254,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D139" s="14" t="inlineStr">
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
         <is>
           <t>Towards ordinary rural resilience: The co-production of social infrastructure and everyday life in rural Guangdong, China</t>
         </is>
       </c>
-      <c r="E139" s="14" t="inlineStr">
+      <c r="F139" s="14" t="inlineStr">
         <is>
           <t>Xinhui Wu; Zhenjie Yuan; Liru Cai</t>
         </is>
       </c>
-      <c r="F139" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G139" s="14" t="inlineStr"/>
-      <c r="H139" s="16" t="inlineStr">
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; China &amp; urban transformation; Transportation</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr"/>
+      <c r="J139" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I139" s="15" t="inlineStr">
+      <c r="K139" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104308</t>
         </is>
@@ -7015,28 +8307,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
         <is>
           <t>The different networking strategies of social cooperatives in social farming: Evidence from Italy</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Caterina De Benedictis; Jacopo Sforzi; Roberta Moruzzo; Leonardo Catena; Giulia Granai</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G140" s="11" t="inlineStr"/>
-      <c r="H140" s="17" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr"/>
+      <c r="J140" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I140" s="12" t="inlineStr">
+      <c r="K140" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104307</t>
         </is>
@@ -7058,28 +8360,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D141" s="14" t="inlineStr">
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
         <is>
           <t>Linking local environmental change to technology adoption and agroecological transition: Evidence from Southern Jiangsu, China</t>
         </is>
       </c>
-      <c r="E141" s="14" t="inlineStr">
+      <c r="F141" s="14" t="inlineStr">
         <is>
           <t>Yingying Li; Jianglong Chen; Jinlong Gao; Cheng Chen</t>
         </is>
       </c>
-      <c r="F141" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G141" s="14" t="inlineStr"/>
-      <c r="H141" s="16" t="inlineStr">
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>China &amp; urban transformation; Climate &amp; green transition; Transportation</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr"/>
+      <c r="J141" s="16" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I141" s="15" t="inlineStr">
+      <c r="K141" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104306</t>
         </is>
@@ -7101,28 +8413,38 @@
           <t>2026-08 (Vol.126)</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
         <is>
           <t>Unlocking success: The impact of institutional rules on governance performance in Chinese farmland irrigation systems</t>
         </is>
       </c>
-      <c r="E142" s="11" t="inlineStr">
+      <c r="F142" s="11" t="inlineStr">
         <is>
           <t>Lin Li; Liesbeth Dries; Yuchun Zhu</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G142" s="11" t="inlineStr"/>
-      <c r="H142" s="17" t="inlineStr">
+      <c r="G142" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr"/>
+      <c r="J142" s="17" t="inlineStr">
         <is>
           <t>— (abstract not auto-retrieved; open via link)</t>
         </is>
       </c>
-      <c r="I142" s="12" t="inlineStr">
+      <c r="K142" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jrurstud.2026.104305</t>
         </is>
@@ -7144,32 +8466,42 @@
           <t>2026 (Vol.160)</t>
         </is>
       </c>
-      <c r="D143" s="14" t="inlineStr">
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
         <is>
           <t>Evaluating the spatial-temporal impact of urban nature on urban vitality in Vancouver: A social media and GPS data approach</t>
         </is>
       </c>
-      <c r="E143" s="14" t="inlineStr">
+      <c r="F143" s="14" t="inlineStr">
         <is>
           <t>Yongming Huang; Jiani Du; Mingze Chen; Yuxuan Lin; Shaopo Huang; Yuxuan Cai</t>
         </is>
       </c>
-      <c r="F143" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G143" s="14" t="inlineStr">
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Transportation; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
         <is>
           <t>Urban nature environment; Urban vitality; Mobility data; Crowdsourced data; Computer vision; Natural language processing; Geographically and Temporally Weighted Regression</t>
         </is>
       </c>
-      <c r="H143" s="14" t="inlineStr">
+      <c r="J143" s="14" t="inlineStr">
         <is>
           <t>Natural elements in urban environments enhance livability and health, strengthening urban vitality. However, existing research has primarily focused on physical indicators, with limited attention paid to the joint influence of behavioral and perceptual dimensions on urban vitality. To address this gap, this study integrates a spatiotemporal analytical framework encompassing three dimensions: natural elements, human perception, and activity diversity. Focusing on Vancouver, we utilized smartphone-GPS and social media data from 2018 to 2023 to explore temporal (weekdays vs. weekends) and spatial dimensions. Using machine learning techniques (Google Vision, K-means and sentiment analysis) on multivariate social media data, we also analyzed changes in activity diversity over time. We assessed the multidimensional influences on urban vitality using the Geographically and Temporally Weighted Regression (GTWR) model. Our results show that during the pandemic, attention to nature and outdoor activities increased significantly, while cultural and social activities and transportation initially decreased but quickly recovered. Sentiment scores, natural elements, and human activity preferences significantly influenced urban vitality during COVID-19, with notable spatiotemporal heterogeneity. The pandemic intensified residents' reliance on natural spaces and green transportation, altering the spatial distribution of urban vitality. These findings provide a basis for optimizing natural spaces and sustainable transportation planning in future urban development.</t>
         </is>
       </c>
-      <c r="I143" s="15" t="inlineStr">
+      <c r="K143" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2025.107824</t>
         </is>
@@ -7191,32 +8523,42 @@
           <t>2026 (Vol.161)</t>
         </is>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
         <is>
           <t>The role of social, policy and economic forces in shaping forest restoration practices in Europe</t>
         </is>
       </c>
-      <c r="E144" s="11" t="inlineStr">
+      <c r="F144" s="11" t="inlineStr">
         <is>
           <t>Maitane Erdozain; Iciar Alberdi; Reka Aszalos; Kurt Bollmann; Vassilis Detsis; Jurij Diaci; Martina Dodan; Georgios Efthimiou; Laszlo Galhidy; Marie Haase; Johanna Hoffmann; Delphine Jaymond; Elisabeth Johann; Henrik Jorgensen; Frank Krumm; Timo Kuuluvainen; Thibault Lachat; Katharina Lapin; Marcus Lindner; Palle Madsen; Liviu Nichiforel; Maciej Pach; Yoan Paillet; Ciprian Palaghianu; Jordi Palau; Jesus Peman; Sanja Peric; Susanne Raum; Silvio Schuler; Jerzy Skrzyszewski; Johan Svensson; Sander Teeuwen; Giorgio Vacchiano; Kris Vandekerkhove; Isabel Canellas; Maria Menendez-Miguelez; Leland Warden; Simon Fleckenstein; Metodi Sotirov; Moses Kazungu; Marcel Hunziker; Luc De Keersmaeker; Aitor Avila Callau; Sergio de-Miguel</t>
         </is>
       </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Place-based policy &amp; inequality; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
         <is>
           <t>Forest policy; Forest governance; History; Ecological restoration; Forest management; Restoration financing</t>
         </is>
       </c>
-      <c r="H144" s="11" t="inlineStr">
+      <c r="J144" s="11" t="inlineStr">
         <is>
           <t>Forest restoration in Europe has a complex history strongly influenced by various social, policy and economic factors. Understanding these influences is essential for shaping effective restoration strategies and avoiding past mistakes, particularly in light of meeting ambitious targets outlined in initiatives such as the EU Nature Restoration Regulation. Here we identify the key social, policy and economic drivers, barriers and enablers that have historically shaped forest restoration across Europe. We analyzed and synthesized detailed information from historical national narratives on forest restoration provided by experts from 18 European countries. Our work details how wars, changes in governance (centralization vs. decentralization) and forest tenure (privatization vs. nationalization), different policy instruments (regulatory, financial, persuasive and organizational), market fluctuations and sociodemographic changes (e.g., rural abandonment, changes in public opinion) have driven the development of forest restoration in Europe. The findings underscore the need to use inclusive and innovative governance mechanisms to reconcile diverging societal paradigms (e.g., rural vs. urban, conservation vs. forestry) partly reflected in incoherent forest-related policies, as well as to address the fragmentation resulting from forest privatization. Ensuring stable funding mechanisms (e.g., remuneration systems for forest ecosystem services) alongside favorable regulatory frameworks will also be key for successful large-scale forest restoration efforts. Policy recommendations are made to ensure the effective implementation of the EU Nature Restoration Regulation, including a hybrid governance model that balances strong national regulatory frameworks with local adaptability to diverse socioecological contexts, integrating socioeconomic metrics, strengthening public engagement, and leveraging market-based and green tax incentives.</t>
         </is>
       </c>
-      <c r="I144" s="12" t="inlineStr">
+      <c r="K144" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2025.107876</t>
         </is>
@@ -7238,32 +8580,42 @@
           <t>2026 (Vol.162)</t>
         </is>
       </c>
-      <c r="D145" s="14" t="inlineStr">
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
         <is>
           <t>Urban land use prediction and construction effectiveness assessment supporting SDG 11.3.1 and regional planning goals</t>
         </is>
       </c>
-      <c r="E145" s="14" t="inlineStr">
+      <c r="F145" s="14" t="inlineStr">
         <is>
           <t>Ze Zhang; Weiguo Jiang; Ziyan Ling; Xudong Guo; Jie Song; Zhijie Xiao; Xiaogan Yin</t>
         </is>
       </c>
-      <c r="F145" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G145" s="14" t="inlineStr">
+      <c r="G145" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H145" s="14" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; Place-based policy &amp; inequality; Transportation</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
         <is>
           <t>SDG 11.3.1; Urban land use simulation; Sustainable urban planning; Urban land use efficiency; Xiongan New Area; China</t>
         </is>
       </c>
-      <c r="H145" s="14" t="inlineStr">
+      <c r="J145" s="14" t="inlineStr">
         <is>
           <t>Urban land use serves as the fundamental foundation for human survival and development, providing essential natural resources. Simulation is an important tool for assessing the impacts of urban planning and construction of new urban areas. To support policy implementation for the development of the Xiongan New Area and promote sustainable urban management, we use the Data-Information-Knowledge-Wisdom (DIKW) model as a framework for predicting future land spatial changes considering sustainable development of urban planning. We developed a novel New Urban Multi-objective Land Use Prediction (NUMLUP) method, integrating a Genetic Algorithm (GA), Multi-Objective Planning (MOP), and the Conversion of Land Use and its Effects at Small Region Extent (CLUES) model. Using this approach, we obtained urban land spatial distribution data for three scenarios: the Historical Continuation Scenario (HCS), Policy Planning Scenario (PPS), and Planned Sustainable Development Scenario (PSDS). To evaluate Sustainable Development Goal (SDG) 11.3.1 and Regional Planning Goals (RPGs), we assessed 19 consecutive years of construction effectiveness—covering both past (2017-2023) and future (2023-2035) periods under the three scenarios. The dataset achieved a multi-year overall accuracy (OA) exceeding 0.87 and a kappa index above 0.83. The built-up area gradually increased, while wetlands (dominated by Baiyangdian) declined significantly from 2017 to 2023. From 2023 to 2035 the expansion of built-up land slows down; under the PPS, forest and wetland areas underwent the most drastic changes, with overall improvement rates ranked PPS &gt; PSDS &gt; HCS. The LCRPGR is consistently greater than 1 from 2023 to 2035, reflecting a plan that provides land to meet population growth and demand. Our research provides robust support for monitoring sustainable urban development and implementing regional policies.</t>
         </is>
       </c>
-      <c r="I145" s="15" t="inlineStr">
+      <c r="K145" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2025.107893</t>
         </is>
@@ -7285,32 +8637,42 @@
           <t>2026 (Vol.164)</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
         <is>
           <t>Legal incentives for public land grabbing via deforestation in the Brazilian Amazon</t>
         </is>
       </c>
-      <c r="E146" s="11" t="inlineStr">
+      <c r="F146" s="11" t="inlineStr">
         <is>
           <t>Brenda Brito; Jeferson Almeida</t>
         </is>
       </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G146" s="11" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Housing &amp; real estate; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
         <is>
           <t>Brazilian Amazon; Land Title; Land Laws; Deforestation; Public Forests</t>
         </is>
       </c>
-      <c r="H146" s="11" t="inlineStr">
+      <c r="J146" s="11" t="inlineStr">
         <is>
           <t>This paper examines how federal and state land laws in the Brazilian Amazon create incentives that benefit private actors illegally occupying public lands, who subsequently seek legalization through land titling. Throughout this process, they invade public lands, deforest the area to signal occupation, request land titles to governmental agencies, and often lobby to modify land laws in favor of title acquisition. While existing scholarship has focused primarily on federal land policies, this study provides a systematic assessment of land laws in all nine Amazonian states, which are particularly relevant given that between 40% and 60% of undesignated public land in the region falls under state jurisdiction. Here, we identify five structural incentives embedded in current land legislation that favor the persistence of public land encroachment: (i) the absence or extension of cut-off dates for the occupation of public lands that can be titled; (ii) the possibility of issuing titles over illegally deforested areas; (iii) the weakness or lack of requirements to restore environmental damage prior to titling; (iv) the pricing mechanisms that substantially undervalues public land; and (v) the limited coordination among land agencies, resulting in an increased risk of titles being issued in areas with other land claims' priorities according to the law. Our results highlight how current land laws contribute to inefficient allocation of public land, fiscal losses, and continued deforestation. These findings provide empirical support for policy debates in Brazil focused on aligning land laws with environmental protection, climate commitments, and more efficient management of public assets.</t>
         </is>
       </c>
-      <c r="I146" s="12" t="inlineStr">
+      <c r="K146" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.107968</t>
         </is>
@@ -7332,32 +8694,42 @@
           <t>2026 (Vol.164)</t>
         </is>
       </c>
-      <c r="D147" s="14" t="inlineStr">
+      <c r="D147" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
         <is>
           <t>A novel approach to undertake a socio-economic impact assessment of a major urban regeneration project</t>
         </is>
       </c>
-      <c r="E147" s="14" t="inlineStr">
+      <c r="F147" s="14" t="inlineStr">
         <is>
           <t>Cathal O'Donoghue; Mohammed Zajeer Ahmed; Patrick McGetrick</t>
         </is>
       </c>
-      <c r="F147" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G147" s="14" t="inlineStr">
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H147" s="14" t="inlineStr">
+        <is>
+          <t>Migration &amp; labor; Climate &amp; green transition; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
         <is>
           <t>Urban regeneration; Impact Analysis; Input-Output model; Deprivation; Social impact; Environmental impact</t>
         </is>
       </c>
-      <c r="H147" s="14" t="inlineStr">
+      <c r="J147" s="14" t="inlineStr">
         <is>
           <t>Urban regeneration investments, particularly those involving multi-million-euro allocations, require diverse evaluation methodologies to comprehensively assess their impacts. This paper aims to evaluate the effects of a substantial urban regeneration investment in Limerick, a county in west of Ireland, characterized by significant deprivation. The case study examined is the Limerick opera house, a major mixed-use development comprising office space, a public library, hotel accommodation, and leisure facilities. This project offers an exemplary context for analysing a complex urban regeneration initiative characterised by multiple, interrelated objective. Utilizing a hybrid, downscaled multi regional input output (MRIO) analysis alongside impact analysis, this study examines the economic, environmental, and social impacts of the project. The results indicate that the project generated 1676 jobs during the construction phase and 2400 jobs in the long-term phase. However, the employment opportunities created did not substantially benefit deprived areas, primarily due to a mismatch between the skill sets required for the jobs and those available within the local population. This study highlights the necessity for supplementary training and upskilling initiatives to effectively target these communities.</t>
         </is>
       </c>
-      <c r="I147" s="15" t="inlineStr">
+      <c r="K147" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.107962</t>
         </is>
@@ -7379,32 +8751,42 @@
           <t>2026 (Vol.165)</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
         <is>
           <t>Computational intelligence based land-use allocation approaches for mixed use areas</t>
         </is>
       </c>
-      <c r="E148" s="11" t="inlineStr">
+      <c r="F148" s="11" t="inlineStr">
         <is>
           <t>Sabab Aosaf; Muhammad Ali Nayeem; Afsana Haque; M. Sohel Rahman</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G148" s="11" t="inlineStr">
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality; Housing &amp; real estate; Transportation</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
         <is>
           <t>Policy support system; Urban land-use allocation; Land-use optimization; Multi-objective optimization; Computational intelligence</t>
         </is>
       </c>
-      <c r="H148" s="11" t="inlineStr">
+      <c r="J148" s="11" t="inlineStr">
         <is>
           <t>Urban land-use allocation represents a complex multi-objective optimization problem critical for sustainable urban development policy. This paper presents novel computational intelligence approaches for optimizing land-use allocation in mixed-use areas, addressing inherent trade-offs between land-use compatibility and economic objectives. We develop multiple optimization algorithms, including custom variants integrating differential evolution with multi-objective genetic algorithms. Key contributions include: (1) CR+DES algorithm leveraging scaled difference vectors for enhanced exploration, (2) systematic constraint relaxation strategy improving solution quality while maintaining feasibility, and (3) statistical validation using Kruskal-Wallis tests with compact letter displays. Applied to a real-world case study with 1290 plots, CR+DES achieves 3.16% improvement in land-use compatibility compared to state-of-the-art methods, while MSBX+MO excels in price optimization with 3.3% improvement. Statistical analysis confirms that algorithms incorporating difference vectors significantly outperform traditional approaches across multiple metrics. These findings provide urban planners and policymakers with evidence-based computational tools for balancing competing objectives in land-use allocation, supporting more effective urban development policies in rapidly urbanizing regions.</t>
         </is>
       </c>
-      <c r="I148" s="12" t="inlineStr">
+      <c r="K148" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.107984</t>
         </is>
@@ -7426,32 +8808,42 @@
           <t>2026 (Vol.165)</t>
         </is>
       </c>
-      <c r="D149" s="14" t="inlineStr">
+      <c r="D149" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
         <is>
           <t>Urban sprawl in Latin America: A systematic review of the existing literature and emerging insights</t>
         </is>
       </c>
-      <c r="E149" s="14" t="inlineStr">
+      <c r="F149" s="14" t="inlineStr">
         <is>
           <t>Reynaldo Hinojosa-Contreras; Eric Gielen; Jose-Sergio Palencia-Jimenez; Isidro Cantarino-Marti</t>
         </is>
       </c>
-      <c r="F149" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G149" s="14" t="inlineStr">
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H149" s="14" t="inlineStr">
+        <is>
+          <t>Place-based policy &amp; inequality; Transportation; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
         <is>
           <t>Urban sprawl; Latin America; Spatial indicators; Systematic review</t>
         </is>
       </c>
-      <c r="H149" s="14" t="inlineStr">
+      <c r="J149" s="14" t="inlineStr">
         <is>
           <t>Urban sprawl has become one of the most pressing challenges in Latin American cities, driven by a complex interplay of economic, political, and spatial factors. Despite being one of the most urbanized regions in the world, Latin America lacks a consistent analytical framework to fully understand the indicators, patterns, approaches and consequences of urban sprawl. This study conducts a systematic review of 56 peer-reviewed articles published between 2004 and 2025, applying a six-dimensional analytical framework: (i) general publication features, (ii) scale of analysis, (iii) methodological approaches, (iv) indicators employed, (v) drivers of change, and (vi) effects of urban sprawl. Findings reveal a strong concentration of city and metropolitan level studies in Mexico, Brazil, and Chile, with GIS-based spatial analysis dominating the methodological landscape, while contemporary approaches, such as machine learning and multi-criteria decision analysis, remain underused. Density and land use/land cover change are the most frequently applied indicators, followed by fragmentation and centrality metrics. The review underlines the context of structural drivers, including neoliberal housing policies, infrastructure-led growth, land market speculation, and governance gaps, which critically shape the spatial outcomes of sprawl. Socio-spatial inequality emerges as the most persistent and structural effect, yet multidimensional indices capturing access to infrastructure, public services, and ecosystem amenities are almost absent. The discussion calls for rethinking the application of Global North metrics to Global South contexts and advocates for the development of justice-oriented, context-sensitive frameworks that reflect Latin America's unique urban realities.</t>
         </is>
       </c>
-      <c r="I149" s="15" t="inlineStr">
+      <c r="K149" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.107980</t>
         </is>
@@ -7473,28 +8865,38 @@
           <t>2026 (Vol.165)</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
         <is>
           <t>Exploring drivers and motivations behind garden management for climate change adaptation</t>
         </is>
       </c>
-      <c r="E150" s="11" t="inlineStr">
+      <c r="F150" s="11" t="inlineStr">
         <is>
           <t>J. Teerlinck; K. Van Meerbeek; K. Wittemans; V. Dewaelheyns; P. Raymaekers; F. Lange; T. Steen; B. Somers</t>
         </is>
       </c>
-      <c r="F150" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G150" s="11" t="inlineStr"/>
+      <c r="G150" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; Housing &amp; real estate; Place-based policy &amp; inequality</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr"/>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
           <t>Serving as an integral part of urban green infrastructure, the collective network of domestic gardens could make a substantial contribution to climate change adaptation. Nevertheless, these private outdoor spaces are autonomously managed by many individual gardeners, often prioritizing aesthetics and maintenance convenience, rather than environmental considerations. Understanding how people manage their gardens, and why they make certain gardening decisions is crucial for unlocking the climate adaptation potential of gardens, shedding light on the current situation and identifying opportunities for change. Unfortunately, limited research has been conducted on the personal drivers behind gardeners' decisions. Therefore, our research aims at unveiling current gardening practices and their drivers through an online citizen science survey of Flemish domestic garden owners (n = 827). Using a Structural Equation Modeling (SEM) approach, we studied how motivations, knowledge, spatial- and socio-economic factors are associated with garden management decisions related to sealed soil, lawns, and tree cover. Our findings show that factors such as spatial context, socio-economic status, and personal motivations are more critical in shaping garden composition and management. The results stress the complexity of garden management, where traditional practices and cultural perceptions coexist with a growing ecological awareness and highlights the intricate relationship between local contexts and the diverse personal drivers influencing individual gardeners' decisions. By recognizing this interconnectedness, we emphasize the need for gardening policies tailored to spatial and socio-economic variations and offer insights that can inform urban planners and policymakers on how to harness the untapped climate adaptation potential within these private outdoor spaces.</t>
         </is>
       </c>
-      <c r="I150" s="12" t="inlineStr">
+      <c r="K150" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.107975</t>
         </is>
@@ -7516,32 +8918,42 @@
           <t>2026 (Vol.167)</t>
         </is>
       </c>
-      <c r="D151" s="14" t="inlineStr">
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
         <is>
           <t>Public open space as a catalyst for income sorting in high-density urban areas: Evidence from Hong Kong</t>
         </is>
       </c>
-      <c r="E151" s="14" t="inlineStr">
+      <c r="F151" s="14" t="inlineStr">
         <is>
           <t>Ruiyang Wang; Shuai Shi; Siu Kei Wong; Huan Lu</t>
         </is>
       </c>
-      <c r="F151" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G151" s="14" t="inlineStr">
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H151" s="14" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Place-based policy &amp; inequality; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
         <is>
           <t>Bid rent theory; Housing market; Income sorting; Spatial equilibrium model; Urban inequality</t>
         </is>
       </c>
-      <c r="H151" s="14" t="inlineStr">
+      <c r="J151" s="14" t="inlineStr">
         <is>
           <t>Due to housing affordability constraints, residents in high-density cities often have limited private residential space (PRS) and may seek proximity to public open space (POS) as a compensatory amenity. However, existing literature largely focuses on estimating the amenity value of POS without considering the trade-offs between PRS and POS across income groups. To address this gap, we develop a spatial equilibrium model (SEM) that disentangles these trade-offs by analysing the income and substitution effects in bidding behaviours for POS. Using 176,865 housing transactions in Hong Kong from 2017 to 2022, we find that higher-income households consistently outbid lower-income households for both POS and PRS, suggesting a link between POS distribution and income sorting. However, when mobility was restricted during the Covid-19 pandemic, lower-income households bid more aggressively for POS at the expense of PRS, indicating an unusual substitution effect. These findings shed light on the inequitable outcomes of amenity-driven bidding mechanisms in housing markets, highlighting implications for planning responses to mitigate housing inequality, particularly in high-density metropolitan areas.</t>
         </is>
       </c>
-      <c r="I151" s="15" t="inlineStr">
+      <c r="K151" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.108060</t>
         </is>
@@ -7563,32 +8975,42 @@
           <t>2026 (Vol.167)</t>
         </is>
       </c>
-      <c r="D152" s="11" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
         <is>
           <t>Uneven recognition: A comparative study of indigenous communities' struggle for securing customary land rights in Indonesia</t>
         </is>
       </c>
-      <c r="E152" s="11" t="inlineStr">
+      <c r="F152" s="11" t="inlineStr">
         <is>
           <t>Andi Rahmat Hidayat; Otto Hospes; C.J.A.M. Termeer</t>
         </is>
       </c>
-      <c r="F152" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G152" s="11" t="inlineStr">
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H152" s="11" t="inlineStr">
+        <is>
+          <t>Rural, food &amp; land; Transportation; Climate &amp; green transition</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
         <is>
           <t>Land; Forest; Customary rights; Adat communities; Struggle; Recognition; Indonesia</t>
         </is>
       </c>
-      <c r="H152" s="11" t="inlineStr">
+      <c r="J152" s="11" t="inlineStr">
         <is>
           <t>The struggle for customary land rights in Indonesia gained prominence following the collapse of Suharto's authoritarian regime in 1998 and the country's subsequent transition to democracy and decentralization. While these changes seized new political space to (re)claim rights over land previously appropriated by public authorities and companies, the realization of these rights has remained limited in practice. This study examines why recognition of customary land rights has succeeded in some communities but not in others by comparing three districts in Sulawesi. We identify four main findings: while various national laws have formally recognized customary land rights of adat communities, in all cases, adat communities struggled with legal fragmentation. Second, those who were able to establish close connections with influential politicians and did not face alliances of predatory interests between state and business elites were best positioned to get their adat claims recognized by local authorities. Third, the local presence of NGOs is crucial in helping the communities navigate complex government procedures, but most importantly, in cultivating and maintaining close ties with state actors. Finally, reform-oriented leadership can facilitate recognition, particularly when communities have established strong informal ties with this leader. Based on these findings, we propose several measures to enhance the prospect for recognition: simplifying bureaucratic procedures; strengthening the capacities and outreach of local NGOs to support adat communities; emphasizing the importance of developing close, informal ties by adat communities with local leaders; and reforming the electoral system to reduce politicians' vulnerability to co-optation by extractive interests.</t>
         </is>
       </c>
-      <c r="I152" s="12" t="inlineStr">
+      <c r="K152" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.108061</t>
         </is>
@@ -7610,32 +9032,42 @@
           <t>2026 (Vol.167)</t>
         </is>
       </c>
-      <c r="D153" s="14" t="inlineStr">
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
         <is>
           <t>Before the ground breaks: Is inclusionary zoning a shield or a signal of gentrification?</t>
         </is>
       </c>
-      <c r="E153" s="14" t="inlineStr">
+      <c r="F153" s="14" t="inlineStr">
         <is>
           <t>Lance Freeman; Yining Lei; Magda Maaoui</t>
         </is>
       </c>
-      <c r="F153" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G153" s="14" t="inlineStr">
+      <c r="G153" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H153" s="14" t="inlineStr">
+        <is>
+          <t>Housing &amp; real estate; Place-based policy &amp; inequality; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
         <is>
           <t>Inclusionary zoning; Housing production; Gentrification; New York City</t>
         </is>
       </c>
-      <c r="H153" s="14" t="inlineStr">
+      <c r="J153" s="14" t="inlineStr">
         <is>
           <t>Inclusionary Zoning (IZ) is a tool in land use planning for leveraging new market-rate housing to produce affordable housing, typically in exchange for increased density. While growing in popularity, IZ receives criticisms for the possibility that its market-rate housing component would lead to gentrification by altering local housing markets. Using New York City's Mandatory Inclusionary Housing (MIH) program, a relatively ambitious IZ effort, we test if IZ increases home sales prices and rents in areas that are designated as MIH zones. Based on a comparison of MIH zones to surrounding control areas, we find evidence of MIH increased both home sales prices and rents, but the most consistent and statistically significant growth occurred in areas immediately surrounding MIH zones. We find little evidence of price escalation in MIH zones. Our findings suggest that for IZs that are geographically limited like MIH, the costs to residents such as gentrification and increased housing prices may be externalized onto nearby neighborhoods. This points to a policy need for more spatially integrated planning approaches to affordable housing, where affordability protections extend beyond narrowly drawn IZ boundaries.</t>
         </is>
       </c>
-      <c r="I153" s="15" t="inlineStr">
+      <c r="K153" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.108033</t>
         </is>
@@ -7657,32 +9089,42 @@
           <t>2026 (Vol.168)</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
         <is>
           <t>Transboundary ecosystem service flows in Central Asia: Enhancing global sustainable development goals (SDGs) through the grain-water-carbon-culture network (GWCCN)</t>
         </is>
       </c>
-      <c r="E154" s="11" t="inlineStr">
+      <c r="F154" s="11" t="inlineStr">
         <is>
           <t>Jiangyue Li; Philippe De Maeyer; Tim Van de Voorde; Xi Chen; Yaoming Li</t>
         </is>
       </c>
-      <c r="F154" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G154" s="11" t="inlineStr">
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>Climate &amp; green transition; Transportation; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
         <is>
           <t>Ecosystem service flows (ESFs); Sustainable development goals (SDGs); Central Asia; Grain-water-carbon-culture network (GWCCN); Cross-border spillover; Global coupling</t>
         </is>
       </c>
-      <c r="H154" s="11" t="inlineStr">
+      <c r="J154" s="11" t="inlineStr">
         <is>
           <t>Transboundary ecosystem service flows (ESFs) are crucial links that connect natural and social systems across regions. With its unique geographical advantages, Central Asia serves as a strategic hub for regional and global connectivity, contributing to trade, cultural exchange, and technological development. This study presents a framework for understanding how ESFs support the achievement of SDGs in 7 transboundary countries and 195 nations globally, with a focus on the cross-border and remote effects of the grain-water-carbon-culture network (GWCCN) in Central Asia. Our findings highlight that water yield and soil conservation services in the Syr Darya and Amu Darya Basins were critical for downstream countries, with Uzbekistan and Turkmenistan relying on upstream flows from Tajikistan and Kyrgyzstan (30% and 21% deficits, respectively). Grain production was concentrated in Uzbekistan (35% of total flows), whereas carbon storage and habitat quality services were highly concentrated in the Fergana Valley (40% and 70%, respectively). Cross-border spillovers benefit neighboring countries and global regions. Approximately 20 million people rely on Central Asia-China transboundary rivers. Globally, water exports range from 0.3 to 82.17 billion t, grain exports range from 0.003 to 8.52 billion t, tourism and cultural flows attract 43.86 billion visitors, and carbon and habitat quality services cover 0.09-7.53 billion ha. Importantly, the ESFs of Central Asia significantly support SDG achievement, with contribution rates of 80-90% in China and Russia, 40-60% in Iran and Afghanistan, and under 10% in Pakistan, Azerbaijan, and Mongolia. Globally, the United States, India, and EU countries receive 43%, 36%, and 13-17%, respectively, supporting the SDGs related to food security, climate action, and socioeconomic development. Overall, Central Asia occupies a strategic position in the global ESF network.</t>
         </is>
       </c>
-      <c r="I154" s="12" t="inlineStr">
+      <c r="K154" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.landusepol.2026.108058</t>
         </is>
@@ -7704,28 +9146,38 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D155" s="14" t="inlineStr">
+      <c r="D155" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
         <is>
           <t>Weathering the Climate Storm: Climate Risk and Urban Export Resilience</t>
         </is>
       </c>
-      <c r="E155" s="14" t="inlineStr">
+      <c r="F155" s="14" t="inlineStr">
         <is>
           <t>Jingmei Ma; Kaixin Deng; Jie Wu</t>
         </is>
       </c>
-      <c r="F155" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G155" s="14" t="inlineStr"/>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H155" s="14" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; Transportation; China &amp; urban transformation</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr"/>
+      <c r="J155" s="14" t="inlineStr">
+        <is>
           <t>Against the backdrop of increasingly frequent extreme weather events worldwide, urban export resilience is under severe threat, and mitigating the adverse effects of climate risk has become an urgent issue for China's pursuit of high-quality development in its open economy. Focusing on prefecture-level and above cities in China, this study combines customs export data and city-level panel data for 2010-2022, quantifies climate risk using text mining and machine learning methods, and constructs an export resilience index incorporating both stability and safety from dynamic and structural perspectives. On this basis, it empirically examines both the direct effect of climate risk on export resilience and the underlying mechanisms. The results show that: (1) Climate risk significantly weakens urban export resilience, and this finding remains robust after addressing endogeneity and conducting multiple robustness tests. (2) The negative impact is more pronounced in central and western cities, in cities outside the Yangtze River Economic Belt, and in small cities, and is further amplified in cities with lower levels of artificial intelligence, market integration, and trade openness. (3) The digital economy and industrial structure play mediating roles in the relationship between climate risk and export resilience. In addition, technological innovation significantly moderates the climate risk-digital economy-export resilience pathway by strengthening the buffering effect of the digital economy, thereby indirectly alleviating the adverse impact of climate risk. These findings are consistent with China's strategic objective of advancing climate adaptation and open development in tandem under the dual-carbon agenda. They also provide policy implications for enhancing urban export resilience in a differentiated manner.</t>
         </is>
       </c>
-      <c r="I155" s="15" t="inlineStr">
+      <c r="K155" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70129</t>
         </is>
@@ -7747,28 +9199,38 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
         <is>
           <t>As Climate Risks Intensify: How Do Key Digital Technologies Promote Pollution Reduction and Carbon Mitigation? Evidence From China</t>
         </is>
       </c>
-      <c r="E156" s="11" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>Shengling Zhang; Ruibing Ji; Wei Dou; Yu Hao</t>
         </is>
       </c>
-      <c r="F156" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G156" s="11" t="inlineStr"/>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; China &amp; urban transformation; Transportation</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr"/>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
           <t>Key digital technology (KDT) serves as a critical technological foundation for advancing pollution reduction and carbon mitigation (PRCM), while increasingly reshaping regional environmental governance capacity. However, the institutional fluctuations and governance uncertainties induced by intensifying climate risks have introduced both challenges and opportunities for the environmental effectiveness of KDT. Drawing on panel data from 276 prefecture-level cities in China between 2011 and 2021, this study investigates the impact of KDT on PRCM synergy across heterogeneous regional contexts. The findings reveal that KDT significantly enhances the degree of PRCM synergy, highlighting its dual environmental benefits. Moreover, climate risks play differentiated moderating roles in this process. Specifically, climate transition risks amplify the PRCM effect of KDT, reflecting the greater marginal adaptability of technological governance under institutional risk scenarios. In contrast, the overall moderating role of climate physical risks is limited. Heterogeneity analysis suggests that under transition risks, KDT possesses compensatory capacities to address institutional uncertainty, whereas under physical risks, its effectiveness is conditioned by regional structural characteristics and governance capacity. Mechanism analysis further demonstrates that KDT influences PRCM synergy through a chain pathway encompassing 'source prevention-process control-end-stage blocking.' Spatial effect analysis indicates a siphon effect of KDT, with significant negative spillovers on the PRCM synergy of adjacent regions, implying the risk of widening inter-regional disparities in environmental governance outcomes.</t>
         </is>
       </c>
-      <c r="I156" s="12" t="inlineStr">
+      <c r="K156" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70114</t>
         </is>
@@ -7790,28 +9252,38 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D157" s="14" t="inlineStr">
+      <c r="D157" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
         <is>
           <t>Spatial Fluidity and the Outcomes of Entrepreneurial Ecosystems: An Analysis Based on Investment Flows</t>
         </is>
       </c>
-      <c r="E157" s="14" t="inlineStr">
+      <c r="F157" s="14" t="inlineStr">
         <is>
           <t>Angelica Pigola; Bruno Fischer; Gustavo Herminio Salati Marcondes de Moraes</t>
         </is>
       </c>
-      <c r="F157" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G157" s="14" t="inlineStr"/>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H157" s="14" t="inlineStr">
         <is>
+          <t>Climate &amp; green transition; Migration &amp; labor; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr"/>
+      <c r="J157" s="14" t="inlineStr">
+        <is>
           <t>The spatiality of Entrepreneurial Ecosystems (EE) has become a topic of recent interest in literature. Traditionally based on a regionally-bounded appraisal of the contextual conditions leading up to entrepreneurial activity, EE research is facing a shift toward the inclusion of more fine-grained territorial approaches that accommodate complex spatial topologies involving heterogeneous trajectories of local, domestic, and international linkages. Yet we still fall short in grasping how the spatial features of EE relate to their respective outcomes. In this article, we take up this challenge by addressing the extent to which spatiality affects the dynamics of development in EE. To that end, we focus on investment data extracted from Crunchbase covering 11,670 investment transactions spanning 2266 EE located in 118 countries. We then assess the spatiality of EE by means of looking into the association between investment inflows and outflows in relation to post-investment valuation at the level of EE (our measure of EE outcomes). We further qualify this association by adding a vector that associates financial flows to leading EE. We complement our overall analysis by running quantile estimations to check for variations in associations across different levels of development in the analyzed EE. Our findings offer consistent evidence of a positive association between the spatial fluidity of EE and its respective outcomes. This is valid for both inward and outward spatial connections, although stronger associations are perceived for the former. Also, where investments come from/go to matters, as receiving/sending investments from/to the most eminent ecosystems is a good predictor of EE outcomes.</t>
         </is>
       </c>
-      <c r="I157" s="15" t="inlineStr">
+      <c r="K157" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70126</t>
         </is>
@@ -7833,28 +9305,38 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
         <is>
           <t>Agglomeration Economies and Intergovernmental Cooperation in Productive Disaster Management Expenditure</t>
         </is>
       </c>
-      <c r="E158" s="11" t="inlineStr">
+      <c r="F158" s="11" t="inlineStr">
         <is>
           <t>Sudong Kim</t>
         </is>
       </c>
-      <c r="F158" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G158" s="11" t="inlineStr"/>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
+          <t>Housing &amp; real estate; Transportation</t>
+        </is>
+      </c>
+      <c r="I158" s="11" t="inlineStr"/>
+      <c r="J158" s="11" t="inlineStr">
+        <is>
           <t>This study examines how disaster management expenditure affects regional economic growth across different institutional contexts. Analyzing panel data from 226 South Korean municipalities (2011-2021) using fixed effects and System GMM, the analysis reveals systematically heterogeneous effects even after explicitly controlling for population density as a proxy for agglomeration: districts demonstrate the strongest impact, whereas counties show the weakest returns. These differences are consistent with agglomeration economies and vertical intergovernmental cooperation advantages in metropolitan districts. The findings contribute to fiscal federalism theory by demonstrating that for public services with network externalities, cooperative governance can be as crucial as local autonomy in shaping the economic returns to resilience-enhancing disaster management expenditure. Results support differentiated regional policies leveraging institutional characteristics.</t>
         </is>
       </c>
-      <c r="I158" s="12" t="inlineStr">
+      <c r="K158" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70124</t>
         </is>
@@ -7876,28 +9358,38 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D159" s="14" t="inlineStr">
+      <c r="D159" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E159" s="14" t="inlineStr">
         <is>
           <t>Urban-Rural Construction Land Market Integration Under Rural Land Institutional Reform: Evidence From Three Pilot Regions in China</t>
         </is>
       </c>
-      <c r="E159" s="14" t="inlineStr">
+      <c r="F159" s="14" t="inlineStr">
         <is>
           <t>Ying Chen; Kejun Li</t>
         </is>
       </c>
-      <c r="F159" s="13" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G159" s="14" t="inlineStr"/>
+      <c r="G159" s="13" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H159" s="14" t="inlineStr">
         <is>
+          <t>Rural, food &amp; land; China &amp; urban transformation; Housing &amp; real estate</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr"/>
+      <c r="J159" s="14" t="inlineStr">
+        <is>
           <t>China's reform permitting rural collective construction land to enter the market has created new institutional conditions for the integration of the urban-rural land market, revitalizing rural areas, and promoting balanced regional development. From the perspectives of property rights differentiation and governance structure, this study constructs a Structure-Conduct-Performance (SCP) analytical framework to examine patterns of market integration under rural land institutional reform. A comparative case study was conducted in three representative regions in China, namely Wujin District (eastern), Changyuan County (central), and Meitan County (western), to examine the mechanisms of urban-rural construction land markets integration. The results indicate significant regional heterogeneity in the degree of market integration across pilot regions operating under a common reform framework. Depending on local property-right foundations, three distinct governance structures have emerged: market-dominated, government-market hybrid, and government-guided. Each governance structure corresponds with a distinct pattern of price integration. Therefore, rural land system reforms should be adapted to local conditions, with governance paths aligned to the existing property rights foundation, to progressively advance urban-rural land market integration through context-specific governance arrangements.</t>
         </is>
       </c>
-      <c r="I159" s="15" t="inlineStr">
+      <c r="K159" s="15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70131</t>
         </is>
@@ -7919,195 +9411,205 @@
           <t>2026 (Early View)</t>
         </is>
       </c>
-      <c r="D160" s="11" t="inlineStr">
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
         <is>
           <t>Resolving the Growth-Equality Paradox? The Synergistic Effects of Returnee Entrepreneurship Policies on Income Distribution</t>
         </is>
       </c>
-      <c r="E160" s="11" t="inlineStr">
+      <c r="F160" s="11" t="inlineStr">
         <is>
           <t>Shaozhuang Wang; Xueru Yang</t>
         </is>
       </c>
-      <c r="F160" s="10" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="G160" s="11" t="inlineStr"/>
+      <c r="G160" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
+          <t>Migration &amp; labor; Place-based policy &amp; inequality; Rural, food &amp; land</t>
+        </is>
+      </c>
+      <c r="I160" s="11" t="inlineStr"/>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
           <t>Returnee migrant entrepreneurs are pivotal agents of rural revitalization. Policies fostering their entrepreneurship directly address structural bottlenecks in China's countryside. This study evaluates the comprehensive impact and mechanisms of two key returnee entrepreneurship policies in China, namely the returnee entrepreneurship pilot policy and the rural entrepreneurship park policy, on rural income levels and income inequality. Using county-level panel data from China, this study employs the propensity score matching-generalized difference-in-difference method for causal inference. The findings indicate that the returnee entrepreneurship pilot policy and the rural entrepreneurship park policy are complementary. Their coordinated implementation significantly promotes rural income growth, as well as effectively reduces rural income inequality. Mechanism analysis reveals that returnee entrepreneurship policies operate through three channels: entrepreneurial effects, employment effects, and agglomeration effects. These effects are achieved through the construction of a more inclusive entrepreneurial ecosystem. Furthermore, this study highlights the heterogeneity in the effects of returnee entrepreneurship policies. The effectiveness of these policies is influenced differently by factors such as the development of digital inclusive finance, cultural characteristics, and economic development levels. The results emphasize that fostering an inclusive entrepreneurial ecosystem through complementary policy design is essential for achieving both growth and equity goals in returnee entrepreneurship policies.</t>
         </is>
       </c>
-      <c r="I160" s="12" t="inlineStr">
+      <c r="K160" s="12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/grow.70121</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I160"/>
+  <autoFilter ref="A1:K160"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/briefing.xlsx
+++ b/briefing.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All papers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All papers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Journal index" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All papers'!$A$1:$L$394</definedName>
@@ -639,7 +639,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>This briefing indexes 393 recent items across 42 journals (research articles plus a few book reviews / corrigenda, flagged in the Type column). Full abstracts were captured for 201; the remainder — mostly Elsevier (ScienceDirect) and Taylor &amp; Francis titles — are listed with complete title/author/DOI metadata, and each abstract is one click away via the DOI link (use your UW–Madison library access). Every paper lives on the 'All papers' tab, sortable and filterable by journal, date, and keyword.</t>
+          <t>This briefing indexes 393 recent items across 42 journals (research articles plus a few book reviews / corrigenda, flagged in the Type column). Full abstracts were captured for 312; the remainder — mostly Elsevier (ScienceDirect) and Taylor &amp; Francis titles — are listed with complete title/author/DOI metadata, and each abstract is one click away via the DOI link (use your UW–Madison library access). Every paper lives on the 'All papers' tab, sortable and filterable by journal, date, and keyword.</t>
         </is>
       </c>
     </row>
@@ -2064,11 +2064,15 @@
           <t>Climate &amp; green transition</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Carbon emissions; Monocentric spatial structure; The “borrowed-size” effect; Urban agglomeration</t>
+        </is>
+      </c>
       <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>The existing literature has yet to examine whether and how the top-down urban agglomeration policy influences the spillover effect for environmental benefits. Furthermore, it remains unexplored how a region's spatial structure shapes this policy-induced environmental spillover, creating a critical gap in understanding the role of spatial structure in sustainability-oriented regional planning. Based on a sample of 195 cities in China from 2004 to 2019, this paper examines whether the urban agglomeration policy affects the spillover effect of carbon emissions and how the spatial structure of urban agglomeration affects this relationship. Using a high-speed rail weighted Spatial Durbin Difference-in-Differences method, our results show that urban agglomeration policy enhances the “borrowed-size” effect in carbon reduction, exhibiting a carbon reduction spillover effect from leading cities to peripheral cities. Furthermore, we demonstrate that spatial structure plays an important role in shaping the patterns of the spillover effect in carbon emissions by showing that the “borrowed-size” effect is weakened in monocentric urban agglomerations. This study extends the “borrowed-size” framework into the environmental domain and establishes spatial structure as a key determinant of sustainability-oriented regional planning.</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
@@ -2114,11 +2118,15 @@
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>City size; Developing country; Manufacturing-to-service ratio</t>
+        </is>
+      </c>
       <c r="J21" s="14" t="inlineStr"/>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>This paper studies the spatial distribution of economic activities across urban hierarchy from an agglomeration perspective by constructing a new economic geography model with manufacturing and service sectors, two types of labor with perfect geographical mobility, and two regions. Holding the size of the sectors constant, the theoretical model shows that the larger city has a disproportionately larger concentration of the manufacturing sector compared to the smaller city. We test this prediction by estimating a spatial panel model with data from 285 Chinese cities over the period 2009–2019. We find a positive and statistically significant relationship between city size and manufacturing-to-service ratio. The findings shed new light on the importance of the manufacturing sector relative to the service sector for urban economic development. Despite the nationwide domination of services, larger cities are relatively specialized in manufacturing due to agglomeration economies.</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
@@ -2326,11 +2334,15 @@
           <t>Environment &amp; health; Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Cohort effects; Elderly longevity; GS2SLS; Public healthcare expenditure; Spatial inequality</t>
+        </is>
+      </c>
       <c r="J25" s="14" t="inlineStr"/>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>Population aging has intensified concerns regarding regional disparities in elderly longevity, even under universal healthcare systems. This study examines how socioeconomic conditions, healthcare capacity, demographic structure, and spatial interdependence influence life expectancy at age 65 (LE65) across Taiwan's 20 counties during 2010–2023. Using a county-level panel dataset and the Generalized Spatial Two-Stage Least Squares (GS2SLS) estimator, the analysis reveals that higher household disposable income and educational attainment are associated with longer life expectancy, whereas poverty and household healthcare-related financial burdens reduce longevity outcomes. Significant positive spillover effects are identified for educational attainment and public healthcare expenditure, indicating that regional longevity is shaped by both local and neighboring conditions. Elderly cohort composition also significantly influences longevity, highlighting the importance of distinguishing cohort effects from age-related effects. The results remain robust after excluding the COVID-19 period. The findings suggest that policies promoting healthy aging should prioritize poverty reduction, educational improvement, alleviation of healthcare-related financial burdens, and stronger interregional coordination in public health investment.</t>
         </is>
       </c>
       <c r="L25" s="15" t="inlineStr">
@@ -2376,11 +2388,15 @@
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr"/>
-      <c r="I26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>Catch-up; Creative destruction; Great recession; Malmquist index; Technical progress</t>
+        </is>
+      </c>
       <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>While most economists argue that demand-driven cyclical fluctuations do not affect long-run total factor productivity (TFP), Kaldorian and Schumpeterian approaches hold different and contrasting views. We analyse this issue computing a Malmquist TFP index for 267 NUTS2 European regions throughout 1995–2016. In particular, one of our main findings is that the Great Recession improved technical efficiency “catch-up” but reduced technical progress, leading to lower long-run TFP growth. In New Member States, catch-up effects were minimal, and the Great recession sharply reduced TFP growth. There is also a group of low growth regions whose TFP growth is relatively insensitive to downturns.</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
@@ -2430,11 +2446,15 @@
           <t>Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Employment subcenters; Endogenous amenities; Exogenous amenities; Household location; Monocentric model; spatial effects</t>
+        </is>
+      </c>
       <c r="J27" s="14" t="inlineStr"/>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>This study investigates from a theoretical point of view the spatial distribution of households by income within metropolitan areas, focusing on three key determinants: the polycentric structure of employment, the spatial distribution and accessibility of public amenities, and the presence of spatial interdependencies. Utilizing a novel and comprehensive dataset, we endogenously identify employment centers within the Barcelona Metropolitan Area (BMA). After incorporating this polycentric employment structure and the availability of public amenities—such as educational institutions, healthcare facilities, childcare centers, and transportation infrastructure—we extend conventional empirical models to account for spatial effects. These effects capture the externalities inherent in residential location choices, particularly the tendency of households to cluster with others of similar income levels. Employing spatial regression techniques, we empirically assess the influence of these factors on household location patterns. The results reveal that employment subcenters exert a significant effect on residential location decisions, that certain public amenities play a statistically significant role, and that neighborhood income level functions as endogenous amenities, further shaping the spatial distribution of income.</t>
         </is>
       </c>
       <c r="L27" s="15" t="inlineStr">
@@ -2484,11 +2504,15 @@
           <t>Migration &amp; labor; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Employment growth; Labour dynamics, long-distance commuting; Mining impacts; Regional economies; Resource curse</t>
+        </is>
+      </c>
       <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>This paper contributes to the resource curse and regional development literature by proposing a labour-market framework that contrasts positive spillover effects with crowding-out mechanisms and by examining how these processes shape employment and income trajectories across Australian regions. Using panel data for 566 local government areas between 2011 and 2021, combined with information on the location and status of mines across the country, we investigate the relationship between mining activity and regional development outcomes. Descriptive evidence indicates that, despite national growth in mining employment, many mining-hosting regions experienced declines in the number of resident miners, suggesting a growing spatial decoupling between mining production and local labour-market benefits. To evaluate the proposed framework, we estimate reduced-form growth models linking changes in mining employment to changes in non-mining employment and family income. Results indicate modest but positive average effects, suggesting that positive spillover mechanisms generally dominate, although crowding-out effects are more prevalent in some regions. Together, the conceptual framework and empirical findings help explain how labour-market dynamics shape subnational resource curse processes and underscore the need for place-based, evidence-informed development strategies.</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -3536,9 +3560,9 @@
       </c>
       <c r="I47" s="14" t="inlineStr"/>
       <c r="J47" s="14" t="inlineStr"/>
-      <c r="K47" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>We study the role of historic transportation in Urban Economics. First, we summarize the literature on transport cost before the Industrial Revolution and how they have influenced the shape and location of cities until today. We collect corresponding travel speed parameters from the literature for antiquity and the middle-ages for different transport modes that suggest limited to no improvements in travel time. We then discuss the sparse literature on transportation, sorting and agglomeration within the pre-industrial city. Lastly, we conclude by highlighting open questions and opportunities for future research.</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
@@ -3588,11 +3612,15 @@
           <t>Housing &amp; real estate; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Housing market; Neighborhood amenities; Private government; Urban regeneration</t>
+        </is>
+      </c>
       <c r="J48" s="11" t="inlineStr"/>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>This paper investigates how Business Improvement Districts (BIDs), business-led organizations financing local safety, cleanliness, and amenity improvements through mandatory commercial levies, affect residential property values in London. Using geocoded transactions from 2000 to 2019 and a staggered difference-in-differences estimator, we find that BID formation raises house prices by 5-6% within boundaries (roughly £26,000 per property), with positive spillovers up to 300 m. We also report that effects are stronger for better-funded BIDs. Following BID formation, neighborhoods see increased shares of one-family households and professionals, accompanied by lower unemployment rates, but reduced inflows of ethnic minority residents.</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
@@ -3700,11 +3728,15 @@
           <t>Transportation</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Difference-in-differences; Property values; Sport stadiums</t>
+        </is>
+      </c>
       <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>The construction of a sports stadium requires substantial resources and generates sweeping spillovers onto its surrounding community. This study explores the effects of 27 different stadium projects on local property values in Japan over almost three decades. The findings, which are supported by multiple difference-in-differences (DiD) estimators and found in multiple datasets, suggest that stadiums increase the value of nearby properties. Effects are strongest for the closest parcels, for parcels near stadiums designed for long-term use by professional teams (as opposed to large athletic stadiums primarily built for one-off events), and for parcels near stadiums in relatively less urban areas. Lastly, we find that increased tax revenue only partially offsets the costs of these projects. This research advances the literature by comprehensively studying a novel setting using modern DiD techniques and high-quality data, offering new insights for urban planners and policymakers considering future sports facility investments.</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr">
@@ -3804,11 +3836,15 @@
           <t>Transportation</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Inter- and intra-city transportation; Urban growth</t>
+        </is>
+      </c>
       <c r="J52" s="11" t="inlineStr"/>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>The literature assessing the effects of transportation infrastructure on how people and economic activity distribute themselves across a system of cities has three main parts. The theoretical literature makes robust predictions about how transportation infrastructure affects the internal structure of cities, but for systems of cities, theory does not let us rule much out. The city-level empirical literature establishes that improved urban transportation infrastructure causes suburban migration, but has only a small impact on city population. This literature is less helpful for understanding the effects of transportation infrastructure on the way people are distributed across a system of cities, but has made some progress. The small empirical literature looking at how transportation infrastructure affects systems of cities using cross-country data remains underdeveloped and is inconclusive.</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
@@ -3904,11 +3940,15 @@
           <t>Transportation</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Land use; Urban transportation</t>
+        </is>
+      </c>
       <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>Transportation infrastructure is central to the operation of cities. A look at consumer expenditure and travel data shows the welfare gains available through higher travel speeds and shorter travel times. Classical land use theory, travel demand estimation, and quantitative spatial urban models all have their places as useful frameworks for conceptualizing and estimating the impacts of transport infrastructure on urban structure and welfare. However, well identified reduced form analysis is centrally important to keep researchers honest and our work accessible to a broad audience.</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
@@ -3958,11 +3998,15 @@
           <t>Transportation; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr"/>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Infrastructure; Opportunity; Rurality</t>
+        </is>
+      </c>
       <c r="J55" s="14" t="inlineStr"/>
-      <c r="K55" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>This paper estimates how Interstate highway construction affected the adult outcomes of individuals born into rural America using longitudinally linked microdata. While aggregate cross-sectional studies find mixed effects of highways on rural economies, we reveal substantial person-based benefits that persist even when individuals migrate. By instrumenting highway construction with the 1947 federal highway plan, we identify highway impacts on persons born into rural America by comparing birth counties which happened to fall between metropolitan transportation hubs on the planned highway grid to those that did not. Using Social Security records linked to Census data for cohorts born 1935–1955, we find that highways benefited those born into rural America, increasing income by 4.4% ($1960), reducing unemployment by 3%, and raising college completion by 8%. Highways also shifted the industrial composition of rural Americans from agriculture to services and enabled strategic out-migration to urban areas and along highways. Further heterogeneity analyses by industry and migration choice show evidence that agricultural workers benefited by out-migration, while non-agricultural workers gained from improved local labor markets. Importantly, benefits accrued to both those who stayed and those who migrated out, suggesting highways improved local opportunities in addition to facilitating migration to opportunities. Comparison with cross-sectional data suggests that much of the county-level income gains reflect direct benefits to rural-born individuals. These findings demonstrate that infrastructure investments generate lasting labor market and human capital gains, which were not visible in conventional cross-sectional analyses.</t>
         </is>
       </c>
       <c r="L55" s="15" t="inlineStr">
@@ -4282,11 +4326,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr"/>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>Local taxation; machine learning; municipalities</t>
+        </is>
+      </c>
       <c r="J61" s="14" t="inlineStr"/>
-      <c r="K61" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>This study investigates whether local taxation decisions can be reliably predicted using machine learning (ML), focusing on the personal income tax sur charge set by Italian municipalities. We evaluate the predictive performance of ML models and identify key determinants of tax-setting behaviour. Results show that municipal tax choices follow systematic and predictable patterns driven by demographic, fiscal, socio-economic and institutional factors. A North–South comparison reveals stronger predictive accuracy in Southern regions, suggesting that tax increases are more closely linked to fiscal constraints than to discretionary political choices. Our findings highlight the usefulness of ML for understanding and supporting local fiscal planning.</t>
         </is>
       </c>
       <c r="L61" s="15" t="inlineStr">
@@ -4336,11 +4384,15 @@
           <t>AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Artificial intelligence; artificial intelligence (AI) innovation and adoption; digital transition; occupational exposure; regional economies in the European Union; territorial inequality</t>
+        </is>
+      </c>
       <c r="J62" s="11" t="inlineStr"/>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K62" s="11" t="inlineStr">
+        <is>
+          <t>This paper maps the geography of artificial intelligence (AI) innovation, exposure and use across European Union (EU) NUTS-2 regions using six complementary indicators. Findings reveal a spatial paradox: while AI exposure and worker-level use are relatively widespread, innovation and firm-level adoption remain concentrated in high gross domestic product (GDP), human capital-intensive hubs. A persistent implementation gap separates structural exposure from productive use, driven by institutional, organisational and capability-related frictions. Income and human capital are strongly associated with AI activity, while trade openness shows a negative relationship. Results point to the need for place-sensitive policies combining support for leading regions with targeted capability-building in lagging ones.</t>
         </is>
       </c>
       <c r="L62" s="12" t="inlineStr">
@@ -4386,11 +4438,15 @@
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr"/>
-      <c r="I63" s="14" t="inlineStr"/>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>border permeability; Borders; cross-border mobility; Europe; functional cross-border regions</t>
+        </is>
+      </c>
       <c r="J63" s="14" t="inlineStr"/>
-      <c r="K63" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>This paper presents a long-term comparative assessment of border permeability across Europe at 10-year intervals between 1960 and 2020. Using a novel 10-point typology of border regimes, it traces spatio-temporal changes in border openness and their relation to the structural potential of cross-border mobility in adjacent regions, operationalised through demographic mass, economic attractiveness and other structural determinants. The results reveal evolving patterns of cross-border mobility potential, where permeability conditions enable the emergence of functional cross-border regions over time.</t>
         </is>
       </c>
       <c r="L63" s="15" t="inlineStr">
@@ -4436,11 +4492,15 @@
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr"/>
-      <c r="I64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Cross-border region; functional region; media; newspaper</t>
+        </is>
+      </c>
       <c r="J64" s="11" t="inlineStr"/>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>Administrative borders rarely match those of functional cross-border regions (CBRs). The mismatch hampers the study of CBRs. Here a novel media-based indicator is proposed for studying functional CBRs. The indicator is based on the similarity of topics, tone and geographical focus of articles in newspapers on adjacent sides of a border. The feasibility of the indicator was tested with three US–Canadian cases. The indicator aligns with tangible cross-border flow data (travellers and goods) proving its potential worth as a new people-centric tool for investigating functional CBRs. The metric can withstand abrupt crisis (such as the COVID-19 pandemic) in border permeability.</t>
         </is>
       </c>
       <c r="L64" s="12" t="inlineStr">
@@ -4490,11 +4550,15 @@
           <t>Natural resources &amp; conservation; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I65" s="14" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>complex adaptive system; Entrepreneurial ecosystem; path dependence; social network analysis; sub-ecosystem</t>
+        </is>
+      </c>
       <c r="J65" s="14" t="inlineStr"/>
-      <c r="K65" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K65" s="14" t="inlineStr">
+        <is>
+          <t>This study enriches entrepreneurial ecosystem (EE) theorisation by integrating complex adaptive systems (CAS) theory with social network analysis (SNA) to address a key gap: the conceptual and empirical understanding of entrepreneurial sub-ecosystems and their relational dynamics. Focusing on the Sherbrooke EE in Canada, the study identifies three main sub-ecosystems: academic, business and entrepreneurial support. SNA highlights the centrality of the University of Sherbrooke, the pivotal brokerage role of the entrepreneurial support sub-ecosystem and differentiated degrees of external openness. These findings clarify how anchoring, intermediation, and openness structure EE dynamics and offer actionable insights for policymakers and ecosystem stakeholders.</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
@@ -4544,11 +4608,15 @@
           <t>Housing &amp; real estate</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Mexico City; short-term rentals; Transnational gentrification</t>
+        </is>
+      </c>
       <c r="J66" s="11" t="inlineStr"/>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>This paper contributes to a growing body of scholarly literature on the regulation and impact of short-term rentals in the Global South more broadly, and Latin America more specifically, by examining the phenomenon’s presence in Mexico City, one of Latin America’s largest cities. Building on the author’s prior research, it offers a case study on the rise of Airbnb in Mexico City, an issue which is growingly salient at the local level in the wake of rapid gentrification processes and a growing protest movement. Via a mixed-methods approach that combines tracing policy histories, quantitative and geospatial analysis, and semi-structured interviews, the article seeks to understand how the rise of short-term rentals in Mexico City is impacting residents’ everyday lives and transforming the city’s socio-spatial dynamics by examining three key issues: how the regulatory framework on the matter has evolved; what spatial factors correlate to its presence; and how its impact is felt by local residents. Findings reveal a highly unregulated environment where the platform is dominated by private actors and significantly tied to increased real estate development and new-build gentrification, and in which residents are increasingly concerned by the platform’s encroachment on their neighbourhoods.</t>
         </is>
       </c>
       <c r="L66" s="12" t="inlineStr">
@@ -4594,11 +4662,15 @@
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr"/>
-      <c r="I67" s="14" t="inlineStr"/>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>regional dynamic capabilities; regional value capture; Social business; value co-creation; value co-destruction</t>
+        </is>
+      </c>
       <c r="J67" s="14" t="inlineStr"/>
-      <c r="K67" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>The contribution of social businesses to regional sustainability has garnered increasing prominence in the regional studies literature. However, there is a lack of research on how social businesses can contribute to sustainable value capture by enhancing regional dynamic capability. By adopting the theoretical lens of dynamic capabilities, this paper draws on data from Bangladesh and Greece and establishes that sustainable regional value capture is achieved through the mutual shaping of regional and firm-level dynamic capabilities, augmented within regional ecosystems. Social businesses can optimise sustainable regional value capture by leveraging four drivers and attributes: collaboration, agility, regulation and entrepreneurial leadership.</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
@@ -4648,11 +4720,15 @@
           <t>Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>decomposition; Disability employment gap; local labour markets; spatial inequalities</t>
+        </is>
+      </c>
       <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>Disabled people fare particularly badly when living in areas that are economically and socially disadvantaged; they therefore have the most to gain from distributing national prosperity more equally. The disability employment gap in Britain (2014–19) was 31 percentage points (pp), but ranged from 17 pp to 43 pp locally. Using novel techniques to decompose spatial variation in the gap into ‘people’ and ‘place’ effects, we find that the key drivers are local population characteristics and economic structure, including the nature of labour demand and the industry composition of the local area. Spatial variation in healthcare, social capital, employer disability policies and the stringency of welfare provision do not explain the gap. The importance of place effects suggests that locally adapted policies to narrow the gap may be more effective than a one-size-fits-all approach. In turn, this requires sufficient capacity at the local level in terms of power, resource and expertise.</t>
         </is>
       </c>
       <c r="L68" s="12" t="inlineStr">
@@ -4702,11 +4778,15 @@
           <t>Climate &amp; green transition; Place-based policy &amp; inequality; Transportation</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr"/>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>grand challenges; Industrial decarbonisation; micro-missions; mission-oriented innovation; orchestration; place-based policy</t>
+        </is>
+      </c>
       <c r="J69" s="14" t="inlineStr"/>
-      <c r="K69" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K69" s="14" t="inlineStr">
+        <is>
+          <t>Climate change has led governments to adopt mission-oriented policies targeting net-zero greenhouse gas emissions. Heavy industry accounts for almost one-sixth of global emissions, making industrial decarbonisation central to this agenda. Though emissions impacts are global, decarbonisation unfolds locally. Yet how place-based micro-missions–small-scale experimental initiatives targeting concrete, localised challenges–are orchestrated in practice remains poorly understood. Examining Shoreham Port, an English industrial cluster in West Sussex, we show how local actors coordinate multi-scalar governance through spatially embedded micro-missions, demonstrating that their coordinated orchestration is essential for place-based industrial transformation, advancing mission-oriented innovation theory by establishing orchestration as a constitutive governance capacity and clarifying how grand challenges can be effectively addressed in local contexts.</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
@@ -4756,11 +4836,15 @@
           <t>Place-based policy &amp; inequality; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>civic capital; collaborative governance; place-based development policy; Smart Specialisation; Transformative innovation policy</t>
+        </is>
+      </c>
       <c r="J70" s="11" t="inlineStr"/>
-      <c r="K70" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>This article examines how regional and local governance arrangements shape the implementation of transformative innovation policy. While national and supra-national jurisdictions lead in designing policies, success depends on the quality of governance at the regional scale. It argues that collaborative governance arrangements, underpinned by civic capital, are critical for reconciling supra-national and national policy directions with bottom-up, place-based processes. Using a comparative analysis of Biden-era place-based policy in the United States and Smart Specialisation Strategies in the European Union, it shows that governance is constitutive of policy effectiveness, with implications for balancing innovation, competitiveness and equity.</t>
         </is>
       </c>
       <c r="L70" s="12" t="inlineStr">
@@ -4810,11 +4894,15 @@
           <t>Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I71" s="14" t="inlineStr"/>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>economic contribution; geographical differentials; Skilled labour; urban amenities</t>
+        </is>
+      </c>
       <c r="J71" s="14" t="inlineStr"/>
-      <c r="K71" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
+          <t>This study challenges the assumption of a homogeneous economic contribution of skilled labour. Extending amenity theory, it examines how urban amenities influence the geography of skilled labour’s economic contribution in China. We reveal that skilled labour’s economic contribution exhibits substantial fluctuations across cities and over time. Various urban amenities play heterogeneous roles in this process. Consumption amenities boost skilled labour’s economic contribution, whereas natural and public service amenities show secondary or institutionally constrained effects. Wages and consumption amenities function as substitutes in shaping this contribution. Coordinating wage incentives and consumption amenities is key to unlocking the talent dividend.</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
@@ -4864,11 +4952,15 @@
           <t>Migration &amp; labor; AI &amp; digital economy; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>artificial intelligence (AI) skills; ChatGPT; creativity; occupational labour market areas; Skill demand</t>
+        </is>
+      </c>
       <c r="J72" s="11" t="inlineStr"/>
-      <c r="K72" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>Drawing on over 182 million UK job postings from January 2017 to November 2025, we investigate how the association between demand for creativity and artificial intelligence (AI) skills evolves across UK occupational labour market areas following ChatGPT’s release. Our findings reveal a strengthened positive association between demand for these two skillsets post-ChatGPT, particularly in local labour market areas with a higher share of high-skilled roles and the presence of creative clusters. We conclude by emphasising the need for place-based interventions that reflect the differentiated demand- and supply-side priorities across regions in the era of generative AI.</t>
         </is>
       </c>
       <c r="L72" s="12" t="inlineStr">
@@ -4914,11 +5006,15 @@
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
-      <c r="I73" s="14" t="inlineStr"/>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>adaptation; Community-based social capital; fuzzy-set qualitative comparative analysis (fsQCA); place-based resilience; resistance</t>
+        </is>
+      </c>
       <c r="J73" s="14" t="inlineStr"/>
-      <c r="K73" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>Small and medium-sized enterprises (SMEs) do not operate in isolation; their resilience is shaped by the ties they build in the neighbourhoods in which they operate, making community-based social capital (CBSC) central to crisis response. Yet the ties that sustain firms during disruption may also limit the strategic reorientation needed for renewal. Drawing on data from 224 SMEs across six neighbourhoods in Isfahan, Iran, alongside interviews and secondary data, we use fuzzy-set qualitative comparative analysis (fsQCA) to examine how CBSC interacts with neighbourhood deprivation and density to shape resistance and adaptation. Our findings identify place-based configurations through which community ties either strengthen or constrain SME resilience across contexts.</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5022,11 +5118,15 @@
           <t>Housing &amp; real estate; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr"/>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>air pollution; Housing rents; spatial econometrics; subjective perceptions</t>
+        </is>
+      </c>
       <c r="J75" s="14" t="inlineStr"/>
-      <c r="K75" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>This study examines how objective and subjective measures of air quality affect housing rental prices in Medellín, Colombia. Building on Rosen’s hedonic framework, we incorporate an interaction between PM2.5 (particulate matter smaller than 2.5 micrometres) concentrations and residents’ perceptions of air quality to assess their joint influence on rents. Controlling for spatial dependence, the results show that subjective perceptions significantly amplify the negative effect of objective pollution on rental prices. We also document substantial spatial heterogeneity across communes. These findings highlight the importance of considering both measured pollution and perceived environmental quality when evaluating housing market responses to air pollution.</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
@@ -5076,11 +5176,15 @@
           <t>AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Adoption; Advanced digital technologies; Greater Manchester; Productivity; Skills</t>
+        </is>
+      </c>
       <c r="J76" s="11" t="inlineStr"/>
-      <c r="K76" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>This study provides firm-level evidence of the adoption of advanced digital technologies (DTs) in Greater Manchester. Examining the drivers and impact of six technologies, namely AI, Big Data, Cloud Computing, 3D-printing, IoT and Robotics. Using random forest models, a predictive machine learning technique, the findings suggest that a disaggregated approach is necessary to analyse and understand DT adoption. This paper argues that while firms’ contextual factors, which include size, age, and turnover, are important for successful digital transformation, firms must combine the adoption of DTs with relevant digital skills to allow companies to turn technological investments into productivity gains.</t>
         </is>
       </c>
       <c r="L76" s="12" t="inlineStr">
@@ -5234,11 +5338,15 @@
           <t>Transportation; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I79" s="14" t="inlineStr"/>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>instrumental variables; migration; Network analysis; violence</t>
+        </is>
+      </c>
       <c r="J79" s="14" t="inlineStr"/>
-      <c r="K79" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>This paper examines how violence impacts migration flows and the strength of migration networks across Mexico’s 2454 municipalities. Using a novel network algorithm and census data from 2005 to 2020, we detect structural changes in domestic and international migration beyond what net flows reveal. To identify causal effects, homicide rates are instrumented using variation in fuel prices and municipal distance to fuel pipelines, capturing exogenous shocks from large-scale fuel theft. Rising violence led to 1.12 million additional domestic emigrants, 50,200 fewer returnees from the United States, stronger emigration networks and reduced highway traffic linking violent areas to the rest of the country.</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
@@ -5284,11 +5392,15 @@
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr"/>
-      <c r="I80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Financial development; green economic efficiency; industry heterogeneity; spatial Durbin model</t>
+        </is>
+      </c>
       <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K80" s="11" t="inlineStr">
+        <is>
+          <t>This study investigates how financial development influences green economic efficiency within a spatial framework. We construct a green economic efficiency index using a spatio-temporal differentiation-based comprehensive evaluation method, and measure financial development through a super-efficiency slacks-based model (SBM) incorporating multiple indicators across the banking, insurance, securities and public finance sectors. Employing a spatial Durbin model (SDM), we examine both the direct effects and spatial spillovers of financial development across Chinese provinces from 2006 to 2020. Our findings indicate that financial development significantly enhances local green economic efficiency while also generating positive spillover effects in neighbouring regions. Further analyses reveal heterogeneity in these effects across regional divisions, financial sub-industries and levels of marketisation. These results offer valuable insights for designing regionally tailored financial and environmental policies to promote sustainable economic growth.</t>
         </is>
       </c>
       <c r="L80" s="12" t="inlineStr">
@@ -5338,11 +5450,15 @@
           <t>Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I81" s="14" t="inlineStr"/>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>Foreign aid; gender roles; spatial dependence; women in politics</t>
+        </is>
+      </c>
       <c r="J81" s="14" t="inlineStr"/>
-      <c r="K81" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K81" s="14" t="inlineStr">
+        <is>
+          <t>This paper examines how the gender composition of national parliaments affects foreign aid allocation in African countries. The findings indicate that female representation in parliament positively correlates with increasing aid directed mainly toward social sectors, which women legislators typically prioritise. Additionally, the study explores the role of spatial interdependence between neighbouring countries, revealing that the distribution of foreign aid is influenced not only by a country's parliamentary gender composition but also by gender representation in the parliaments of neighbouring countries. These results emphasise the importance of promoting gender parity in political institutions to achieve more effective and targeted aid allocation.</t>
         </is>
       </c>
       <c r="L81" s="15" t="inlineStr">
@@ -5388,11 +5504,15 @@
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr"/>
-      <c r="I82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>exposure; natural hazards; principal component analysis; Vulnerability</t>
+        </is>
+      </c>
       <c r="J82" s="11" t="inlineStr"/>
-      <c r="K82" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>Measuring vulnerability accurately is essential for strengthening resilience and supporting disaster risk reduction. While international frameworks such as the INFORM Risk Index and Risk Data Hub (RDH) Vulnerability Index provide valuable benchmarks, they often overlook local socio-economic and environmental specificities. This study advances vulnerability assessment by introducing a Regional Risk Index that integrates hazard, exposure and vulnerability through principal component analysis (PCA). By deriving data-driven weights, PCA reduces subjectivity and improves robustness compared to equal-weighted approaches. The index innovates conceptually by incorporating new variables that capture underexplored dimensions of resilience, including education quality (school abandonment), business vitality, accessibility to green spaces and public transport, and environmental stressors (tree loss, carbon emissions, air pollution). These additions extend existing methodologies by combining social, economic and ecological factors with hazard intensity and recurrence. Applied to Romania’s 42 NUTS 3 (nomenclature of territorial units for statistics, level 3) regions, the index reveals higher vulnerability in the northeast and southeast, and stronger resilience in areas such as Timiș, Ilfov and Tulcea. Robustness tests confirm the stability of results under alternative normalisation and weighting schemes. Overall, the framework offers a transferable tool for disaster risk analysis, contributing both conceptually and methodologically to vulnerability measurement and providing policymakers with more nuanced evidence for resilience planning.</t>
         </is>
       </c>
       <c r="L82" s="12" t="inlineStr">
@@ -5442,11 +5562,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I83" s="14" t="inlineStr"/>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>Fertility level; light data; spatial spillover effect; urbanisation</t>
+        </is>
+      </c>
       <c r="J83" s="14" t="inlineStr"/>
-      <c r="K83" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K83" s="14" t="inlineStr">
+        <is>
+          <t>China’s population growth rate has been consistently below the replacement level. Urbanisation is a key structural factor influencing changes in the fertility rate, so it is particularly urgent to clarify its mechanism of action. Existing studies often rely on conventional measures of urbanisation, which may not fully capture its spatial-economic intensity, and seldom examine its nonlinear dynamics or spatial spillover effects on fertility. To address these gaps, this study develops a spatio-temporal consistent and high-resolution urbanisation index using DMSP/OLS nighttime light data. Employing provincial panel data from 2004 to 2019 and applying both panel and spatial econometric models, this paper assesses the impact of urbanisation on fertility and its mechanisms. The results reveal an ‘inverted S-shaped’ relationship between urbanisation and the fertility rate. Specifically, a one-unit increase in the urbanisation index is associated with an average decline in the birth rate of approximately 0.033 percentage points. While the ‘two-child’ policy raised the fertility rate by about 0.007 percentage points, its effect is negatively moderated by urbanisation, each unit increase in urbanisation weakens the policy’s boost by roughly 0.004 percentage points. Spatial analysis further indicates that urbanisation’s suppressive effect spills over across regions, leading to an additional decrease of about 0.022 percentage points in neighbouring areas through spatial linkages. Additionally, factors such as female labour force participation, educational attainment, and social endowment insurance exhibit significant negative effects on fertility, whereas housing prices show a positive association. This study proposes to implement a regional collaborative policy system, transcending the single encouragement of childbirth and shifting towards a people-centred urbanisation path, emphasising balanced spatial development, and establishing a full life-cycle support system, thereby alleviating the constraint effect of urbanisation on the fertility level.</t>
         </is>
       </c>
       <c r="L83" s="15" t="inlineStr">
@@ -5596,11 +5720,15 @@
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr"/>
-      <c r="I86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>diversification; knowledge recombination; non-specialisations; Relatedness</t>
+        </is>
+      </c>
       <c r="J86" s="11" t="inlineStr"/>
-      <c r="K86" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>We propose a fundamental modification of the relatedness density index which considers the region’s whole technological structure, including linkages between technologies in which the region is specialised and those in which it is not. When carefully disentangled, relatedness to technologies in which the region is not ostensibly specialised is shown to boost diversification into new technologies, over and above the positive role of relatedness to technologies where a local specialisation does exist. This phenomenon is more pronounced in high-income regions, and provides the crucial insight that these more varied and complex local linkages help high productivity regions be so productive.</t>
         </is>
       </c>
       <c r="L86" s="12" t="inlineStr">
@@ -5646,11 +5774,15 @@
         </is>
       </c>
       <c r="H87" s="14" t="inlineStr"/>
-      <c r="I87" s="14" t="inlineStr"/>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>Digital economy; dynamic data envelopment analysis (DEA); regional innovation efficiency; two-stage DEA</t>
+        </is>
+      </c>
       <c r="J87" s="14" t="inlineStr"/>
-      <c r="K87" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K87" s="14" t="inlineStr">
+        <is>
+          <t>This study evaluates regional innovation efficiency in China under the digital economy using a nested parallel dynamic two-stage data envelopment analysis model. The model captures heterogeneous innovation actors, cross-stage linkages and intertemporal carry-over effects. Results for 30 Chinese regions from 2011 to 2020 show clear regional disparities. Efficiency generally follows a descending pattern from eastern to central, western and northeastern China. The central region performs relatively well in research and development (R&amp;D), while western regions lag in commercialisation. The findings highlight the importance of digitalisation in improving innovation performance and provide implications for regional innovation policy.</t>
         </is>
       </c>
       <c r="L87" s="15" t="inlineStr">
@@ -5700,11 +5832,15 @@
           <t>Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>density-aware index; inter- vs intra-type competition; location optimisation; Spatial competition; spatial HHI (Herfindahl–Hirschman); urban services; Voronoi tessellation</t>
+        </is>
+      </c>
       <c r="J88" s="11" t="inlineStr"/>
-      <c r="K88" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>We propose a density-aware spatial extension of the Herfindahl–Hirschman Index (sHHI) that incorporates population distribution and facility locations into measures of market concentration. The approach uses Voronoi catchments to allocate population to the nearest unit and derives concentration measures at both unit and type levels. We further introduce a nested decomposition that distinguishes inter-type competition from intra-type crowding. Using simulations, we examine the behaviour of the index under alternative spatial configurations of demand and supply. Empirical illustrations for Warsaw retail networks and public schools demonstrate how accounting for spatial heterogeneity alters concentration assessment and supports location-allocation decisions.</t>
         </is>
       </c>
       <c r="L88" s="12" t="inlineStr">
@@ -6024,15 +6160,19 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr"/>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Common European Asylum System; Crisis; Cross-border; European Cohesion; European Union; Integration; Resilience</t>
+        </is>
+      </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
           <t>Re-bordering Schengen? Explaining the spatial patterns of border control measures.</t>
         </is>
       </c>
-      <c r="K94" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>This article examines the temporary reintroduction of internal border controls within the Schengen area and its implications for spatial and political integration. While European cross-border integration has intensified over recent decades, recent crises, most notably the migration crisis and the COVID-19 pandemic, have exposed the vulnerability of a ‘borderless’ Europe. The study addresses two research questions: How can temporary border controls be categorised from thematic, spatial, and temporal perspectives? How can the observed spatial patterns be explained in relation to political dynamics and officially stated justifications? Empirically, the analysis draws on European Commission data covering the period 2006–2025 and examines border control measures across all Schengen border pairs. Border permeability is operationalised through the number of days with temporary controls and their formal reasons. The findings reveal a clear increase in the frequency of border controls over time, accompanied by strong spatial differentiation across Europe. Asymmetric patterns, where controls are introduced unilaterally or persist longer in one country, are more common than symmetric ones. These asymmetries are closely linked to uneven levels of policy integration, particularly in fields such as migration and health. Uncoordinated national responses to crises tend to produce spatially uneven re-bordering dynamics. These findings highlight the interdependence of policy domains and underline the limits of existing cross-border governance mechanisms. Overall, the study contributes to the literature by conceptualising border pairs as analytical units and by demonstrating how political asymmetries translate into spatial patterns, with significant implications for cross-border cooperation and European cohesion.</t>
         </is>
       </c>
       <c r="L94" s="12" t="inlineStr">
@@ -6082,15 +6222,19 @@
           <t>Natural resources &amp; conservation; Environment &amp; health</t>
         </is>
       </c>
-      <c r="I95" s="14" t="inlineStr"/>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>Election; Ganges River; Pollution Cleanup; Retrospective Voting</t>
+        </is>
+      </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
           <t>Elections and water pollution cleanup in the Ganges River in India.</t>
         </is>
       </c>
-      <c r="K95" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K95" s="14" t="inlineStr">
+        <is>
+          <t>We analyze the role of regular elections in ensuring water pollution cleanup in the Ganges river in a north Indian city. Our central result is that, in the absence of elections, politicians have no incentive to undertake pollution cleanup, leading to poor environmental outcomes. In contrast, when elections are present, retrospective voting by a representative voter, who re-elects incumbents only if observed cleanup exceeds a threshold, can discipline politicians. We show that this threshold strategy induces politicians to choose positive levels of pollution abatement in equilibrium. By explicitly characterizing the optimization problems of the politician, the voter, and the resulting equilibrium, we show that electoral accountability can serve as a powerful mechanism for improving water quality in the Ganges. Our findings highlight the critical role of democratic institutions in mitigating environmental externalities in developing country contexts.</t>
         </is>
       </c>
       <c r="L95" s="15" t="inlineStr">
@@ -6140,15 +6284,19 @@
           <t>Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr"/>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Gender Disparities; Macroeconomic factors; NEET; Spatial Panel Data; Urban–Rural Inequalities; Youth Unemployment</t>
+        </is>
+      </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
           <t>Analysing the macroeconomic determinants of NEET youth in Iran: A spatial panel data approach.</t>
         </is>
       </c>
-      <c r="K96" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>Youth disengagement is persistently high in Iran due to economic sanctions, rapid demographic growth, and uneven regional development. Macroeconomic factors determine youth not in Employment, Education, or Training (NEET) status, but spatial spillovers, gender, and urban-rural heterogeneity are rarely considered. This study examines the association between NEET rates and provincial-level GDP per capita, unemployment, inflation, government spending, urbanization, the Gini coefficient, vocational training programs (VET), gross value added in agriculture and services, industrial diversity, and human capital indicators across Iran's 30 provinces. This study differentiates between male, female, urban, and rural youth. We estimate spatial autoregression (SAR) models. Diagnostic tests (Moran's I, Pesaran CD, unit root, and cointegration) confirm spatial autocorrelation, cross-sectional dependence, and stationarity. The results show that a 1% increase in GDP per capita reduces NEET rates by approximately 0.18%, with stronger effects for males. Human capital and government spending also yield significant negative elasticities, particularly in rural provinces. Contrary to expectations, moderate inflation exhibits a small negative NEET elasticity (≈ −0.047), likely reflecting demand-pull labor opportunities. The SAR spatial lag (ρ = -0.334, P &lt; 0.05) reveals significant negative spillovers, where higher NEET in one province corresponds to lower NEET in its neighbors, suggesting labor market migration effects. To fully comprehend and overcome youth disengagement in Iran requires understanding spatial interdependencies and subgroup heterogeneities. NEET rates could be reduced by combining regionally tailored economic strategies, coordinated cross-provincial training initiatives, and targeted gender and rural-focused interventions.</t>
         </is>
       </c>
       <c r="L96" s="12" t="inlineStr">
@@ -6198,15 +6346,19 @@
           <t>Place-based policy &amp; inequality; Natural resources &amp; conservation</t>
         </is>
       </c>
-      <c r="I97" s="14" t="inlineStr"/>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>Cobb-Douglas production function; Ecosystem services; Growth accounting; Natural capital; Regional economic growth; Spatial regression models; Spatial spillovers</t>
+        </is>
+      </c>
       <c r="J97" s="14" t="inlineStr">
         <is>
           <t>Spillover effects of natural capital: Implications for regional development and cohesion policy in the European Union.</t>
         </is>
       </c>
-      <c r="K97" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K97" s="14" t="inlineStr">
+        <is>
+          <t>The relationship between natural capital and economic growth has gained considerable attention in recent years, particularly within the framework of sustainable development and European regional cohesion policy. Despite its recognised importance, natural capital remains largely absent from regional growth accounting frameworks, and its spatial spillover effects across regions are still insufficiently understood. This paper addresses both gaps by integrating natural capital- defined from an ecosystem services perspective- into an augmented Cobb-Douglas production function, and by applying a Spatial Durbin Model to assess the direct and indirect contributions of natural capital to economic output across EU NUTS2 regions. The results reveal a statistically significant positive association between natural capital and regional economic performance. A 10% increase in natural capital is associated with a 0.7% rise in gross value added, of which 0.4% is attributed to direct productive effects and 0.3% to spillovers from neighbouring regions. Spatial analysis further reveals marked territorial heterogeneity: above-average effects are concentrated in Central and Eastern Europe, while core Western European regions exhibit weaker spillover benefits, consistent with their lower structural dependence on ecosystem service flows. Although the estimates are associational rather than causal, the consistency of results across multiple model specifications supports their robustness. The study provides a proof of concept for integrating natural capital into regional development planning and demonstrates its relevance for advancing EU cohesion policy objectives. The findings also offer policy-relevant evidence to support future investments in biodiversity protection and ecosystem restoration, in line with the European Green Deal and the EU Biodiversity Strategy for 2030.</t>
         </is>
       </c>
       <c r="L97" s="15" t="inlineStr">
@@ -6256,15 +6408,19 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr"/>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Discourse analysis; European Commission; Resilience; Solidarity; Territorial policy; Ukraine</t>
+        </is>
+      </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
           <t>Resilience and solidarity in European Commission communication on the war in Ukraine: Instruments, territories and integration signals.</t>
         </is>
       </c>
-      <c r="K98" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>This article examines how the European Commission used four policy registers — resilience, solidarity, unity, and security — in relation to concrete instruments with territorial scope in its communication on Ukraine between March 2022 and June 2025. The study relies on 125 press releases and combines lexicometric analysis with qualitative coding. The results show that resilience was repeatedly associated with instruments such as the Ukraine Facility, macro-financial assistance, guarantees, REPowerEU energy measures, and the modernised DCFTA, with implications for municipalities, corridors, border regions, and infrastructure nodes. Solidarity and unity operated as signals of collective commitment and institutional proximity, while also being linked to obligations for specific places and levels of government. The discourse shifted from crisis containment to a more programmatic script with territorial anchors and a sequence running from fiscal protection to network reinforcement and market integration. Strengthening associations between “Ukraine” and belonging markers are interpreted as evidence that Commission communication helped frame integration as a gradual, policy-embedded process ahead of formal enlargement decisions. The article contributes a policy-relevant account of how official EU communication links registers, instruments, and territorial referents in the context of war, recovery, and integration.</t>
         </is>
       </c>
       <c r="L98" s="12" t="inlineStr">
@@ -6314,15 +6470,19 @@
           <t>Migration &amp; labor; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I99" s="14" t="inlineStr"/>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>Great Britain; Hybrid working; Internal migration; Regional disparities; Remote working; Rural development</t>
+        </is>
+      </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
           <t>Changing work/places: Remote work and the prospect of rural and coastal revival in Great Britain.</t>
         </is>
       </c>
-      <c r="K99" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K99" s="14" t="inlineStr">
+        <is>
+          <t>This paper investigates the geographical implications of the post-COVID surge in remote working across Great Britain, contributing to the literature a new conceptual distinction between fully remote work and ‘office-centric’ versus ‘remote-centric’ hybrid roles. Drawing on the UK Labour Force Survey 2022 and 2025, it analyses relationships between different modalities of remote work and residential patterns, internal migration and regional economic disparities. The analysis reveals distinct residential and migration profiles based on the degree of locational flexibility permitted by each form of remote work. Fully remote work is associated with inter-regional migration and a measurable ‘rural revival’. Remote-centric hybrid work (≥50% remote) shows limited expansion into rural locales. In contrast, office-centred hybrid work (&lt;50% remote) remains geographically indistinguishable from traditional on-site employment. Furthermore, remote working has not facilitated living in coastal areas. Across all modes of remote work, we find location patterns continue to mirror traditional core-periphery wage hierarchies, consolidating rather than mitigating existing regional disparities due to the persistent link to high wage areas. Because the most prevalent remote work arrangements – hybrid models – require proximity to the office, they are unlikely to drive a meaningful redistribution of human capital and wealth. Consequently, regional rebalancing strategies should focus on the specific infrastructure required to attract fully remote populations to peripheral regions or pursue alternative forms of structural investment.</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
@@ -6480,11 +6640,15 @@
           <t>AI &amp; digital economy; Place-based policy &amp; inequality; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I102" s="11" t="inlineStr"/>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Digitalization; Periphery; Remote work; Sustainable labour markets; Technical transformation</t>
+        </is>
+      </c>
       <c r="J102" s="11" t="inlineStr"/>
-      <c r="K102" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>This article explores the impact of technological transformation as one of the global megatrends in modern times. We focus on how new technologies, especially digitalization, have made it possible for people in peripheral places to work remotely. The focus is on the case municipalities in Iceland, especially Húsavík in in Norðurþing in northern Iceland, but also in a comparative context with remote municipalities in Norway, Sweden, and Åland. The empirical data used is from the Nordic project SUNREM (Sustainable Nordic Remote Labour Markets), which has been studying the impacts of megatrends on the sustainability of remote labour markets in four Nordic countries. Data is collected from in-depth interviews with stakeholders, policymakers, and ordinary citizens in seven selected cases in the four countries. The key research questions dealt with here are: What is the situation of remote work in selected cases in Nordic sparsely populated areas? What preconditions are needed for remote digital working? Has remote work made the labour market more sustainable? The main conclusions are that remote working exists in all of the Nordic cases investigated. The town of Húsavík in the municipality of Norðurþing in North Iceland, stands out with its well-developed remote work centres. There are clear signs that facilities where people can work and meet other remote workers are important. This enables broader recruitment into the labour market, since for example spouses can use this option, enabling them to move to more remote places. Remote work from people's homes has some disadvantages, as pointed out by various researchers, and therefore infrastructure for remote working contributes to making labour markets in the periphery more sustainable.</t>
         </is>
       </c>
       <c r="L102" s="12" t="inlineStr">
@@ -6642,11 +6806,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I105" s="14" t="inlineStr"/>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>Connectivity to public land; Land conservation; Non-market valuation; Policymaking; Public lands</t>
+        </is>
+      </c>
       <c r="J105" s="14" t="inlineStr"/>
-      <c r="K105" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K105" s="14" t="inlineStr">
+        <is>
+          <t>Conserving and restoring wildlife habitat is increasingly prioritized as economies focus on sustainable development. This study estimates the nonmarket value of the 7,000-acre Pilot Hill Recreation and Wildlife Habitat Management Area (WHMA) in southeastern Wyoming, which connects the City of Laramie to over 65,000 acres of national forest and state recreation lands. Using both a benefit transfer analysis and a contingent valuation survey of more than 1000 households, we evaluate willingness to pay (WTP) for the area's recreational and habitat attributes. The contingent valuation estimates show that the average WTP for this WHMA was $9.43 per household per visit, which aggregates to a regional economic benefit of $4.27 million per year. The benefit transfer approach yields a higher aggregate value of $16.76 million. Households also reported preferring the current WHMA plan with trails more than 2:1 over leaving the area as open space or using it for other economic development projects. Survey respondents indicate that the two most important attributes of this WHMA are protecting the area from residential development and connecting the adjacent city to recreation lands. Results suggest that the total cost of Pilot Hill, $10.5 million for the land purchase and $4.5 million for facilities and trails, represents an efficient and socially beneficial investment in conservation and recreation.</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
@@ -6750,11 +6918,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I107" s="14" t="inlineStr"/>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>Bath; Beppu; Hot-spring cities; Industrial cluster; Location quotient; Tourism and regional development; Vichy</t>
+        </is>
+      </c>
       <c r="J107" s="14" t="inlineStr"/>
-      <c r="K107" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K107" s="14" t="inlineStr">
+        <is>
+          <t>Hot-spring resources are abundant in Japan, yet they have not consistently generated broad-based regional prosperity. This study examines the conditions under which hot-spring cities can evolve from tourism-dependent destinations into higher-value urban service clusters. It compares Beppu (Japan) with Bath (UK) and Vichy (France), two benchmark spa cities included among the Great Spa Towns of Europe. Using a qualitative comparative case study supported by descriptive statistical evidence and location quotient profiles, the study shows that outcomes depend less on the volume of hot-spring resources than on institutional coordination, brand credibility, and the integration of wellness, heritage, healthcare, education, and related service industries. Bath and Vichy demonstrate how relatively limited hydrothermal resources can be converted into more durable and higher-value urban development through coordinated governance, long-stay demand, and clear quality signalling. By contrast, Beppu retains exceptional resource endowments and a strong domestic tourism base but remains dependent on volume-based tourism and shows weaker cross-sector orchestration. The study argues that the developmental potential of hot-spring cities should be understood as a place-based institutional and spatial process rather than an automatic consequence of resource abundance. Policy implications are presented for Beppu and for Japanese hot-spring cities generally.</t>
         </is>
       </c>
       <c r="L107" s="15" t="inlineStr">
@@ -6804,11 +6976,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I108" s="11" t="inlineStr"/>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Advanced regionalization; Decentralized cooperation; Institutional misalignment; Morocco; Multi-level governance; Regional development planning; Regional policy; Structured literature review; Territorial cohesion</t>
+        </is>
+      </c>
       <c r="J108" s="11" t="inlineStr"/>
-      <c r="K108" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>This article analyzes how the growing prominence of decentralized cooperation in Morocco interacts—or fails to interact—with the regional development planning instruments put in place under advanced regionalization. Drawing on contributions from the literatures on multi-level governance, development planning in the Global South, and territorial cohesion, it examines institutional gaps between the legal framework, planning tools, and the actual practices of territorial actors. Based on a structured documentary review combining a systematic search protocol, qualitative content analysis of legislative texts and twelve post-2015 regional development plans, and critical engagement with institutional reports, the study identifies three types of misalignments: a largely implicit and fragmented integration of decentralized cooperation projects into planning documents; uneven coordination between levels of government around external resources; and a persistent tension between stated territorial cohesion objectives and competitive logics of partnership capture by certain regions. The article argues that these gaps currently limit the capacity of decentralized cooperation to become a structuring lever for territorial convergence, while at the same time opening up prospects for institutional reforms. It contributes to debates in regional science and regional policy by showing how the design and coordination of planning instruments condition the ability of decentralized cooperation to support more inclusive regional development and territorial cohesion within the framework of advanced regionalization.</t>
         </is>
       </c>
       <c r="L108" s="12" t="inlineStr">
@@ -6858,11 +7034,15 @@
           <t>Place-based policy &amp; inequality; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I109" s="14" t="inlineStr"/>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>Counterurbanisation; Internal migration; Labour-market; Regional revitalization; Skill-relatedness; Structural change</t>
+        </is>
+      </c>
       <c r="J109" s="14" t="inlineStr"/>
-      <c r="K109" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
+          <t>Counterurban migration from metropolitan to smaller and rural regions has attracted renewed attention as a potential driver of regional revitalisation, yet its economic consequences remain poorly understood. This paper examines whether and how counterurban migrants contribute to structural change in non-metropolitan labour markets in Sweden. Using longitudinally matched employer–employee data for the period 2002–2019, we analyse how the activities of counterurban migrants relate to regional capability structures, compared with those of local incumbents across the urban hierarchy. Drawing on evolutionary measures of match, coherence, and structural change, the results show that counterurban migrants are more likely to enter activities that are less aligned with existing regional structures, particularly in small-town and rural regions, thereby introducing short-run labour market variation. However, this variation is not sustained. Over time, the activities in which migrants are employed become increasingly similar to those of incumbents, indicating that incoming skills and experiences are largely absorbed and filtered by existing regional capability structures. Overall, the findings suggest that counterurban migration contributes to gradual and context-dependent adjustment rather than serving as a general engine of regional diversification or transformation.</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
@@ -6912,11 +7092,15 @@
           <t>Place-based policy &amp; inequality; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr"/>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Economic Integration; Geopolitical Fragmentation; macroeconometric regional growth model, scenario analysis, regional disparities</t>
+        </is>
+      </c>
       <c r="J110" s="11" t="inlineStr"/>
-      <c r="K110" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K110" s="11" t="inlineStr">
+        <is>
+          <t>The current geopolitical landscape is highly fragmented and complex. It is characterized by rising tensions, shifting alliances, and by a largely uncertain global governance. This turbulence has dire consequences, especially at territorial level: it may contribute to widening interregional disparities. Prior ex ante assessments of the way these instabilities may find a solution suggest that a scenario with the EU deepening its internal integration, coupled with tighter global economic linkages (Integration scenario), would yield stronger economic performance, associated with smaller increases in cross-country disparities. By contrast, a scenario with looser internal integration within the EU, coupled with a fragmented global economy (Fragmentation scenario), would bring about comparatively larger within-country disparities, as slower economic expansion would keep internal inequality more contained. In this paper we propose a set of simulations aiming at disentangling the role played by pre-market, in-market, and post-market factors in driving regional inequalities. Simulations are based on the fifth generation of the MAcroeconometric Social Sectoral Territorial (MASST5) model. Our results suggest a mosaic of often contradictory effects. Should either state of the world depicted in the two scenarios prevail, our simulation results provide a detailed picture of the mechanisms driving overall results, thereby informing policy interventions aiming at minimizing the negative effects of specific development patterns.</t>
         </is>
       </c>
       <c r="L110" s="12" t="inlineStr">
@@ -7856,15 +8040,19 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I126" s="11" t="inlineStr"/>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>Accra (Ghana); Agbogbloshie; demolition; displacement; e-waste; spatial justice; urban informality</t>
+        </is>
+      </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
           <t>Reordering labour, value, and informality in Accra's e-waste economy: Circuits of persistence and precarity.</t>
         </is>
       </c>
-      <c r="K126" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>The demolition of the Agbogbloshie scrapyard in 2021 disrupted Accra’s central hub of electronic waste (e-waste) processing, displacing thousands of workers. This study examines how these informal economies persist and adapt to this territorial reordering through mobility, role-combination, and increased reliance on intermediaries. The reorganisation of these economies reveals the economic interdependence of formal and informal systems. We draw on interviews with informal and formal stakeholders, site observation, and relevant secondary materials to advance a 3-part framework for understanding demolition-driven displacement in e-waste economies. First, we show how informal practices persist through improvisation, sustaining material circulation under conditions of heightened precarity. Second, we demonstrate how demolition intensified new forms of mediated interdependence between informal labour and formal institutions, as access to markets, training, and safer practices became more gatekeepered. Third, we analyse the plural rationalities of value that structure e-waste economies, contrasting repair and reuse logics oriented to use-value with extraction logics prioritising exchange-value, and show how displacement reweighted the viability of these strategies under more uncertain spatial and market conditions. We argue for an inclusive governance framework that promotes environmental justice and supports more equitable integration of informal recyclers into formal systems. The study contributes to debates on urban informality, waste economies, and economic geography by theorising demolition as both a political technology of (re)ordering and an enclosure/dispossession mechanism. It also shows how displacement reorganises waste livelihoods while workers’ responses sustain circulation in more fragmented and precarious geographies.</t>
         </is>
       </c>
       <c r="L126" s="12" t="inlineStr">
@@ -7914,15 +8102,19 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I127" s="14" t="inlineStr"/>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>business and violence; extractive imperialism; gold mining; illicit economies; postcolonial political economy</t>
+        </is>
+      </c>
       <c r="J127" s="14" t="inlineStr">
         <is>
           <t>Gold, drugs, blood, and global capital: The new business imperialism and extractivism dynamics in postcolonial Peru.</t>
         </is>
       </c>
-      <c r="K127" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K127" s="14" t="inlineStr">
+        <is>
+          <t>This article examines how Peru’s gold economy, at the intersection of licit and illicit circuits, has become a conduit for contemporary forms of business imperialism. Against a backdrop of rising global demand for gold and sustained capital inflows, both formal mining operations and illegal gold extraction have expanded rapidly in Peru—facilitated by weak institutional oversight, transnational corporate networks, and growing links with drug trafficking circuits. Drawing from the frameworks of extractive imperialism, informal empire, and “slow violence,” the paper interrogates how multinational actors and global commodity chains reproduce historical patterns of asymmetrical accumulation, while externalizing environmental degradation, health crises, and systemic violence to the peripheral territories of Peru. Through a political economy lens grounded in Latin American structuralism and postcolonial theory, the study highlights the paradox of a country with persistent trade surpluses but chronic current account deficits—driven by low royalties, primary income outflows, and the enclave nature of its resource sector. By tracing the gold economy’s integration with coca-based illicit economies and its reliance on mercury-intensive extraction methods, the paper exposes how imperial dynamics of extraction have morphed, rather than disappeared, in the postcolonial era. Ultimately, this case repositions Peru’s contemporary gold boom within broader discussions on the business history of imperialism, suggesting that modern extractive regimes are less a rupture with colonial forms than their reconfiguration through financial globalization and deregulated capital flows.</t>
         </is>
       </c>
       <c r="L127" s="15" t="inlineStr">
@@ -8594,9 +8786,9 @@
       </c>
       <c r="I138" s="11" t="inlineStr"/>
       <c r="J138" s="11" t="inlineStr"/>
-      <c r="K138" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>Older people and rural places remain neglected subjects within the academic literature on food insecurity. In this paper, we investigate the relations between food insecurity and older people in rural England. We do this in a couple of ways. First, we utilise findings from an analysis of national survey data on food insecurity to examine levels of food insecurity and engagements with food assistance services amongst older people and those living in rural places. Second, we draw on materials from ethnographic research at a community food club in a rural district to explore older people's understandings of, and encounters with, food, food insecurity and community food provision. Three key findings emerge from our study. First, levels of food insecurity and engagements with food aid services are particularly low amongst older age groups and those living in rural places. Second, the relationship between older people and food insecurity in rural places is complex, bound up with cultures of denial, thriftiness, sharing and informal support. Third, community-based food provision can overcome some of the stigmatic aspects of food insecurity and food aid to provide meaningful social food experiences for older people in rural places. Food insecurity older people community food rural places UK.</t>
         </is>
       </c>
       <c r="L138" s="12" t="inlineStr">
@@ -8646,11 +8838,15 @@
           <t>Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I139" s="14" t="inlineStr"/>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>Care ethics; England; Rural gerontology; Rural idyll; Rural informal care; Scotland</t>
+        </is>
+      </c>
       <c r="J139" s="14" t="inlineStr"/>
-      <c r="K139" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K139" s="14" t="inlineStr">
+        <is>
+          <t>Despite the emergence of a flourishing body of work on care within geography in recent decades, research into rural informal care specifically remains relatively sparse. Addressing such a gap, this paper draws on 14 months of ethnographic fieldwork and semi-structured interviews with 36 participants to examine the moral expectations, practices, and limits of care among people aged 65 and over living in rural and remote locations in Scotland and England. Building on a feminist ethics of care, I develop the notion of a ‘rural ethic of care’, pointing to rural social intimacy, generalised reciprocity, and moral obligation as its perceived defining attributes. I also explore a series of escalating critiques put forward by participants of this ethic, including the distinct role neighbours, friends, and acquaintances played in the provision of care and lack of physically intimate care among these relations; struggles around asking for and offering care ethically as a result of ideals of independence; and the idea that social intimacy could itself impede practices of care. Two major sets of conclusions are drawn. First, I argue that rurality can both facilitate and detract from care, simultaneously supporting and challenging broader notions of rural spaces as ‘idyllic’. Second, I reflect on the implications of the findings for those ageing in rural places. While many older adults are providers of informal care to others in their community, the challenges to care posed by the rural setting are magnified amongst those ageing in a more vulnerable fashion.</t>
         </is>
       </c>
       <c r="L139" s="15" t="inlineStr">
@@ -8754,11 +8950,15 @@
           <t>Rural communities &amp; land; AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I141" s="14" t="inlineStr"/>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>Cultural construction; De-tagging the digital village; Digital technologies; Governance transformation</t>
+        </is>
+      </c>
       <c r="J141" s="14" t="inlineStr"/>
-      <c r="K141" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>Against the backdrop of accelerating global digitalization, digital village construction has emerged as a critical strategy for rural governance transformation across the Global South. Integrating digital technological infrastructure with rural community governance constitutes a fundamental challenge in digital village initiatives throughout the Global South. However, existing scholarship predominantly examines digital technology adoption through a techno-determinist lens, overlooking the interactive mechanisms between digital technology and local culture as well as grassroots agency. This study presents an investigation into a digital village initiative in an ordinary village in China's underdeveloped mountainous areas. Drawing on semi-structured interviews with diverse stakeholders, the research examines the sociotechnical process through which the synergy of digital technology embedding and cultural construction drives rural governance transformation. The study identifies a grassroots phenomenon termed “de-tagging the Digital Village”—a practice that dilutes the administrative label of “digital village” and repositions digital tools as a means for cultural preservation and governance. Key findings indicate that: 1) demand-oriented digital adaptation constitutes the foundation for technological effectiveness; 2) rebuilding villagers' agency consciousness is central to integrating digital technology into rural governance; and 3) “de-tagging the Digital Village,” as a manifestation of cultural self-awareness, reconstructs community identity and collective action through cultural construction, serving as a crucial mechanism through which the synergy of digital technology and cultural development enables rural governance transformation in mountainous areas. This study offers a critical alternative to the techno-determinist approaches prevalent in international scholarship, providing practical insights for advancing sustainable rural governance in the Global South.</t>
         </is>
       </c>
       <c r="L141" s="15" t="inlineStr">
@@ -8808,11 +9008,15 @@
           <t>Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I142" s="11" t="inlineStr"/>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Architecture preservation; Government-led tourism; Poverty alleviation; Rural change; Sustainable tourism</t>
+        </is>
+      </c>
       <c r="J142" s="11" t="inlineStr"/>
-      <c r="K142" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>While tourism-led rural development commonly brings economic benefits, it also typically alters the appearance of traditional villages. Thus, balancing the economic benefits from rural tourism development and the protection of traditional architecture has been difficult. Existing research on the impact of tourism development on vernacular architecture primarily focuses on cases of rural tourism development driven by commercial enterprises or local residents. Nonetheless, the spatial effects of rural tourism development within the government-led mode have been insufficiently explored. The current research addresses this gap by examining the impact of government-led tourism development on the architecture of the traditional village of Lijiashan, Shanxi Province, China. Employing a qualitative multi-method approach, encompassing field surveys and in-depth interviews, the study found that while the government-led model has successfully maintained the overall appearance of the village and improved the preservation of traditional Yaodong courtyards—cave-shaped folk houses—it also presents drawbacks. Standardized renovations and delays in repairing Yaodong courtyards have negative spatial impacts on the historical fabric of the village, including the damage of authenticity and the shift of original appearance. Therefore, this case highlights the complex interplay between rural development, preservation of vernacular architecture, and the specific challenges and opportunities presented by a government-led approach.</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
@@ -8862,11 +9066,15 @@
           <t>Agriculture &amp; food; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I143" s="14" t="inlineStr"/>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>Discourse analysis; Farmer; Food system; Land management; Livestock; Regenerative agriculture; Transformation</t>
+        </is>
+      </c>
       <c r="J143" s="14" t="inlineStr"/>
-      <c r="K143" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>Regenerative agriculture (RA) has been promoted as a transformative approach to sustainable land management, even as its meaning remains fluid, with livestock integration often considered as a central principle. Drawing on interviews with UK food system stakeholders, we apply a critical discourse analysis, revealing how livestock functions as a key organising reference point in the RA discourse, through three dominant, partially overlapping narratives of livestock's function: as labourers, landscape managers, and food security stewards. These narratives frame grazing livestock as central to land regeneration and as addressing environmental degradation, supporting rural economic resilience, and contributing to the production of all food. While conveying a strong sense of rural empowerment and offering farmers a form of moral and practical agency in navigating policy, market, and climate uncertainties, this discourse simultaneously works through and rearticulates long-standing hierarchies in land-use priorities, market relations and agricultural subsidy structures. At a time when climate and ecological debates increasingly foreground the need for land-use change, our analysis highlights how RA discourse gives relatively limited consideration to questions of livestock scale, despite livestock occupying a dominant proportion of UK agricultural land. In positioning livestock integration as an assumed component of regeneration, the discourse risks narrowing the scope for imagining more plural and differentiated transformative pathways, including approaches aligned with livestock reduction and stockfree regenerative systems.</t>
         </is>
       </c>
       <c r="L143" s="15" t="inlineStr">
@@ -8916,11 +9124,15 @@
           <t>Agriculture &amp; food; Migration &amp; labor; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I144" s="11" t="inlineStr"/>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Agri-food systems; Agricultural entrepreneurship; Gender norms; Informality; Women entrepreneurship; Women's entrepreneurial identity</t>
+        </is>
+      </c>
       <c r="J144" s="11" t="inlineStr"/>
-      <c r="K144" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>Women's entrepreneurship has played a vital role in the transition of agri-food systems. However, empirical research on how women's entrepreneurial identity influences or shapes their roles, especially within the informal agri-food sector, remains limited. While women's entrepreneurial identity in this sector has become a crucial capital for women who rely on agriculture for their livelihoods and household income, entrepreneurship theories have failed to adequately theorize or incorporate women's entrepreneurial identity in the informal sector. To fill this gap, we explore women entrepreneurs in Benin's informal agri-food sector through a qualitative exploratory study to understand how their entrepreneurial identity influences their roles in response to gender norms, institutional barriers, and market challenges as they navigate the socio-economic constraints that shape their identities. Based on the findings, we present an empirically grounded conceptual framework, the Informal Women Entrepreneurs' Identity (IWEI). The IWEI focuses on identity, grounded in the lived experiences of women entrepreneurs in Benin's informal agri-food sector, deepening our understanding of women's entrepreneurship not just as an economic activity but as a gendered process of self-recognition, navigation, and innovation within agri-food systems. By emphasizing the relevance of the IWEI, we contribute to scholarship on women's entrepreneurship, identity, and rural development within informal agri-food systems, offering both theoretical insights and policy implications for future research.</t>
         </is>
       </c>
       <c r="L144" s="12" t="inlineStr">
@@ -9186,11 +9398,15 @@
           <t>Transportation; AI &amp; digital economy; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I149" s="14" t="inlineStr"/>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>Agroecological transition; Local environmental change; Mediating mechanism; Spatial diffusion pattern; Technology adoption</t>
+        </is>
+      </c>
       <c r="J149" s="14" t="inlineStr"/>
-      <c r="K149" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K149" s="14" t="inlineStr">
+        <is>
+          <t>Green technology adoption and agricultural transition, as key elements of sustainable agricultural development, have long been central to academic inquiry. This paper investigates the spatial dynamics of agroecological transition and the mediating role of technology adoption within a three-dimensional conceptual framework of local environmental change, using Southern Jiangsu as a case study. The findings indicate that the transition follows an evolutionary diffusion pattern, radiating from the central urban areas to peripheral areas. Local environmental change indirectly shapes the transition by influencing technology adoption. In particular, a supportive policy framework and a robust industrial base promote the transition by facilitating adoption, whereas rising market demand currently hinders both. As peripheral areas emerge as key agricultural zones, local government initiatives and accumulated agrarian knowledge have effectively supported technology adoption and regional agricultural transition. Given China's current stage of socio-economic development, rising market demand may intensify market segmentation, competitive pressures, and income inequality, thereby hindering the transition. In response, government regulation can complement green production markets by fostering technology adoption and enhancing regional coordination.</t>
         </is>
       </c>
       <c r="L149" s="15" t="inlineStr">
@@ -9240,11 +9456,15 @@
           <t>Rural communities &amp; land; Agriculture &amp; food; Natural resources &amp; conservation</t>
         </is>
       </c>
-      <c r="I150" s="11" t="inlineStr"/>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>China; Farmland irrigation systems; Governance performance; Institutional rules; Panel data</t>
+        </is>
+      </c>
       <c r="J150" s="11" t="inlineStr"/>
-      <c r="K150" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K150" s="11" t="inlineStr">
+        <is>
+          <t>Farmland irrigation systems are essential for global food security and agricultural sustainability but face governance challenges due to their reliance on shared water resources. Following Ostrom's Institutional Analysis and Development Framework, we posit that institutional rules are instrumental to successful governance as they provide guidelines for the allocation and use of shared resources, establish mechanisms for monitoring and enforcement, and foster collective decision-making among stakeholders. This study draws on panel data from 160 villages across seven Chinese provinces in 2018 and 2023 to investigate the role of institutional rules in enhancing the governance performance of farmland irrigation systems. The analysis shows a clear link between the implemented institutional rules and the governance performance of farmland irrigation systems, with social trust playing a crucial mediating role in the action situation between the two. In addition, the influence of different institutional rules on the governance performance of irrigation systems is not uniform, with implementation and monitoring rules (including position, information, choice, and aggregation rules) exhibiting a more pronounced effect than others. In regions in the south and in food-cropping areas, the impact of institutional rules on the governance performance of farmland irrigation systems is particularly pronounced. The discussion reveals that the interactions among position-information, position-aggregation, and choice-aggregation significantly impact governance performance. This research improves understanding of the governance of farmland irrigation systems and offers valuable insights for policy-making and future studies on shared resource management.</t>
         </is>
       </c>
       <c r="L150" s="12" t="inlineStr">
@@ -10310,15 +10530,19 @@
           <t>AI &amp; digital economy; Migration &amp; labor; Rural communities &amp; land</t>
         </is>
       </c>
-      <c r="I169" s="14" t="inlineStr"/>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>digital empowerment; digital literacy; digital rural development; information utilization; non-agricultural entrepreneurship; regional inequality</t>
+        </is>
+      </c>
       <c r="J169" s="14" t="inlineStr">
         <is>
           <t>Digital Empowerment and Rural Transformation: How Digital Rural Development Shapes Non-Agricultural Entrepreneurship in China.</t>
         </is>
       </c>
-      <c r="K169" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K169" s="14" t="inlineStr">
+        <is>
+          <t>Digital rural development has emerged as a crucial strategy for narrowing spatial inequalities and fostering rural transformation. However, existing literature has predominantly focused on infrastructure accessibility, often overlooking how disparities in digital capabilities shape entrepreneurial outcomes. Drawing on digital empowerment theory, this study investigates how digital rural development influences farmers' non-agricultural entrepreneurship in China. Specifically, we integrate the County Digital Rural Development Index with microdata from the China Family Panel Studies (CFPS), utilizing empirical models to identify both the impact and the underlying mechanisms. The findings show that digital rural development significantly increases the likelihood of farmers engaging in non-agricultural entrepreneurship. This effect operates through two complementary capabilities: the development of digital literacy, and the cultivation of sophisticated skills for processing and applying information, which together enable farmers to effectively leverage digital resources. In addition, the non-agricultural entrepreneurial effect is more pronounced among middle-aged and older men in eastern China, highlighting the uneven distribution of digital dividends across regions and demographic groups. By focusing on individual capability formation, this study enriches rural entrepreneurship research, and provides insights for inclusive digital strategies and rural revitalization.</t>
         </is>
       </c>
       <c r="L169" s="15" t="inlineStr">
@@ -10422,11 +10646,15 @@
           <t>Markets, trade &amp; prices; Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I171" s="14" t="inlineStr"/>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>Bertrand–Nash equilibrium; buyer power; oligopsony; price discrimination; price markdown; procurement contracts</t>
+        </is>
+      </c>
       <c r="J171" s="14" t="inlineStr"/>
-      <c r="K171" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K171" s="14" t="inlineStr">
+        <is>
+          <t>We develop a spatially-explicit model of the U.S. beef packing industry to study key questions related to competition in an oligopsony setting. Cattle supplies are modeled at the county level, and packing plants' location, capacity, and ownership are taken as given. Packers procure negotiated cattle by competing in prices in each local (county) market, while accounting for transportation costs and pre-existing contracted supplies (alternative marketing arrangements). The model, calibrated to match observed 2022 data, is solved for the Bertrand–Nash equilibrium prices. The computed markdown in the price packers pay for fed cattle is decomposed into three components: the portion due to the inherent spatial oligopsony power; the amount due to an aspect of market concentration (firms owning multiple plants); and the component due to contracting. We find that markdowns are moderate, about $3.69/cwt or 2.6% of the fed cattle price, on average. About 54% of this markdown is due to the spatial configuration of plants, 40% is due to pre-contracted supplies, and only 6% of the markdown is attributed to multi-plant ownership by firms. Separately from markdowns, capacity constraints are found to lower fed cattle prices by 0.8% on average. Beyond the baseline, simulated counterfactual scenarios highlight specific policy-relevant questions. Markdowns are reasonably robust across counterfactuals, decreasing only modestly when plants operate independently or the use of contracting is limited. Across all counterfactual scenarios, cattle prices per se are most affected by tightening capacity constraints (as arising from a major plant closure or an upward swing in the cattle cycle).</t>
         </is>
       </c>
       <c r="L171" s="15" t="inlineStr">
@@ -10476,11 +10704,15 @@
           <t>Agriculture &amp; food; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I172" s="11" t="inlineStr"/>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>behavioral anomalies; discrete choice experiment; local and regional food systems; origin-identified markets; proactive and reactive preferences; public goods provision; risk preferences; social preferences</t>
+        </is>
+      </c>
       <c r="J172" s="11" t="inlineStr"/>
-      <c r="K172" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K172" s="11" t="inlineStr">
+        <is>
+          <t>To explain how some farmers' decisions may diverge from profit-maximization, we incorporate proactive social preferences for public goods in an expected utility framework, in addition to reactive risk preferences to uncertainty. We offer empirical evidence that proactive preferences influence farmers' decisions alongside reactive preferences by combining a discrete choice experiment, a dictator game, and the Eckle Grossman risk elicitation method. In our application, farmers choose between selling to origin-identified (OI) markets, which may provide public goods but involve uncertainty, and to wholesale markets, which offer certainty but do not provide public goods. Farmers are heterogeneous in their valuation of OI markets, but, on average, are willing to accept loss in profit to sell to OI markets. This willingness-to-accept is partially explained by farmers' social preferences, even when controlling for risk preferences. Our results show that when evaluating policies, failure to consider either social or risk preferences leads to considerably different outcomes. To increase sales through OI markets and support the perceived associated public goods, policymakers could leverage farmers' preferences for these markets with carefully designed incentives.</t>
         </is>
       </c>
       <c r="L172" s="12" t="inlineStr">
@@ -10584,11 +10816,15 @@
           <t>Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I174" s="11" t="inlineStr"/>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>data envelopment analysis; denitrification-decomposition (DNDC) model; network production technology; nitrogen use efficiency</t>
+        </is>
+      </c>
       <c r="J174" s="11" t="inlineStr"/>
-      <c r="K174" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K174" s="11" t="inlineStr">
+        <is>
+          <t>Both the rate and timing of crop fertilizer application play an important role in agricultural productivity. However, inefficient fertilizer use can significantly increase production costs, water pollution, and greenhouse gas emissions. To capture both the spatial heterogeneity and dynamic nature of this problem, we develop a multi-stage network production model, which links the sequential stages of crop growth within the overall crop production process. We use this framework to estimate nitrogen fertilizer application inefficiency and to determine the optimal rate and timing of fertilizer application. We apply this framework to wheat production at the field scale, using an agronomic simulation model calibrated to experimental data from Australia. Our results indicate that it is optimal to reduce the overall fertilizer application rate and to move away from the current practice of front-loading fertilizer in the initial stages of crop growth toward the intermediate stages. This can be achieved without compromising yields while also reducing nutrient losses.</t>
         </is>
       </c>
       <c r="L174" s="12" t="inlineStr">
@@ -10692,11 +10928,15 @@
           <t>Agriculture &amp; food; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I176" s="11" t="inlineStr"/>
+      <c r="I176" s="11" t="inlineStr">
+        <is>
+          <t>agricultural employment; Dust Bowl; intergenerational mobility; natural disasters; occupational choice; structural transformation</t>
+        </is>
+      </c>
       <c r="J176" s="11" t="inlineStr"/>
-      <c r="K176" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K176" s="11" t="inlineStr">
+        <is>
+          <t>This paper examines how a natural disaster, the Dust Bowl, shapes occupational choices in farm households across generations. Using full-count US census data, I find that young adult sons shift away from self-employed farming toward wage farm work and nonagricultural sectors after the Dust Bowl. Younger children with affected farming parents are more likely to leave agriculture and earn higher income. Migration and schooling serve as mechanisms, and New Deal relief spending mitigates the Dust Bowl's effects. Overall, the Dust Bowl accelerated occupational reallocation among younger children of farmers and contributed to US mid-20th century structural change.</t>
         </is>
       </c>
       <c r="L176" s="12" t="inlineStr">
@@ -10854,11 +11094,15 @@
           <t>Place-based policy &amp; inequality; Agriculture &amp; food; AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I179" s="14" t="inlineStr"/>
+      <c r="I179" s="14" t="inlineStr">
+        <is>
+          <t>E-commerce; income gaps; poverty alleviation; smallholder farmers</t>
+        </is>
+      </c>
       <c r="J179" s="14" t="inlineStr"/>
-      <c r="K179" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K179" s="14" t="inlineStr">
+        <is>
+          <t>Lifting smallholder farmers out of poverty depends largely on boosting their agricultural operating incomes, a persistent challenge despite numerous efforts. This study evaluates the impact of China's “E-Commerce into the Countryside” (ECC) program—the first and largest e-commerce initiative in the developing world—on both the level and distribution of smallholders' farm earnings. Employing a quasi-experimental design, we find that the ECC program significantly increases household per capita agricultural operating income. We show that this gain is driven by expanded market access through online sales, which facilitate income growth via three primary mechanisms: operational scale expansion, higher output prices, and a shift toward high-value-added crops. However, these benefits are unevenly distributed. The program also widens the income gap among smallholders, a disparity largely attributable to pre-existing differences in human, productive, and digital capital. Our findings highlight that e-commerce policies, while potent for income generation, require complementary measures to mitigate disparities that arise from heterogeneous initial endowments.</t>
         </is>
       </c>
       <c r="L179" s="15" t="inlineStr">
@@ -10962,11 +11206,15 @@
           <t>Place-based policy &amp; inequality; Transportation; Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I181" s="14" t="inlineStr"/>
+      <c r="I181" s="14" t="inlineStr">
+        <is>
+          <t>administrative data linkage; bivariate probit model; community food access; food assistance infrastructure; SNAP participation</t>
+        </is>
+      </c>
       <c r="J181" s="14" t="inlineStr"/>
-      <c r="K181" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K181" s="14" t="inlineStr">
+        <is>
+          <t>We link American Community Survey and SNAP records for 185,000 units with ground-sourced social food infrastructure data from FindFoodIL (Illinois Extension SNAP-Ed) to examine SNAP participation determinants among eligible units. Bivariate probit models reveal, beyond SNAP offices, quantity of social infrastructure is associated with participation: each additional senior program is associated with 5.89 percentage points (pp) higher participation probability, school/summer meal sites with 3.84 pp, and food pantries with 2.94 pp, potentially through trust, repeated contact, and navigation assistance. This first macro-level quantitative evidence shows policymakers that embedding enrollment assistance within institutions already serving eligible families—schools, senior centers, food pantries—is associated with reduced SNAP participation gaps. JEL Classification: I38, Q18, R23, R58.</t>
         </is>
       </c>
       <c r="L181" s="15" t="inlineStr">
@@ -11070,11 +11318,15 @@
           <t>Place-based policy &amp; inequality; Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I183" s="14" t="inlineStr"/>
+      <c r="I183" s="14" t="inlineStr">
+        <is>
+          <t>agricultural policy; agriculture; ARIS–REDS; high-yielding varieties; income mobility; mechanization; technological change</t>
+        </is>
+      </c>
       <c r="J183" s="14" t="inlineStr"/>
-      <c r="K183" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K183" s="14" t="inlineStr">
+        <is>
+          <t>We examine the relationship between farm size and productivity during India's Green Revolution, a period of rapid technological transformation. Using a unique panel of over 5000 Indian farm households that spans the Green Revolution (1971–1999), we show that the classic (linear) inverse farm size–productivity relationship gradually evolved into the U-shaped pattern observed today in India, with both small and large farms outperforming mid-sized ones, by the turn of the century. The roll-out of high-yielding varieties seems to have driven this change, and also driven the increased rate of hired labor use and mechanization on large farms (relative to mid-sized farms) that underpins that enhanced large farm productivity. Last, we show that the Green Revolution may have reduced the propensity of the smallest farms to grow into medium-sized farms over time.</t>
         </is>
       </c>
       <c r="L183" s="15" t="inlineStr">
@@ -11124,11 +11376,15 @@
           <t>Place-based policy &amp; inequality; Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I184" s="11" t="inlineStr"/>
+      <c r="I184" s="11" t="inlineStr">
+        <is>
+          <t>computable general equilibrium model; global competitiveness; livestock and meat trade; productivity improvements</t>
+        </is>
+      </c>
       <c r="J184" s="11" t="inlineStr"/>
-      <c r="K184" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K184" s="11" t="inlineStr">
+        <is>
+          <t>This study examines the competitiveness between Latin American and U.S. livestock and meat sectors. We employ a computable general equilibrium modeling framework to evaluate two scenarios: coordinated improvements in Latin American productivity, transport efficiency, and market access (Scenario I), and the minimum productivity gains required in the U.S. to regain its competitive position given improvements from Scenario I (Scenario II). Results highlight Latin America's transformative potential through advancements in technology, infrastructure, and trade, while emphasizing the importance of U.S. strategies to maintain market leadership. Policy implications focus on innovation, supply chain efficiency, and trade agreements to ensure sustained global competitiveness.</t>
         </is>
       </c>
       <c r="L184" s="12" t="inlineStr">
@@ -11286,11 +11542,15 @@
           <t>Place-based policy &amp; inequality; Agriculture &amp; food; Markets, trade &amp; prices</t>
         </is>
       </c>
-      <c r="I187" s="14" t="inlineStr"/>
+      <c r="I187" s="14" t="inlineStr">
+        <is>
+          <t>agricultural lending; banks; demand for agricultural loans</t>
+        </is>
+      </c>
       <c r="J187" s="14" t="inlineStr"/>
-      <c r="K187" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K187" s="14" t="inlineStr">
+        <is>
+          <t>This study examines the degree to which changes in non-real-estate agricultural loans at commercial banks are driven by changes in supply or demand. Our identification strategy exploits information provided by agricultural lending surveys conducted by three Federal Reserve Banks: Chicago, Kansas City, and Minneapolis. Building on recent studies of loan officer opinion surveys, we estimate the changes in agricultural loan supply and demand using an unbalanced panel of 1028 banks across the 2002–2021 period. The survey responses provide instruments for supply and demand changes to examine fluctuations in bank-level agricultural loan volumes obtained from Federal Financial Institutions Examinations Council quarterly “call reports.” We find that changes in the volume of non-real-estate farm loans at commercial banks are principally driven by changes in excess loan demand. These findings support a careful approach for policies aimed at boosting supply of agricultural credit. JEL Classification: Q14, G21, Q00.</t>
         </is>
       </c>
       <c r="L187" s="15" t="inlineStr">
@@ -11340,11 +11600,15 @@
           <t>Place-based policy &amp; inequality; Agriculture &amp; food</t>
         </is>
       </c>
-      <c r="I188" s="11" t="inlineStr"/>
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>actuarial science; cost cuts; crop insurance; fiscal responsibility; premium rate; subsidies; taxpayer savings</t>
+        </is>
+      </c>
       <c r="J188" s="11" t="inlineStr"/>
-      <c r="K188" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K188" s="11" t="inlineStr">
+        <is>
+          <t>Government-subsidized agricultural insurance plays a vital role in farm risk management but exposes taxpayers to substantial fiscal risk, intensifying debates over program efficiency and fiscal restraint. Using more than 3 million observations across 32 U.S. commodities from 2001 to 2024, this study evaluates how routine adjustments to rating parameters affect taxpayer costs. The results show that updating all ratemaking parameters reduces taxpayer expenditure by roughly 10% annually, while updating reference yields alone can generate savings of up to 15%. Although most states benefit, gains are uneven, underscoring the challenges of achieving actuarially and fiscally sound pricing.</t>
         </is>
       </c>
       <c r="L188" s="12" t="inlineStr">
@@ -11396,9 +11660,9 @@
       </c>
       <c r="I189" s="14" t="inlineStr"/>
       <c r="J189" s="14" t="inlineStr"/>
-      <c r="K189" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K189" s="14" t="inlineStr">
+        <is>
+          <t>Meeting the US Sustainable Aviation Fuel Grand Challenge target of 35 billion gal annually by 2050 will require an estimated 380 million–700 million dry tons of agricultural biomass feedstock. This study evaluates the implications of large-scale biomass production for land use, crop production, and market outcomes under mature market conditions. Results suggest that producing 476 million–843 million dry tons of biomass annually from agriculture would reduce cropland planted in corn, wheat, and soy by 8%–14%. However, convergence toward higher-quality cropland raises per-acre yields by 2%–9% relative to a business-as-usual baseline, limiting net production losses to 1%–3%. At the same time, farm market incomes increase by 20%–33%, whereas food price impacts remain below 1%. These findings indicate that substantial expansion of agricultural biomass for sustainable aviation fuel can be achieved with relatively modest impacts on food production and prices while also improving farm income.</t>
         </is>
       </c>
       <c r="L189" s="15" t="inlineStr">
@@ -12024,11 +12288,15 @@
           <t>Agriculture &amp; food; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I200" s="11" t="inlineStr"/>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>agri-environmental measures; coarsened exact matching; common agricultural policy; difference-in-differences</t>
+        </is>
+      </c>
       <c r="J200" s="11" t="inlineStr"/>
-      <c r="K200" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K200" s="11" t="inlineStr">
+        <is>
+          <t>This study examines the impact of agri-environmental measures on crop and livestock costs, labour inputs and income growth, using FADN farm-level data for the years 2006 and 2013, covering the 2007–2013 programming period in 22 EU countries. Employing a difference-in-differences model combined with coarsened exact matching, the results show that while some specific production costs rise on subsidized farms, these increases differ by region. Income growth and labour inputs are consistently higher across all regions. In particular, crop protection costs rise significantly in Western countries, while labour inputs do so in Southern and Eastern countries and at the EU level. Positive and significant effects on productivity outcomes are observed in the EU and Western EU countries.</t>
         </is>
       </c>
       <c r="L200" s="12" t="inlineStr">
@@ -12074,11 +12342,15 @@
           <t>Agriculture &amp; food; Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I201" s="14" t="inlineStr"/>
+      <c r="I201" s="14" t="inlineStr">
+        <is>
+          <t>3-nitrooxypropanol (3-NOP); climate change; discrete choice experiment; feed additive; greenhouse gases; information provision</t>
+        </is>
+      </c>
       <c r="J201" s="14" t="inlineStr"/>
-      <c r="K201" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K201" s="14" t="inlineStr">
+        <is>
+          <t>In a discrete choice experiment with 320 Swedish dairy farmers, we investigate preferences for methane-reducing feed additives, finding that higher environmental effectiveness and a farm advisor as the provider of accompanying information increase the probability of adoption. Additionally, an information treatment on methane reduction policy objectives lowers willingness to accept for the 30 per cent methane-reduction level of the feed additive. Latent class analysis shows that innovation-friendly farmers are more likely to be adopters, while those with stronger pro-animal-welfare attitudes are not. Finally, we predict feed additive market shares and discuss the economic implications for emissions reduction.</t>
         </is>
       </c>
       <c r="L201" s="15" t="inlineStr">
@@ -12124,11 +12396,15 @@
           <t>Agriculture &amp; food; Climate &amp; green transition</t>
         </is>
       </c>
-      <c r="I202" s="11" t="inlineStr"/>
+      <c r="I202" s="11" t="inlineStr">
+        <is>
+          <t>adaptation; dynamic panel; FADN; farm-level data; rainfall; seasonal data; temperature</t>
+        </is>
+      </c>
       <c r="J202" s="11" t="inlineStr"/>
-      <c r="K202" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K202" s="11" t="inlineStr">
+        <is>
+          <t>Understanding how seasonal weather anomalies brought by climate change impact on agricultural productivity is fundamental to food security. To allow proper site- and season-specific policy responses, micro-level assessments are needed. This study uses a panel data econometric approach to assess the impact of weather anomalies on Italian farms’ total factor productivity (TFP) over the period 2008–2020 using micro-level data. Estimates point to a complex TFP–weather relationship. Results confirm that seasonal weather anomalies have a negative effect on agricultural performance of different farm typologies. Effects tend to be larger the larger the weather anomalies.</t>
         </is>
       </c>
       <c r="L202" s="12" t="inlineStr">
@@ -12908,11 +13184,15 @@
           <t>Climate &amp; green transition; Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I216" s="11" t="inlineStr"/>
+      <c r="I216" s="11" t="inlineStr">
+        <is>
+          <t>carbon tax; carbon-free energy; climate policy acceptability; energy transition; FIP; subsidies to renewable energy</t>
+        </is>
+      </c>
       <c r="J216" s="11" t="inlineStr"/>
-      <c r="K216" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K216" s="11" t="inlineStr">
+        <is>
+          <t>Faced with political opposition to efficient carbon pricing, climate policy resorts to alternative instruments, which come with welfare and fiscal costs of acceptability. To assess these costs, this study examines second-best policies combining a constant carbon tax with subsidies to carbon-free electricity generation and storage. Using a stylized dynamic model of the energy transition featuring fossil and clean energy sources and a carbon budget, we show that the lower the carbon tax, the greater the carbon pricing gap, and the larger the subsidies required to meet the carbon budget. Overaccumulation of clean capital may be needed to crowd out fossil fuels. Calibration to the European energy market reveals costs of acceptability up to 2.6% of welfare and a budget shortfall equivalent to 56% of the present value of electricity consumption. This suggests that relying on green subsidies for the energy transition may be unwise.</t>
         </is>
       </c>
       <c r="L216" s="12" t="inlineStr">
@@ -12962,11 +13242,15 @@
           <t>Climate &amp; green transition; Rural communities &amp; land; Environment &amp; health</t>
         </is>
       </c>
-      <c r="I217" s="14" t="inlineStr"/>
+      <c r="I217" s="14" t="inlineStr">
+        <is>
+          <t>climate adaptation; heat; nutrition; rural households; temperature</t>
+        </is>
+      </c>
       <c r="J217" s="14" t="inlineStr"/>
-      <c r="K217" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K217" s="14" t="inlineStr">
+        <is>
+          <t>We examine the impact of temperature during the growing season on household diets in the subsequent year in rural India, a setting with a high prevalence of small family farms. High growing-season temperatures reduce crop yields, which would presumably reduce incomes and home-grown food for consumption. However, household adaptation could mitigate how the reductions in yields affect diets. We find that heat increases the number of strongly undernourished households in the subsequent year, as measured by the consumption of calories, iron, zinc, thiamine, and niacin. We also find suggestive evidence that households adapt to heat-induced losses of home-grown crops by purchasing more food.</t>
         </is>
       </c>
       <c r="L217" s="15" t="inlineStr">
@@ -13016,11 +13300,15 @@
           <t>Place-based policy &amp; inequality; Natural resources &amp; conservation</t>
         </is>
       </c>
-      <c r="I218" s="11" t="inlineStr"/>
+      <c r="I218" s="11" t="inlineStr">
+        <is>
+          <t>deforestation; fiscal federalism; Q23; Q50; social welfare loss; two-principal one-agent model</t>
+        </is>
+      </c>
       <c r="J218" s="11" t="inlineStr"/>
-      <c r="K218" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K218" s="11" t="inlineStr">
+        <is>
+          <t>Deforestation has been a major problem in China’s key northeastern forestry region, where the central government sets harvesting quotas, but local state forest enterprises have no incentives to comply with these limits. We develop a novel federalistic two-principal one-agent model to assess the social cost of state forest enterprise-driven deforestation, assuming that state managers make hidden decisions under the influence of provincial and central governments. We derive an expression of the social cost of hidden actions resulting in deforestation, and panel data are used to compute social losses and identify the main factors in these costs. We find the most important factors to be large natural forests and weak signals that the central forest administration has of harvesting. Our results collectively show that first best social cost minimizing outcomes are not possible unless policy reforms are undertaken.</t>
         </is>
       </c>
       <c r="L218" s="12" t="inlineStr">
@@ -13604,9 +13892,9 @@
       </c>
       <c r="I229" s="14" t="inlineStr"/>
       <c r="J229" s="14" t="inlineStr"/>
-      <c r="K229" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K229" s="14" t="inlineStr">
+        <is>
+          <t>Does heat increase the probability of missing work for formal-sector workers? We address this question by analyzing nearly three years of daily data on 274 employees across 86 locations of a large welding firm in India. We find that a 1°C rise in daily mean temperature increases the probability of missing work for workers without workplace climate control by 3.4% of the mean rate of absence. The same temperature increase decreases the probability of missing work by 2.5% relative to mean absenteeism for workers with climate control.</t>
         </is>
       </c>
       <c r="L229" s="15" t="inlineStr">
@@ -13820,9 +14108,9 @@
       </c>
       <c r="I233" s="14" t="inlineStr"/>
       <c r="J233" s="14" t="inlineStr"/>
-      <c r="K233" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K233" s="14" t="inlineStr">
+        <is>
+          <t>This meta-analysis of stated preference studies involving over 49,500 respondents quantifies the economic value of co-benefits from nature-based solutions (NBSs) that address climate risks. The results indicate that the willingness to pay for co-benefits increases with GDP per capita and decreases with NBS size. Recreational and aesthetic benefits, as well as NBSs developed in urban gray areas, are more valued than conservation and maintenance of current nature sites. The novel value transfer function can assist future research and policy makers in assessing the economic co-benefits of NBSs for climate risk based on the policy site characteristics.</t>
         </is>
       </c>
       <c r="L233" s="15" t="inlineStr">
@@ -14912,11 +15200,15 @@
           <t>Climate &amp; green transition</t>
         </is>
       </c>
-      <c r="I252" s="11" t="inlineStr"/>
+      <c r="I252" s="11" t="inlineStr">
+        <is>
+          <t>Analytical hierarchy process; Disaster risk management; Household vulnerability; Khyber Pakhtunkhwa; Multi-criteria decision-making; Pakistan; TOPSIS; Urban flooding</t>
+        </is>
+      </c>
       <c r="J252" s="11" t="inlineStr"/>
-      <c r="K252" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K252" s="11" t="inlineStr">
+        <is>
+          <t>Urban flooding is a significant natural disaster that affects human life and the economy. Assessing the household flood vulnerability of urban regions is gaining popularity worldwide. Researchers and policymakers are attempting to mitigate flood disaster risks by employing various methods to assess flood vulnerability. This study aimed to assess household flood vulnerability using multi-criteria decision-making (MCDM) in urban regions of Khyber Pakhtunkhwa (KP) Province, Pakistan. This study combines the analytical hierarchy process (AHP) method and the TOPSIS model along with sensitivity analysis to assess households' flood vulnerability through four key indicators (social, economic, infrastructural, and institutional) and their sub-indicators. The AHP assigned weights to the sub-indicators, while the TOPSIS technique gives ranks to vulnerability in the selected areas. The findings indicate that the Nowshera District ranks highest in household flood vulnerability, followed by the Peshawar and Mardan Districts. The combination of AHP and TOPSIS methodologies provides a systematic solution for evaluating household flood vulnerability, thereby demonstrating their effectiveness in urban flood risk assessment. The results reveal that social vulnerability is the primary indicator, and household age is the key sub-indicator of household flood vulnerability. The sensitivity analysis confirmed the reliability of the research results by identifying the most important sub-indicators. Based on the study's findings, the study provides several recommendations to policymakers for reducing flood risk in the selected region.</t>
         </is>
       </c>
       <c r="L252" s="12" t="inlineStr">
@@ -14966,11 +15258,15 @@
           <t>Place-based policy &amp; inequality; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I253" s="14" t="inlineStr"/>
+      <c r="I253" s="14" t="inlineStr">
+        <is>
+          <t>Depopulated area designation policy; Japan; Shrinking cities; Small and medium-sized cities; Staggered difference-in-differences</t>
+        </is>
+      </c>
       <c r="J253" s="14" t="inlineStr"/>
-      <c r="K253" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K253" s="14" t="inlineStr">
+        <is>
+          <t>Small and medium-sized cities (SMCs) are vital to sustaining balanced national development. However, many SMCs have experienced significant population decline in recent years. This study examines the effects of Japan's Depopulated-Area-Designation (DAD) policy on population and employment in SMCs. Using a staggered difference-in-differences approach across municipalities designated at different times, we estimate the policy's demographic and employment impacts over a 30-year post-designation horizon. The results indicate that the DAD policy was not associated with significant population change during the main analysis period. Specifically, the policy neither increased nor decreased population levels within the first 15 years after designation. However, approximately 20 years after designation, populations began to decline sharply. The trend in employed persons closely mirrored this population decline, while the number of employed residents showed no significant change even 20 years after designation. These findings suggest that analyses limited to employed residents would fail to capture the subsequent decline in both population and employed persons observed after 20 years. In conclusion, the results suggest that although the DAD policy produced no short- or medium-term effects, disadvantages may emerge in the long term. These findings are striking because they contradict the goals of the DAD policy. The results imply that policy designation alone cannot reverse—or even stabilize—the structural trends of population and economic decline in SMCs. Policymakers should therefore reconsider whether—and how—area-designation instruments can effectively address rural depopulation.</t>
         </is>
       </c>
       <c r="L253" s="15" t="inlineStr">
@@ -15020,11 +15316,15 @@
           <t>AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I254" s="11" t="inlineStr"/>
+      <c r="I254" s="11" t="inlineStr">
+        <is>
+          <t>Dematerialization; Digitalization; Net sustainability; Smart cities; Urban governance; Urban health and well-being</t>
+        </is>
+      </c>
       <c r="J254" s="11" t="inlineStr"/>
-      <c r="K254" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K254" s="11" t="inlineStr">
+        <is>
+          <t>Digitalization can reduce the material, energy and travel intensity of urban work, but its environmental dividend becomes urban sustainability only when it reaches residents as lived capability. This paper asks how cities can account for that transmission as urban functions shift from land- and building-anchored routines to code-, data- and platform-coordinated routines. We develop the Melting–Relief–Vitality (MRV) model as a source-based, provenance-coded diagnostic accounting framework. MRV links the structurality-to-digitality transition, the dematerialization-relief account generated by that transition, and two vitality gates representing cognitive and physical transmission conditions. We apply MRV to Montreal, London and Tokyo, 1900–2050, using a decadal panel assembled from public and administrative data, land-use and floorspace records, digital adoption series, health and mobility indicators, population series, documented harmonization and modelled reconstruction where direct series are unavailable. Under the reference calibration, all three cities record increasing dematerialization relief within MRV, but transmission diverges: Tokyo's later threshold crossing and lower accumulated exposure preserve the largest share, Montreal remains intermediate, and London records the strongest vitality discount. Per-capita outcomes show that aggregate environmental improvement does not automatically imply per-resident gain. We also test a post-2025 dividend-to-vitality compact directing 25% of incremental relief to vitality interventions. Stability checks across thresholds, exposure attenuation, recovery, compact strength and population denominators confirm the central transmission ordering and identify policy leverage. MRV makes the environmental-to-social transmission assumption explicit, auditable and operational for city-level policy, planning and governance.</t>
         </is>
       </c>
       <c r="L254" s="12" t="inlineStr">
@@ -15070,11 +15370,15 @@
         </is>
       </c>
       <c r="H255" s="14" t="inlineStr"/>
-      <c r="I255" s="14" t="inlineStr"/>
+      <c r="I255" s="14" t="inlineStr">
+        <is>
+          <t>Accessibility; Bike-sharing; Sustainable cities; Urban big data; Urban equity; X-minute cities</t>
+        </is>
+      </c>
       <c r="J255" s="14" t="inlineStr"/>
-      <c r="K255" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K255" s="14" t="inlineStr">
+        <is>
+          <t>In recent years, the X-minute city concept has been adopted worldwide as a strategy to reduce car dependency, improve urban energy-saving, as well as prioritise urban equity to ensure that cities are accessible and fair for all residents. However, most existing research assumes walking as the default travel mode in understanding X-minute cities, while ignoring the potential role of bike-sharing serving as a sustainable travel option in the X-minute city context. To fill this gap, this study compares the equity impact of bike-sharing in 36 cities in Zhejiang Province, China using a dual-scale (i.e., the grid and city scales) framework and multi-source big data. Specifically, we measure the X-minute cities in both walking and bike-sharing scenarios, then evaluate the equity impact from both horizontal and vertical perspectives. Our findings show that while bike-sharing reduces the overall population-weighted X from 19.42 to 16.76 min, it simultaneously worsens horizontal equity, with the Gini coefficient rising from 0.49 to 0.51 and the Theil index from 0.33 to 0.46. Vertical equity analysis shows that bike-sharing provides more benefits to females, but disadvantages seniors, and has a negligible equity impact on non-locals and youth. This study provides valuable insights for urban and transport planning, demonstrating that bike-sharing can support the development goals of the X-minute cities, but requires improved spatial layout to enhance urban inclusivity.</t>
         </is>
       </c>
       <c r="L255" s="15" t="inlineStr">
@@ -15120,11 +15424,15 @@
         </is>
       </c>
       <c r="H256" s="11" t="inlineStr"/>
-      <c r="I256" s="11" t="inlineStr"/>
+      <c r="I256" s="11" t="inlineStr">
+        <is>
+          <t>Location-based social media data; MomePy; Morphometric tessellation; Neighbourhood delimitation; Open urban data; Socio-functional clustering; Southern European cities; Urban morphology</t>
+        </is>
+      </c>
       <c r="J256" s="11" t="inlineStr"/>
-      <c r="K256" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K256" s="11" t="inlineStr">
+        <is>
+          <t>Understanding how urban form and activity interact to shape neighbourhood structure remains a central challenge in urban analysis. While morphological and activity-based approaches have been widely developed, their integration remains methodologically uneven, which can limit their ability to capture the socio-functional organisation of urban space. This paper proposes a reproducible computational workflow that integrates morphometric descriptors with location-based social media data to address two questions: to what extent does combining form and activity signals reveal socio-functional differentiation that morphology-only approaches cannot capture at comparable spatial resolution, and do the resulting units expose identifiable neighbourhood cores structured around concentrated activity? Using MomePy-based tessellations enriched with Foursquare-derived activity indexes within a unified clustering framework, the method is applied to 29 Southern European cities. The results show that this integration reveals consistent and recurrent patterns across cities: socio-functional differentiation within morphologically homogeneous fabrics, functional convergence across morphologically distinct areas, and the emergence of neighbourhood cores as centres of gravity within the resulting units. These patterns remain less visible when relying on morphology alone. The consistency of these findings across diverse urban contexts supports the robustness of the approach and its transferability as a basis for fine-grained urban diagnostics using open data, with direct relevance for neighbourhood-scale analysis and planning.</t>
         </is>
       </c>
       <c r="L256" s="12" t="inlineStr">
@@ -15170,11 +15478,15 @@
         </is>
       </c>
       <c r="H257" s="14" t="inlineStr"/>
-      <c r="I257" s="14" t="inlineStr"/>
+      <c r="I257" s="14" t="inlineStr">
+        <is>
+          <t>CLIP; Generative urban design; LLM; Performance evaluation; Urban texture</t>
+        </is>
+      </c>
       <c r="J257" s="14" t="inlineStr"/>
-      <c r="K257" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K257" s="14" t="inlineStr">
+        <is>
+          <t>The role of artificial intelligence (AI) in urban science has evolved from early-stage analytical support to active involvement in generative design, transforming how designers conceptualize and iterate spatial solutions. Benefitting from the rapid growth of generative urban design, urban designers can now quickly receive many design solutions, but selecting the best among numerous results remains challenging. In response, this study attempts to develop an intelligent method capable of measuring a key performance in design evaluation, i.e., the aesthetic performance of two-dimensional urban textures. Specifically, we first apply large language models (LLMs) to extract and refine key evaluative dimensions, providing a theoretical basis for aesthetic assessment. Four dimensions related to urban morphological aesthetic performance were selected based on classical urban theory: orderliness, richness, imaginability, and building density. Using urban texture data from OpenStreetMap and expert ratings collected through questionnaires, we built a training dataset of paired images and scores. The evaluation method was then developed through a multimodal approach via the Contrastive Language-Image Pre-Training (CLIP), which can identify numerical aesthetic performance of urban textures and has demonstrated accuracy comparable to expert evaluations. Moreover, using LLMs within a transformer-based architecture, the interactive interface provides textual feedback based on the evaluation results, improving interpretability and usability for designers. In short, this study contributes to generative urban design and quantitative urban morphology by providing a multi-model approach to measure morphological aesthetic performance.</t>
         </is>
       </c>
       <c r="L257" s="15" t="inlineStr">
@@ -15224,11 +15536,15 @@
           <t>Climate &amp; green transition</t>
         </is>
       </c>
-      <c r="I258" s="11" t="inlineStr"/>
+      <c r="I258" s="11" t="inlineStr">
+        <is>
+          <t>Climate resilience; Land allocation structure; Polycentric spatial structure; Sustainable Development Goals; Technological innovation; Transportation infrastructure</t>
+        </is>
+      </c>
       <c r="J258" s="11" t="inlineStr"/>
-      <c r="K258" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K258" s="11" t="inlineStr">
+        <is>
+          <t>Amidst global climate change and the intensification of local climate effects like the urban heat island, cities face increasingly severe climate risks. Optimizing urban spatial structure and enhancing urban climate resilience have become globally recognized priorities and are embedded in the Sustainable Development Goals (SDGs). This study employs panel data for 273 Chinese cities from 2010 to 2022 to systematically examine the impact of polycentric spatial structure (PSS) on urban climate resilience (CR) and explore its underlying mechanisms. The results show that: (1) PSS significantly enhances urban CR. Specifically, a one-unit increase in the degree of polycentricity is associated with an average 2.5% increase in urban CR. (2) Optimizing land allocation structure, improving transportation infrastructure, and promoting technological innovation are three key pathways through which PSS enhances CR. (3) The positive effect of PSS on CR is more pronounced in eastern regions, large cities, and non-resource-based cities. (4) Improving marketization level and informatization level can strengthen the positive effect of PSS on CR. These findings provide guidance for improving urban spatial structures tailored to local conditions and for enhancing urban resilience to climate change, thereby contributing to the achievement of SDG 13.</t>
         </is>
       </c>
       <c r="L258" s="12" t="inlineStr">
@@ -15278,11 +15594,15 @@
           <t>Housing &amp; real estate; Place-based policy &amp; inequality; Natural resources &amp; conservation</t>
         </is>
       </c>
-      <c r="I259" s="14" t="inlineStr"/>
+      <c r="I259" s="14" t="inlineStr">
+        <is>
+          <t>Ecosystem services; Environmental valuation; Hedonic pricing; Land value capture; Spatial econometrics; Urban inequality</t>
+        </is>
+      </c>
       <c r="J259" s="14" t="inlineStr"/>
-      <c r="K259" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K259" s="14" t="inlineStr">
+        <is>
+          <t>Urban green infrastructure generates substantial ecosystem services, yet the economic value of these benefits is often captured privately through housing markets rather than reinvested in public ecological provision. This paper addresses this gap by introducing Urban Green Credits (UGC), a planning-oriented framework that links ecological performance to fiscal instruments. We develop a parcel-level Index of Ecosystem Services (IES) integrating carbon sequestration, thermal regulation, ecological connectivity, and accessibility to green spaces. Using 5230 residential transactions in Porto, Portugal, we estimate the capitalisation of ecological performance into housing prices through hedonic, spatial econometric, instrumental variable, and difference-in-differences models. Results show that ecosystem services are consistently and significantly reflected in property values, with robust effects across specifications and identification strategies. Building on these estimates, we simulate the fiscal potential of UGC, demonstrating that even modest capture rates can generate meaningful revenues and support redistribution towards ecologically underserved areas. The findings contribute to bridging ecosystem service valuation and urban fiscal policy, advancing a framework that integrates environmental performance, land markets, and equity considerations. While conceptual and requiring contextual calibration, UGC provides a novel pathway for financing urban greening while addressing spatial inequalities.</t>
         </is>
       </c>
       <c r="L259" s="15" t="inlineStr">
@@ -15328,11 +15648,15 @@
         </is>
       </c>
       <c r="H260" s="11" t="inlineStr"/>
-      <c r="I260" s="11" t="inlineStr"/>
+      <c r="I260" s="11" t="inlineStr">
+        <is>
+          <t>Economic development; Land use planning; Local government; Logistics sprawl; Spatial imaginaries; Urban edge</t>
+        </is>
+      </c>
       <c r="J260" s="11" t="inlineStr"/>
-      <c r="K260" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K260" s="11" t="inlineStr">
+        <is>
+          <t>Due to the changing demands of global supply chains, the facilities and related infrastructures that support the movement of goods have shifted away from inner-city locations toward suburban and ex-urban sites with spaces suitable for the construction of large-footprint warehouses and distribution centres. This article explores the relationship between the demands of the global logistics industry and suburban local governments through a case study of a southeastern suburb in British Columbia's Lower Mainland, Canada. It traces municipal efforts to accommodate large-scale industrial users at the rural-suburban fringe. Through a qualitative approach including analysis of city planning documents, newspapers, real estate publications, Census data, and interviews with local planning officials, we analyze how the post-suburban spatial imaginaries of local officials are propelling industrial growth forward, calling into question not only the long-standing emphasis in the literature on residential growth as the driver of expansion of the suburban edge, but also how various types of sprawl may be perceived differently and thus subject to different planning treatments. The article reveals the deep intertwining of these previously rural communities and their economic futures with the global logistics industry and the need to more explicitly consider logistics development in local and regional planning.</t>
         </is>
       </c>
       <c r="L260" s="12" t="inlineStr">
@@ -15384,9 +15708,9 @@
       </c>
       <c r="I261" s="14" t="inlineStr"/>
       <c r="J261" s="14" t="inlineStr"/>
-      <c r="K261" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K261" s="14" t="inlineStr">
+        <is>
+          <t>Whether seaports function as engines of regional upgrading depends not only on how efficiently they operate, but also on how effectively port advantages are translated into port-industry-city (PIC) coordination. This study examines the link across 22 major ports in China’s five coastal port clusters over 2015–2023 by integrating a three-stage SBM-SFA-SBM model, entropy-weighted TOPSIS, a coupling coordination degree (CCD) model, and obstacle-degree diagnostics. The results show that environmental adjustment materially reshapes the port-efficiency landscape, indicating that unadjusted benchmarking partly captures external endowments rather than managerial capability. PIC coordination has generally improved, but the upgrading process is highly uneven across and within clusters, with persistent segmentation rather than uniform convergence. Obstacle diagnostics further reveal that industry-related constraints constitute the dominant common barrier, while the binding bottlenecks differ by region: the Bohai Rim and Yangtze River Delta are mainly constrained by weak industrial upgrading, openness, and port-related linkage; the Pearl River Delta and Southeast Coastal cluster face strong port-side efficiency bottlenecks; and the Southwest Coastal cluster is limited by city-side support and landward connectivity. By embedding environment-adjusted port efficiency into PIC coordination analysis, the study offers a more comparable and policy-relevant framework for diagnosing uneven coordinated upgrading in coastal port clusters.</t>
         </is>
       </c>
       <c r="L261" s="15" t="inlineStr">
@@ -15436,11 +15760,15 @@
           <t>Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I262" s="11" t="inlineStr"/>
+      <c r="I262" s="11" t="inlineStr">
+        <is>
+          <t>comparison; entrepreneurialism; global climate initiatives; Intermediaries; urban experimentation</t>
+        </is>
+      </c>
       <c r="J262" s="11" t="inlineStr"/>
-      <c r="K262" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K262" s="11" t="inlineStr">
+        <is>
+          <t>Practitioners implementing urban climate initiatives are frequently faced with the intermittent nature of urban projects and the short-termism of policy experiments. In this conjuncture, understanding how urban transformations are advanced necessitates grasping how small-scale efforts are carried forward or sustained despite these brief time horizons and a related condition of resource scarcity that urban bureaucracies also confront. To address this question, this article develops a figure we provisionally term the chainmaker. Building on literature that discusses the role of intermediaries in debates on entrepreneurial governance and urban experimentation, this heuristic captures the role of urban practitioners who build temporal chains, that is, who sustain ideas, projects or reforms across different initiatives and bureaucratic cycles in the long run. We draw on a comparative study that traced the functioning of these initiatives in four secondary cities in Mexico and India to explore two different dimensions of intermediation over time. This work of anchoring and sustaining small-scale policy efforts to effect lasting change reveals the challenges to creating continuity and effecting structural change and the different conditions of that work in the studied contexts.</t>
         </is>
       </c>
       <c r="L262" s="12" t="inlineStr">
@@ -15544,11 +15872,15 @@
           <t>Climate &amp; green transition; Place-based policy &amp; inequality</t>
         </is>
       </c>
-      <c r="I264" s="11" t="inlineStr"/>
+      <c r="I264" s="11" t="inlineStr">
+        <is>
+          <t>carbon accounting; carbon lock-in; circular economy; municipal climate action; renewable natural gas; waste-to-biofuel</t>
+        </is>
+      </c>
       <c r="J264" s="11" t="inlineStr"/>
-      <c r="K264" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K264" s="11" t="inlineStr">
+        <is>
+          <t>Waste-to-biofuel (WTB) programs have gained popularity as a municipal circular economy and an emissions reduction strategy. The upgrading of biofuels to renewable natural gas (RNG) has drawn particular interest, as RNG can displace conventional fossil fuels in any existing natural gas end use and be delivered through existing pipeline infrastructure. This article examines RNG produced at the City of Toronto’s waste facilities in partnership with Enbridge Distribution Inc. Toronto has framed its program as a strategy to ‘close the carbon loop’, recirculating waste as a new energy resource and, by extension, the carbon embodied in municipal waste. The article, first, examines the construction of the carbon loop policy narrative that draws from the technical work of emissions accounting. Second, it discusses how and why choices that shape energy systems are made as part of such programs. In Toronto, distributing through the Enbridge pipeline network has enabled the production of flexible environmental attributes that can be virtually assigned to a range of end uses and users. Understanding how policy narratives are constructed to describe municipal policy experimentation and situate municipal experiments within wider energy systems and energy system politics is critical to ensure experiments contribute to long-term net zero pathways.</t>
         </is>
       </c>
       <c r="L264" s="12" t="inlineStr">
@@ -15648,11 +15980,15 @@
           <t>Housing &amp; real estate; Migration &amp; labor</t>
         </is>
       </c>
-      <c r="I266" s="11" t="inlineStr"/>
+      <c r="I266" s="11" t="inlineStr">
+        <is>
+          <t>consumption and leisure economy; ecological civilization; extended urbanization; land and housing financialization; mountain peripheries; urban entrepreneurialism</t>
+        </is>
+      </c>
       <c r="J266" s="11" t="inlineStr"/>
-      <c r="K266" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K266" s="11" t="inlineStr">
+        <is>
+          <t>This article develops the concept of a territorial business model (TBM) to renew the analysis of the production of the urban built environment beyond established urban cores. Based on the case of Chongli, a site for the 2022 Beijing Winter Olympics, this article provides a double decentering of the ways in which a mountain region was urbanized within a context of State-led financialized green entrepreneurialism. We emphasize that, as a bet on future revenues from growth and by considering extra-economic purposes, the built environment questions territorial value creation and extraction. By reflecting on the impacts of the increasing circulation of individuals’ incomes on territorial development, we posit that territorial value creation refers to a system made up of export-, visitor- and household-based flows of revenues that circulate at varied and larger scales. Simultaneously, the built environment incorporates this territorial value and is transformed into financial assets through various circuits of finance and value extraction. The TBM extends the business model concept developed by post-neoliberal/colonial scholars that calls for decentering analysis away from the dominant variegated financialization of the built environment approach that was developed from Western contexts. It further decenters the analysis by addressing urbanization processes beyond large city centers.</t>
         </is>
       </c>
       <c r="L266" s="12" t="inlineStr">
@@ -15698,11 +16034,15 @@
         </is>
       </c>
       <c r="H267" s="14" t="inlineStr"/>
-      <c r="I267" s="14" t="inlineStr"/>
+      <c r="I267" s="14" t="inlineStr">
+        <is>
+          <t>adaptive use of university campuses; innovation-driven economies; partnerships; socialist land masters; town–gown relationships; university real estate practices</t>
+        </is>
+      </c>
       <c r="J267" s="14" t="inlineStr"/>
-      <c r="K267" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K267" s="14" t="inlineStr">
+        <is>
+          <t>Chinese universities are important but undertheorized players in the production of urban built environments. Most work focuses on purpose-built university towns, neglecting the redevelopment of underutilized downtown campuses. Therefore, this article considers how two publicly funded universities in Nanjing attempted to establish ‘innovation complexes’ in their older, poorly maintained urban campuses. These two real estate developments were legitimized by promises of technological innovation that would spearhead China’s transition to an innovation-driven economy. They accommodated both universities’ evolving spatial needs and revived underutilized spaces for more ‘productive’ purposes. Both universities worked with local government and external actors to develop their innovation complexes. However, their different academic strengths, prior experience with knowledge valorization and place histories affected the resulting partnerships and led to divergent outcomes. This comparison underscores the breadth of university real estate practices, evolving town–gown relationships, and the politics of urban regeneration, as China seeks to replace economic growth driven by land development with an innovation-driven economy.</t>
         </is>
       </c>
       <c r="L267" s="15" t="inlineStr">
@@ -15956,11 +16296,15 @@
         </is>
       </c>
       <c r="H272" s="11" t="inlineStr"/>
-      <c r="I272" s="11" t="inlineStr"/>
+      <c r="I272" s="11" t="inlineStr">
+        <is>
+          <t>Large language models; P-median problem; Spatial reasoning</t>
+        </is>
+      </c>
       <c r="J272" s="11" t="inlineStr"/>
-      <c r="K272" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K272" s="11" t="inlineStr">
+        <is>
+          <t>The p-median problem is a classical, NP-hard model in location science, and decades of research have produced exact, heuristic, and meta-heuristic algorithms to solve it. In parallel, large language models (LLMs) have begun to assist in optimization by interpreting problem descriptions and generating solver code; however, their intrinsic ability to reason about spatial structure in facility-location problems remains underexplored. We introduce an LLM-as-proposer framework for the discrete p-median problem that embeds an LLM within a classical local search with external evaluation. The LLM's contribution as a spatially informed proposer is evaluated within a controlled search structure and compared fairly with established heuristics. We benchmark the proposed framework with three frontier LLMs on six TSPLIB point sets commonly used in location analysis across multiple p facilities, comparing against (i) exact mixed-integer problem references and (ii) five classical heuristics and meta-heuristics baselines. Across all settings, LLM-guided search consistently outperforms greedy baselines, frequently attains near-optimal solutions on small-to-medium instances, and evaluates orders of magnitude fewer objectives than tabu search, although inference remains the dominant runtime cost. Prompt ablation further shows that some spatial summaries materially improve robustness on larger instances, whereas some local diagnostic cues can be counterproductive. Taken together, these results show that contemporary LLMs exhibit meaningful spatial reasoning as proposers in p-Median local search, while also clarifying the current gap to mature meta-heuristics in solution quality and computational efficiency, motivating continued exploration of hybrid designs as LLMs become more capable.</t>
         </is>
       </c>
       <c r="L272" s="12" t="inlineStr">
@@ -16010,11 +16354,15 @@
           <t>Environment &amp; health</t>
         </is>
       </c>
-      <c r="I273" s="14" t="inlineStr"/>
+      <c r="I273" s="14" t="inlineStr">
+        <is>
+          <t>Environmental inequality; Geographic information science; Graph neural networks; Health prescription modelling; Spatial data science; Urban analytics; Urban health</t>
+        </is>
+      </c>
       <c r="J273" s="14" t="inlineStr"/>
-      <c r="K273" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K273" s="14" t="inlineStr">
+        <is>
+          <t>Understanding how social, demographic, environmental, and spatial factors jointly shape urban outcomes is essential for sustainable urban development and evidence-based policy. Traditional statistical approaches often struggle to capture complex non-linear relationships, while many machine learning methods overlook the joint roles of spatial autocorrelation and network topology in urban systems. Recent advances in GeoAI have addressed these challenges only partially, often treating spatial effects, graph structure, evaluation, and interpretability separately. We present UST-GNN, a unified spatial–topological graph neural network framework that integrates neighbourhood connectivity, heterogeneous urban features, and positional/locational embeddings into a single representation. Using the MedSAT dataset, which contains over 150 environmental and socio-demographic variables and six prescription outcomes across 4835 neighbourhoods in Greater London, UST-GNN outperforms strong statistical, geographically enhanced, and graph Machine Learning baselines, improving out-of-sample R2 by 8.4–13.2% under strict spatial cross-validation. We further introduce a lightweight principal-component module to interpret learned node embeddings geographically and relate them to policy-relevant covariates. The resulting analyses recover established patterns, offer new perspectives on debated associations, and reveal novel predictors warranting further causal investigation. Together, these findings demonstrate the value of graph-based spatial machine learning for urban health analytics, environmental inequality assessment, and evidence-based urban policy. Beyond predictive gains, UST-GNN provides a unified GeoAI analytical pipeline that can be embedded into urban digital twin workflows for scenario testing, monitoring, and data-informed decision-making for healthier, more sustainable cities.</t>
         </is>
       </c>
       <c r="L273" s="15" t="inlineStr">
@@ -16060,11 +16408,15 @@
         </is>
       </c>
       <c r="H274" s="11" t="inlineStr"/>
-      <c r="I274" s="11" t="inlineStr"/>
+      <c r="I274" s="11" t="inlineStr">
+        <is>
+          <t>Big geospatial data; Human mobility; Intra-urban activity redistribution; Rainfall events; Spatiotemporal heterogeneity</t>
+        </is>
+      </c>
       <c r="J274" s="11" t="inlineStr"/>
-      <c r="K274" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K274" s="11" t="inlineStr">
+        <is>
+          <t>Extreme rainfall increasingly disrupts urban systems, yet its short-term effects on the spatial redistribution of intra-urban activity remain insufficiently quantified at the national scale. Leveraging more than 800 million hourly geolocation records from 200 Chinese cities and high-resolution meteorological data, we develop the Urban Spatial Dispersion Index (USDI) to capture the dispersion dimension of intra-urban activity. We then integrate this index into a multi-level mixed-effects framework to provide a nationwide, multi-context quantification of rainfall-associated changes in human activity distribution. Rainfall produces a distinctly nonlinear dispersion response: each 1 mm h−1 increase in intensity corresponds to a 0.9% rise in spatial dispersion, while high-intensity events trigger abrupt and disproportionate disruption. Dispersion sensitivity exhibits pronounced spatiotemporal heterogeneity, peaking during rigid mobility periods such as commuting hours and winter seasons, and displaying strong climatic asymmetry, with arid-region cities experiencing the strongest responses. Structural equation modeling links cross-city differences in dispersion sensitivity primarily to climatic background and urban development intensity, while green space and drainage infrastructure are associated with potential buffering effects. By quantifying high-resolution spatiotemporal inequalities in response sensitivity across cities and temporal contexts, this study advances urban mobility research from event-specific disruption toward systematic dispersion response regimes, providing a multi-context empirical foundation for climate-resilient urban systems.</t>
         </is>
       </c>
       <c r="L274" s="12" t="inlineStr">
@@ -16214,11 +16566,15 @@
           <t>AI &amp; digital economy</t>
         </is>
       </c>
-      <c r="I277" s="14" t="inlineStr"/>
+      <c r="I277" s="14" t="inlineStr">
+        <is>
+          <t>Difference-in-differences; Digital platforms; Remote sensing; Ridesharing; Transportation economics; Urban development; Urban periphery; Urban sprawl</t>
+        </is>
+      </c>
       <c r="J277" s="14" t="inlineStr"/>
-      <c r="K277" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K277" s="14" t="inlineStr">
+        <is>
+          <t>Digital platforms are reshaping how people navigate and interact with cities, yet assessing their impact on urban development remains challenging due to spatial and temporal uncertainty in observational data. This paper estimates the causal effect of digital rideshare platforms on urban expansion at the periphery of U.S. cities. Leveraging the staggered rollout of rideshare services such as Uber or Lyft between 2010 and 2015, we implement a difference-in-differences design that exploits variation in launch timing across 167 geographic units. To measure development, we combine satellite imagery with a convolutional neural network (CNN) and a spatio-temporal model that accounts for uncertainty in image classification. This approach produces consistent estimates of built-up land over time, which we use in our causal analysis. We find that access to rideshare services significantly increases the rate of development in network peripheral areas, particularly those with low transit accessibility. These findings are consistent with theoretical predictions from urban economic models, which posit that reductions in effective commuting costs expand the urban fringe. More broadly, our results highlight how digital transportation platforms—absent direct public investment—can reshape land use by altering the accessibility landscape of cities.</t>
         </is>
       </c>
       <c r="L277" s="15" t="inlineStr">
@@ -16268,11 +16624,15 @@
           <t>Natural resources &amp; conservation</t>
         </is>
       </c>
-      <c r="I278" s="11" t="inlineStr"/>
+      <c r="I278" s="11" t="inlineStr">
+        <is>
+          <t>Built environment; Machine learning; Natural hazards; Risk; Spatial data; Urban</t>
+        </is>
+      </c>
       <c r="J278" s="11" t="inlineStr"/>
-      <c r="K278" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K278" s="11" t="inlineStr">
+        <is>
+          <t>Understanding the relationship between the built environment (BE) and disaster impacts is critical for improving resilience and risk assessment in urban areas. This study investigates how the shape and organization of the BE is related to damage outcomes from Hurricane Harvey across multiple spatial scales and levels of the administrative hierarchy. Mixed Effects Random Forest (MERF) models incorporate distributional summaries of fractal dimension (FD) of the BE computed at the block group, tract, and county levels, combined with water network heterogeneity. These models assess whether hierarchically structured BE attributes can serve as reproducible, data-driven predictors of flood damage at the block group level within the Hurricane Harvey study region. The models perform consistently well across model specifications with county-level mean FD emerging as the dominant predictor measured by its feature importance, followed by tract- and block-group-level distributional features. The BE is organized around underlying structural dependencies, notably the water network, which further conditions damage severity through spatially heterogeneous waterway exposure. Random effects-only benchmarks, which retain the spatial grouping effects but omit all covariates, yield R2 ≈ 0 at every resolution, confirming that the predictive signal derives from BE and water network features rather than from spatial autocorrelation alone. Furthermore, the FD signal is robust to differences in building stock exposure across block groups. These findings demonstrate that the hierarchical organization of the BE constitutes a consistent predictor of flood damage susceptibility within the Hurricane Harvey study area and provides a methodological foundation for spatially structured damage prediction.</t>
         </is>
       </c>
       <c r="L278" s="12" t="inlineStr">
@@ -16962,9 +17322,9 @@
           <t>Travel dynamics under MaaS bundles: The role of uncertainty in intertemporal choices and learning behavior.</t>
         </is>
       </c>
-      <c r="K290" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K290" s="11" t="inlineStr">
+        <is>
+          <t>Mobility-as-a-Service (MaaS) bundles offer discounted access to multiple travel modes in exchange for a periodic subscription fee, encouraging travelers to better anticipate their mobility needs and thereby reducing operational uncertainty faced by service providers. However, this subscription model introduces complex intertemporal decision-making, as subscribers need to allocate a predetermined number of discounts across sequential trips within each bundle cycle. The uncertainty of real-world travel demand further complicates this allocation process. While these travel dynamics are crucial for designing effective MaaS bundles, little is known about how such intertemporal choices evolve over the long term. This study investigates travel dynamics under MaaS bundles across varying uncertainty levels. A dynamic discrete choice model (DDCM) that accounts for bundle constraints is developed to capture two dimensions of behavioral dynamics: (1) intertemporal decision-making within each subscription cycle, and (2) learning effects across multiple subscription cycles. As users gain experience with MaaS bundles, they place less weight on travel time and cost. Over repeated cycles, travelers demonstrate a declining preference for private cars and ride-sourcing, particularly for planned trips, whereas this adaptive shift is less pronounced under uncertain travel demand. Furthermore, users strategically conserve discounts when facing high demand uncertainty. These findings demonstrate a shift in user focus from trip-level attributes to bundle-level resource management, suggesting that the attractiveness of MaaS can be improved through tailoring bundle design and effective marketing strategy to accommodate travel demand uncertainty.</t>
         </is>
       </c>
       <c r="L290" s="12" t="inlineStr">
@@ -17024,9 +17384,9 @@
           <t>Desirable bikeshare routes: Nonlinear impacts of micro-level street environments.</t>
         </is>
       </c>
-      <c r="K291" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K291" s="14" t="inlineStr">
+        <is>
+          <t>Facilitating an attractive and safe street environment (SE) for cyclists can yield multifaceted benefits for sustainable, healthy cities. However, due to limited urban-scale trajectory data, the influence of micro-level SE (e.g., trees, shrubs, perceptions, and road cracks) on cyclists’ route preferences remains less understood. Using over 4,000 Lime Dockless Bikeshare trajectories, this study constructed a Desirable Bikeshare Index (DBI) that measures differences between observed trips and the shortest routes suggested by Google Maps at the street-segment level. Using computer vision, road damage was detected in street view images, alongside objective streetscape features and subjective perceptions (e.g., enclosure) to characterize micro-level SEs comprehensively. Nonlinear associations between SE and DBI were identified using explainable machine learning algorithms, and customer satisfaction theory (e.g., basic, excitement, performance factors) was adopted to interpret the threshold effects. Contrary to earlier findings, green spaces do not always attract cyclists – lush trees draw cyclists, while too many shrubs repel them. Moreover, sidewalks are a must-have (basic factor), while road damage is more common where cyclists aggregate, underscoring the need for timely monitoring and maintenance of bicycle infrastructure. Perceptions of accessibility, order, and richness are excitement factors that explain route desirability. Interestingly, perceived ecology and enclosure promote cycling at low values, then quickly play a negative role beyond mid-to-high values. Our findings underscore the need to combine subjective perceptions with objective streetscapes to delineate a comprehensive micro-level SE. Urban designers and transport planners can leverage revealed thresholds to implement cost-effective infrastructure upgrades that facilitate desirable street environments for cyclists.</t>
         </is>
       </c>
       <c r="L291" s="15" t="inlineStr">
@@ -17086,9 +17446,9 @@
           <t>A systematic review of quantitative assessments of traffic-focused urban air quality regulations.</t>
         </is>
       </c>
-      <c r="K292" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K292" s="11" t="inlineStr">
+        <is>
+          <t>This systematic review follows PRISMA 2020 guidelines to identify whether measurable impacts have been observed following urban air quality interventions targeting private road users. A structured search was conducted on Scopus in February 2025, identifying 2088 studies. After applying strict inclusion criteria - requiring studies to examine urban-scale air quality interventions, target private road users, and apply quantitative ex post causal inference techniques - 59 studies were included for review. Our review examines publication trends, geographic focus, outlets, methods, key variables, and overall findings, classifying impacts on air quality, economic, behavioural, and health outcomes as positive, mixed, or negative. We identify three intervention types: (1) vehicle bans by type/time, (2) access charges for urban areas, and (3) fines for non-compliant vehicles. When splitting the papers by intervention type, outcome studied, and categorisation of impact, sample sizes become small. Only for intervention types (1) and (3), is there a sample of ≥ 10 studies examining the impacts on one outcome: air quality. Of these papers, a higher proportion examining fines for non-compliance found positive effects on air quality. While studies commonly report improvements in air quality and health, results are mixed for behavioural and economic variables. This review provides an up-to-date synthesis of policy effectiveness and highlights methodological and geographic gaps in the literature, supporting future evidence-based policy design.</t>
         </is>
       </c>
       <c r="L292" s="12" t="inlineStr">
@@ -17148,9 +17508,9 @@
           <t>Consumer preferences for uncrewed aerial vehicles delivery service.</t>
         </is>
       </c>
-      <c r="K293" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K293" s="14" t="inlineStr">
+        <is>
+          <t>The rapid advancement of technology has led to the emergence of innovative solutions in delivery services, notably unmanned aerial vehicles (UAVs), or drones. This study investigates consumer preferences for UAV-based delivery services using data from a nationwide stated choice experiment conducted with 1,000 Australian respondents. The experiment covered four delivery contexts − letters, food, medicine, and general goods − by varying key attributes such as delivery time, cost, and item type, with an aim for both geographic and demographic representativeness. The data were analysed using a latent class choice model, which identified distinct consumer segments with varying sensitivities to pricing, delivery urgency, and non-monetary concerns such as privacy and safety. Results indicate that, all else being equal, the market share of UAV delivery ranges from 33% for food delivery to 41% for letters. Respondents show greater interest in using UAVs for lighter and time-sensitive items such as letters and medicine, while they are less inclined to use drones for food delivery. Safety and reliability emerge as key concerns across most segments. Generally, younger adults, individuals with higher education and income levels, and those with greater familiarity with drones are more inclined to adopt UAV delivery services. Australians also demonstrate a wide range of willingness to pay for faster delivery − ranging from A$0.30 for letters to A$4.90 for food delivered within five minutes. This study contributes to a deeper understanding of consumer preferences in UAV delivery and offers practical insights for businesses, policymakers, and researchers navigating this evolving landscape.</t>
         </is>
       </c>
       <c r="L293" s="15" t="inlineStr">
@@ -17210,9 +17570,9 @@
           <t>Congestion pricing in New York city: Effects on ride-hailing and transit.</t>
         </is>
       </c>
-      <c r="K294" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K294" s="11" t="inlineStr">
+        <is>
+          <t>On January 5, 2025, New York City implemented the Central Business District Tolling Program (CBDTP), which includes a $1.50 per-trip charge on for-hire vehicles operating within the Central Business District. This study examines the effects of the per-trip charge on Uber, Lyft, and subway ridership using a two-way fixed effects design. Leveraging Lyft's temporary $1.50 rider credit in January 2025, we isolate platform-specific responses to this $1.50 charge. We find that Uber trips declined by up to 6%, while Lyft trips increased by 2–5% during the subsidy period and remained slightly elevated afterward. At the aggregate level, overall ride-hailing volume fell by 0.5–1.5%, while subway ridership rose by approximately 1%. Heterogeneity analyses show that the response was concentrated among short trips and low-fare rides, which declined by over 9% and 35%, respectively, while longer and higher-fare trips were largely unaffected. We also find that base fares and platform revenue per trip increased, especially for Uber, while driver pay gains were limited. These findings highlight how the CBDTP per-trip charge and platforms’ pricing strategies jointly shape ridership patterns and prices.</t>
         </is>
       </c>
       <c r="L294" s="12" t="inlineStr">
@@ -17272,9 +17632,9 @@
           <t>Bilevel subsidy-enabled mobility hub network design with perturbed utility coalitional choice-based assignment.</t>
         </is>
       </c>
-      <c r="K295" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K295" s="14" t="inlineStr">
+        <is>
+          <t>Urban mobility is undergoing rapid transformation with the emergence of new services. Mobility hubs (MHs) have been proposed as physical-digital convergence points, offering a range of public and private mobility options in close proximity. By supporting Mobility-as-a-Service, these hubs can serve as focal points where travel decisions intersect with operator strategies. We develop a bilevel MH platform design model that treats MHs as control levers. The upper level (platform) maximizes revenue or flow by setting OD based pricing to travelers and subsidies to incentivize last-mile operators. The lower level captures joint traveler-operator decisions with a link-based Perturbed Utility Route Choice (PURC) assignment, yielding a strictly convex quadratic program. We reformulate the bilevel problem to a single-level program via the KKT conditions of the lower level and solve it with a gap-penalty method and an iterative warm-start scheme that exploits the computationally cheap lower-level problem. Numerical experiments on a toy network and a Long Island Rail Road (LIRR) case (380 nodes, 642 links, 78 ODs) show that the method attains sub-1% optimality gaps in less than 30 min. In the base LIRR case, the model allows policymakers to set the optimal platform access fee and operator subsidy. We then evaluate the impact of operator competition, quantify the social surplus value of a MH, and how restrictive subsidy can discourage operator participation.</t>
         </is>
       </c>
       <c r="L295" s="15" t="inlineStr">
@@ -17334,9 +17694,9 @@
           <t>Regional population mobility network changes driven by central city lockdowns.</t>
         </is>
       </c>
-      <c r="K296" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K296" s="11" t="inlineStr">
+        <is>
+          <t>Drawing on China Mobile cellphone signaling data, this study uses 128 sub-cities in the core area of the Yangtze River Delta as units of analysis. Employing complex network topology metrics, a Weighted Stochastic Block Model, and improved Within-module degree and Participation coefficients, this study systematically examines the evolutionary characteristics of the regional intercity population mobility network at the macro-, meso-, and micro-scales before, during, and after Shanghai's 2022 lockdown. The findings are as follows: At the macro level, network connectivity and efficiency declined significantly during the lockdown, then rapidly recovered and achieved adaptive optimization. At the meso level, the network structure underwent a systematic transition—from a multi-community homogeneous structure before the lockdown to a hybrid structure combining core-periphery and random connections during the lockdown, and finally to a nested multi-community structure after the lockdown. At the micro level, most nodes in the network were peripheral, whereas a few key nodes performed core functions; their roles and numbers changed mainly during periods of network volatility and were not strongly correlated with overall mobility. The study demonstrates that regional population mobility networks possess intrinsic resilience mechanisms. Although the lockdown of a megacity temporarily deconstructed the original intercity travel network, the network tended toward localized or regional reintegration during the recovery phase. This research extends the theoretical perspective at the urban sub-city scale over a large regional scope and provides scientific evidence and policy references for pandemic control strategies, regional resilience planning, and coordinated development of urban agglomerations.</t>
         </is>
       </c>
       <c r="L296" s="12" t="inlineStr">
@@ -17396,9 +17756,9 @@
           <t>Revolutionizing elderly mobility through autonomous demand-responsive transport services.</t>
         </is>
       </c>
-      <c r="K297" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K297" s="14" t="inlineStr">
+        <is>
+          <t>The ageing population presents a global demographic challenge, as elderly mobility declines rapidly due to their lack of stable income and limited physical and cognitive abilities. Autonomous demand-responsive transport emerges as a potential solution to cater to their specific transport needs. To comprehend their acceptance and adoption of autonomous demand-responsive transport, a stated preference survey was conducted, interviewing 232 elderly individuals aged 60 or above in Hong Kong. The design of choice experiments was pivoted with respect to revealed trips from the surveyed elderly to simulate realistic choice scenarios. Using the collected data, logit models were developed to identify contributory factors influencing their mode choice between their currently chosen alternative and the new transport mode. The results indicate that travel fare, walk time, on-street wait time, in-vehicle travel time, seat availability, and the provision of on-board staff are the significant attributes. Notably, seat availability possesses the highest impact among all attributes. It is therefore recommended that seats should be reserved in conjunction with the demand-responsive service. An unobserved heterogeneity among the elderly is identified in the provision of on-board staff. About 35% of them hold a negative perception of this arrangement while others were more likely to adopt an on-board staff member for safety concerns. The study highlights that the elderly were hesitant to shift to autonomous demand-responsive transport due to their concerns about autonomous driving and digital proficiency. As such, it is recommended that the implementation of autonomous demand-responsive transport should be progressive in a transit-oriented city.</t>
         </is>
       </c>
       <c r="L297" s="15" t="inlineStr">
@@ -17458,9 +17818,9 @@
           <t>Vehicle design dictates the geography of urban air mobility accessibility.</t>
         </is>
       </c>
-      <c r="K298" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K298" s="11" t="inlineStr">
+        <is>
+          <t>The advent of Urban Air Mobility (UAM) demands a fundamental re-evaluation of the reciprocal relationship between emerging vehicle technologies and the established urban form. Beyond the immediate challenges of engineering optimisation, this study posits that electric vertical takeoff and landing (eVTOL) aircraft design parameters function as primary determinants of metropolitan accessibility, equity, and spatial structure. By developing an integrated infrastructure-cost framework applied to 283,647 building footprints in Shanghai, we systematically trace how seemingly technical choices, specifically wingspan and seating capacity—cascade through the rigid constraints of the built environment to produce profound, often unanticipated societal outcomes. The empirical analysis reveals a decisive “spatial filtering” mechanism: as vehicle wingspan increases from 6 to 16 m, feasible vertiport sites decline by 75.7 percent, with aggregate network capacity collapsing by 93.0 percent. Crucially, this attrition is disproportionately concentrated in dense, high-value central districts, effectively forcing larger aircraft to the urban periphery. These findings challenge the prevailing technology-centric discourse, demonstrating that the accumulated legacy of urban morphology—building codes and land use patterns unrelated to aviation—acts as a binding constraint on technological deployment. Consequently, the interaction between vehicle and infrastructure dictates the economic geography of the system. We find that optimised, compact Multirotor configurations achieve costs of $0.063 per passenger-kilometre, drastically undercutting larger winged architectures not merely due to energy efficiency, but through superior infrastructure compatibility. This implies that design decisions made upstream in the manufacturing process carry embedded assumptions about who will benefit from aerial mobility: compact designs foster accessible, city-centre integration, while larger footprints risk entrenching UAM as a premium, exclusionary service restricted to peripheral corridors. Ultimately, this study illustrates that new mobility modes do not simply reshape the city; they are profoundly shaped by it. We argue that vehicle design cannot be treated in isolation from the urban systems it serves. For planners and policymakers, this underscores that preserving optionality for equitable transportation requires foresight into how the physical constraints of the city interact with the dimensions of the machine, demanding a holistic approach to designing our urban futures.</t>
         </is>
       </c>
       <c r="L298" s="12" t="inlineStr">
@@ -17520,9 +17880,9 @@
           <t>Urban traffic evaluation with social media data: A consensus-based LLM negotiation paradigm.</t>
         </is>
       </c>
-      <c r="K299" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K299" s="14" t="inlineStr">
+        <is>
+          <t>Evaluating urban traffic systems from the perspective of travelers is critical for traffic planning and operations management, and social media data has been proven to be a rich and timely source for extracting travel experiences. However, it is challenging to evaluate urban traffic using social media data due to difficulties in obtaining a high-quality dataset that reveals travel experiences and conducting precise evaluations based on the collected posts. With recent advancements in large language models (LLMs), this paper establishes a consensus-based LLM negotiation paradigm to address these challenges. Firstly, we propose an LLM-driven automated data collection and processing pipeline for social media data. Specifically, the understanding and reasoning abilities of LLMs facilitate filtering the obtained raw data with high accuracy. More importantly, LLMs do not require any manual labeling of data or extensive pre-training compared to traditional machine learning methods. As for the evaluation system, we leverage the LLMs to cluster and summarize the key indicators for urban traffic evaluation. Furthermore, we propose a consensus-based LLM negotiation mechanism in which two distinct LLMs serve as the generator and discriminator, respectively. They iteratively evaluate and refine their assessments for each social media post until consensus is reached. In this way, the text data is classified into its associated indicators, with scores assigned based on sentiment analysis. Lastly, we propose the LLM-augmented analytic hierarchy process (AHP), by which the weights of each indicator are determined by LLMs with different role-playing prompts. The effectiveness of the proposed framework is validated in Shanghai and Beijing using social media posts collected from Weibo. The obtained dataset by LLMs is significantly enhanced in both quality and quantity. Moreover, the negotiation mechanism of LLMs can provide not only reliable and robust evaluation results, but also identify key issues behind the evaluation results and offer targeted and precise suggestions. This paper contributes to the use of LLMs in future traffic evaluation and operations.</t>
         </is>
       </c>
       <c r="L299" s="15" t="inlineStr">
@@ -17582,9 +17942,9 @@
           <t>Optimal timetabling and charger deployment for urban–rural electric bus services: Formulation and case study.</t>
         </is>
       </c>
-      <c r="K300" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K300" s="11" t="inlineStr">
+        <is>
+          <t>The electrification of rural bus systems is increasingly advocated as a critical strategy for achieving low-carbon transportation goals. However, the unique challenges of these areas, including sparse passenger demand, extended route lengths, and poor stop accessibility, often render electric bus systems economically inefficient compared to their urban counterparts. This paper presents an optimization model for jointly planning timetables and charging infrastructure for urban–rural battery electric bus (BEB) services, aiming to minimize both passenger and operator costs. The model incorporates en-route charging and flexible battery sizing to capitalize on time-of-use electricity tariffs. An adaptive large neighborhood search (ALNS) algorithm is developed to solve the proposed model efficiently. Using a real-world case study from Chibi City China, we demonstrate the model's application through comparing various charging modes against the existing operational scheme. The results reveal that the introduction of BEBs with en-route charging can create a “triple-win” outcome for passengers, operators, and society. Specifically, the optimized en-route charging system reduces total social costs by 28% compared to the current scheme and cuts carbon emissions by 44% relative to traditional diesel bus operations.</t>
         </is>
       </c>
       <c r="L300" s="12" t="inlineStr">
@@ -17644,9 +18004,9 @@
           <t>Social psychological and contextual drivers of cargo bike usage: Insights from a comprehensive structural equation model.</t>
         </is>
       </c>
-      <c r="K301" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K301" s="14" t="inlineStr">
+        <is>
+          <t>Cargo bikes represent a promising yet often overlooked alternative to cars for private and commercial transportation purposes. While previous research examined the determinants of mode choice across various modes of transportation, much less is known about the interplay of different categories of determinants on cargo bike use, particularly for private transportation. This study aims to address this research gap by building on a comprehensive survey of 2590 private cargo bike-sharing users in Germany. Using a structural equation model, an adapted version of the Comprehensive Action Determination Model is tested to explain cargo bike usage for private transportation purposes. Thus, this study investigates the relationship and interplay of normative and value-based processes (i.e., sufficiency orientation), perceived and objective situational constraints, demographic characteristics, intentional processes, and habitual processes. The results indicate a good overall fit of the model combining social psychological with contextual factors. In particular, the findings suggest that private cargo bike usage can be predicted by well-established concepts from psychological research (i.e., the Theory of Planned Behavior) when complemented by additional constructs such as bicycle weather orientation. Based on the results, implications for future research as well as for policy makers are derived.</t>
         </is>
       </c>
       <c r="L301" s="15" t="inlineStr">
@@ -17706,9 +18066,9 @@
           <t>Do intentions translate into use? Transit market evolution and intention-behavior gaps after a new BRT service in Montreal, Canada.</t>
         </is>
       </c>
-      <c r="K302" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K302" s="11" t="inlineStr">
+        <is>
+          <t>This study investigates how transit market profiles evolve and how intentions align with actual behavior following the implementation of a Bus Rapid Transit (BRT) system in Montreal, Canada. While prior research has focused primarily on ridership trends, this paper adopts a behavioral lens, integrating market segmentation and the intention-behavior gap concept to examine individual-level behavior. Drawing on longitudinal data from the Montreal Mobility Survey, the analysis uses a pre-BRT sample of 578 respondents (2021) and a post-BRT sample of 1882 respondents (2023–2024), including a panel of 209 individuals who responded before and after implementation. Using exploratory factor analysis and weighted k-means clustering, four market profiles were identified both before and after implementation: transit-reliant riders, telecommuter choice riders, walkability-oriented individuals, and car-oriented individuals. While the profile structure was consistent at the aggregate level, panel tracking showed heterogeneous profile stability: car-oriented individuals were most likely to remain in their baseline profile, whereas telecommuter choice riders were most likely to transition to a different profile. A separate multinomial model assessed the intention-behavior gap, revealing that closeness to the infrastructure can influence intention follow-through. The results provide empirical evidence that infrastructure alone is insufficient to ensure adoption and suggest that targeted interventions are necessary to bridge the gap between intention and use. The findings in this study can be of interest to transit agencies and policymakers interested in user-centered public transit planning strategies.</t>
         </is>
       </c>
       <c r="L302" s="12" t="inlineStr">
@@ -17768,9 +18128,9 @@
           <t>How teleworking reshapes travel distance and mode use for work and non-work tours: A panel analysis.</t>
         </is>
       </c>
-      <c r="K303" s="17" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K303" s="14" t="inlineStr">
+        <is>
+          <t>This paper investigates the effects of teleworking on tour generation and travel distance for home-based work and non-work tours using various modes of transportation. We analyzed three waves of the Netherlands Mobility Panel, collected in 2017, 2018, and 2019. Six zero-inflated gamma mixed effect models of travel distance by car, active modes, and public transportation for work and non-work tours were estimated with teleworking duration as a key explanatory variable. Our models incorporated differences in traveler's mode use preferences by categorizing individuals into exclusive mode users and multimodal travelers based on their levels of car, active mode, and public transportation use across the three survey waves. The results of our analyses revealed that teleworking led to fewer work tours but also to increased distances of non-work tours using cars and active modes. In addition, while teleworking was found to reduce the distances of work tours, these reductions were greater for travelers who exclusively used the car or active modes compared to multimodal travelers. Our findings suggest that the relationship between teleworking, tour generation, and travel distances varies by tour purpose, type of mode used, and individuals’ long-term mode use preferences. This highlights the importance of considering travel modes and trip purposes in investigating the impact of teleworking.</t>
         </is>
       </c>
       <c r="L303" s="15" t="inlineStr">
@@ -17830,9 +18190,9 @@
           <t>Understanding walking route choice preferences and pedestrian network flows: From individual trajectories to city-scale patterns using empirical data from Sydney.</t>
         </is>
       </c>
-      <c r="K304" s="16" t="inlineStr">
-        <is>
-          <t>— (abstract not auto-retrieved; open via link)</t>
+      <c r="K304" s="11" t="inlineStr">
+        <is>
+          <t>This study investigates the influence of built environment factors on pedestrian route choices in an urban context using passively collected mobile phone trajectory data from Sydney, Australia. We estimate and compare multiple discrete choice models including C-Logit, Path Size Logit (PSL), and Error Component (EC) models to quantify associations between pedestrian route choices and route characteristics such as distance, slope, turns, crossings, amenities, and greenery. The models are applied to a high-resolution sidewalk network to simulate pedestrian flows across the city. Our findings are broadly consistent with existing literature, highlighting the importance of route simplicity, directness, and terrain in walking behavior. A key contribution of this study is the integration of passively collected GPS trajectories with route choice modeling and network-level flow assignment, demonstrating a scalable framework for understanding and forecasting pedestrian behavior. The approach enables city-scale assessments of pedestrian infrastructure and offers valuable insights for data-driven planning of walkable urban environments.</t>
         </is>
       </c>
       <c r="L304" s="12" t="inlineStr">
@@ -23431,7 +23791,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
@@ -23467,7 +23827,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
@@ -23485,7 +23845,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
@@ -23503,7 +23863,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
@@ -23539,7 +23899,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
@@ -23611,7 +23971,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
@@ -23629,7 +23989,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
@@ -23665,7 +24025,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
@@ -23683,7 +24043,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
@@ -23701,7 +24061,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
@@ -23737,7 +24097,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
@@ -23773,7 +24133,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
@@ -23791,7 +24151,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
@@ -23845,7 +24205,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
@@ -23863,7 +24223,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" s="25" t="inlineStr">
         <is>
@@ -23895,7 +24255,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
@@ -23913,7 +24273,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
@@ -24393,7 +24753,7 @@
         <v>393</v>
       </c>
       <c r="D63" s="27" t="n">
-        <v>201</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/briefing.xlsx
+++ b/briefing.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All papers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All papers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Journal index" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All papers'!$A$1:$L$663</definedName>
@@ -625,7 +625,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rolling archive across 15 journals · last updated 2026-08-18</t>
+          <t>Rolling archive across 15 journals · last updated 2026-08-24</t>
         </is>
       </c>
     </row>
